--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -1313,25 +1313,17 @@
           <t>The MongolZ</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D24" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="n">
+        <v>22</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,17 +474,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Falcons</t>
+          <t>Vitality</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -494,7 +494,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -512,17 +512,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Furia</t>
+          <t>Astralis</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -532,7 +532,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -550,27 +550,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FaZe</t>
+          <t>Liquid</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Liquid</t>
+          <t>Mythic</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -603,12 +603,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -626,17 +626,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Iluminar Gaming</t>
+          <t>Heroic</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -664,12 +664,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NAVI</t>
+          <t>Fnatic</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -679,12 +679,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -702,17 +702,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Imperial</t>
+          <t>FaZe</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spirit</t>
+          <t>BIG</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -755,12 +755,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -778,17 +778,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BC.Game</t>
+          <t>ENCE</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Astana Dragons</t>
+          <t>Ninjas in Pyjamas</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -831,12 +831,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Copenhagen Wolves</t>
+          <t>FURIA</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -892,17 +892,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Copenhagen Flames</t>
+          <t>Legacy</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -930,17 +930,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>TYLOO</t>
+          <t>MIBR</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -950,7 +950,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -968,17 +968,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Outsiders</t>
+          <t>Natus Vincere</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Heroic</t>
+          <t>MOUZ</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1021,12 +1021,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1044,27 +1044,27 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Dignitas</t>
+          <t>G2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1082,27 +1082,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>iBUYPOWER</t>
+          <t>OG</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1120,32 +1120,32 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Fnatic</t>
+          <t>paiN</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Vitality</t>
+          <t>Imperial</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1173,12 +1173,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1196,27 +1196,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SK Gaming</t>
+          <t>Virtus.pro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1234,27 +1234,27 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>mousesports</t>
+          <t>Spirit</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ninjas in Pyjamas</t>
+          <t>Entropiq</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1287,12 +1287,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1310,25 +1310,5381 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
+          <t>Copenhagen Flames</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="n">
+        <v>24</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Envy</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="n">
+        <v>25</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>iBUYPOWER</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="n">
+        <v>26</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Evil Geniuses</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="n">
+        <v>27</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Dignitas</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="n">
+        <v>28</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Cloud9</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="n">
+        <v>29</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="n">
+        <v>30</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Luminosity</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="n">
+        <v>31</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Vexed</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="n">
+        <v>32</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Iluminar</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="n">
+        <v>33</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Falcons</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="n">
+        <v>34</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Sangal</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="n">
+        <v>35</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>ShindeN</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="n">
+        <v>36</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>SAW</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" t="n">
+        <v>37</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Nexus</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" t="n">
+        <v>38</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>9Pandas</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" t="n">
+        <v>39</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Passion UA</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" t="n">
+        <v>40</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>ARCRED</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" t="n">
+        <v>41</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Qiang</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" t="n">
+        <v>42</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Permitta</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" t="n">
+        <v>43</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Rebels</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" t="n">
+        <v>44</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Eternal Fire</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" t="n">
+        <v>45</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>3DMAX</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" t="n">
+        <v>46</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" t="n">
+        <v>47</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Complexity</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" t="n">
+        <v>48</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>M80</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" t="n">
+        <v>49</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Wildcard</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" t="n">
+        <v>50</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>BESTIA</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" t="n">
+        <v>51</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>ECSTATIC</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" t="n">
+        <v>52</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>RED Canids</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" t="n">
+        <v>53</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" t="n">
+        <v>54</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>KRU</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" t="n">
+        <v>55</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Elevate</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" t="n">
+        <v>56</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>GamerLegion</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" t="n">
+        <v>57</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Underground</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" t="n">
+        <v>58</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>9z</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" t="n">
+        <v>59</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Orbit</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" t="n">
+        <v>60</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Limitless</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" t="n">
+        <v>61</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Homyno</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" t="n">
+        <v>62</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Take Flyte</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" t="n">
+        <v>63</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>The Huns</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" t="n">
+        <v>64</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Sharks</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" t="n">
+        <v>65</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>ODDIK</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" t="n">
+        <v>66</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>inSanitY</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="n">
+        <v>66</v>
+      </c>
+      <c r="B68" t="n">
+        <v>67</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Team Solid</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="n">
+        <v>67</v>
+      </c>
+      <c r="B69" t="n">
+        <v>68</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Bounty Hunters</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="n">
+        <v>68</v>
+      </c>
+      <c r="B70" t="n">
+        <v>69</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Galorys</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" t="n">
+        <v>70</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Spirit Academy</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="n">
+        <v>70</v>
+      </c>
+      <c r="B72" t="n">
+        <v>71</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Tricked</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="n">
+        <v>71</v>
+      </c>
+      <c r="B73" t="n">
+        <v>72</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
           <t>The MongolZ</t>
         </is>
       </c>
-      <c r="D24" t="n">
-        <v>2</v>
-      </c>
-      <c r="E24" t="n">
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="n">
+        <v>72</v>
+      </c>
+      <c r="B74" t="n">
+        <v>73</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>FlyQuest</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="n">
+        <v>73</v>
+      </c>
+      <c r="B75" t="n">
+        <v>74</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>PARIVISION</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="n">
+        <v>74</v>
+      </c>
+      <c r="B76" t="n">
+        <v>75</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Lynn Vision</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="n">
+        <v>75</v>
+      </c>
+      <c r="B77" t="n">
+        <v>76</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>VP.Prodigy</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="n">
+        <v>76</v>
+      </c>
+      <c r="B78" t="n">
+        <v>77</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>TALON</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="n">
+        <v>77</v>
+      </c>
+      <c r="B79" t="n">
+        <v>78</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Arcade</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="n">
+        <v>78</v>
+      </c>
+      <c r="B80" t="n">
+        <v>79</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>NAVI Junior</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="n">
+        <v>79</v>
+      </c>
+      <c r="B81" t="n">
+        <v>80</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>BC.Game</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="n">
+        <v>80</v>
+      </c>
+      <c r="B82" t="n">
+        <v>81</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Vantage</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="n">
+        <v>81</v>
+      </c>
+      <c r="B83" t="n">
+        <v>82</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>TYLOO</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="n">
+        <v>82</v>
+      </c>
+      <c r="B84" t="n">
+        <v>83</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>CatEvil</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="n">
+        <v>83</v>
+      </c>
+      <c r="B85" t="n">
+        <v>84</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Outsiders</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="n">
+        <v>84</v>
+      </c>
+      <c r="B86" t="n">
+        <v>85</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Chinggis Warrios</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="n">
+        <v>85</v>
+      </c>
+      <c r="B87" t="n">
+        <v>86</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>ATOX</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="n">
+        <v>86</v>
+      </c>
+      <c r="B88" t="n">
+        <v>87</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>IHC</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="n">
+        <v>87</v>
+      </c>
+      <c r="B89" t="n">
+        <v>88</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>MenaceGG</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="B90" t="n">
+        <v>89</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>The Dice</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="n">
+        <v>89</v>
+      </c>
+      <c r="B91" t="n">
+        <v>90</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>ad hoc</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="n">
+        <v>90</v>
+      </c>
+      <c r="B92" t="n">
+        <v>91</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Aravt</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="n">
+        <v>91</v>
+      </c>
+      <c r="B93" t="n">
+        <v>92</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Gods Reign</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="n">
+        <v>92</v>
+      </c>
+      <c r="B94" t="n">
+        <v>93</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>True Rippers</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="n">
+        <v>93</v>
+      </c>
+      <c r="B95" t="n">
+        <v>94</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Alliance</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="B96" t="n">
+        <v>95</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Carnival</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="B97" t="n">
+        <v>96</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Wings Up</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="n">
+        <v>96</v>
+      </c>
+      <c r="B98" t="n">
+        <v>97</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Nemiga</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="n">
+        <v>97</v>
+      </c>
+      <c r="B99" t="n">
+        <v>98</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Red Viperz</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="B100" t="n">
+        <v>99</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Victores Sumus</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="n">
+        <v>99</v>
+      </c>
+      <c r="B101" t="n">
+        <v>100</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Onyx Ravens</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="B102" t="n">
+        <v>101</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Skinvault</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>-6</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="n">
+        <v>101</v>
+      </c>
+      <c r="B103" t="n">
+        <v>102</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Reason Gaming</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="n">
+        <v>102</v>
+      </c>
+      <c r="B104" t="n">
+        <v>103</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Bad News Eagles</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="n">
+        <v>103</v>
+      </c>
+      <c r="B105" t="n">
+        <v>104</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Wizards</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="n">
+        <v>104</v>
+      </c>
+      <c r="B106" t="n">
+        <v>105</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>devils.one</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="B107" t="n">
+        <v>106</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>LCDC</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="n">
+        <v>106</v>
+      </c>
+      <c r="B108" t="n">
+        <v>107</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Enemy</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="n">
+        <v>107</v>
+      </c>
+      <c r="B109" t="n">
+        <v>108</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Titan</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="n">
+        <v>108</v>
+      </c>
+      <c r="B110" t="n">
+        <v>109</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>hoorai</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="n">
+        <v>109</v>
+      </c>
+      <c r="B111" t="n">
+        <v>110</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>GODSENT</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="n">
+        <v>110</v>
+      </c>
+      <c r="B112" t="n">
+        <v>111</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Verdant</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="n">
+        <v>111</v>
+      </c>
+      <c r="B113" t="n">
+        <v>112</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Kappa Bar</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="n">
+        <v>112</v>
+      </c>
+      <c r="B114" t="n">
+        <v>113</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>MAD Lions</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="n">
+        <v>113</v>
+      </c>
+      <c r="B115" t="n">
+        <v>114</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Copenhagen Wolves</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="n">
+        <v>114</v>
+      </c>
+      <c r="B116" t="n">
+        <v>115</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Astana Dragons</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="n">
+        <v>115</v>
+      </c>
+      <c r="B117" t="n">
+        <v>116</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>VeryGames</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="n">
+        <v>116</v>
+      </c>
+      <c r="B118" t="n">
+        <v>117</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>mousesports</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="n">
+        <v>117</v>
+      </c>
+      <c r="B119" t="n">
+        <v>118</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Vox Eminor</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="n">
+        <v>118</v>
+      </c>
+      <c r="B120" t="n">
+        <v>119</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>LGB eSports</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="n">
+        <v>119</v>
+      </c>
+      <c r="B121" t="n">
+        <v>120</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Epsilon</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="n">
+        <v>120</v>
+      </c>
+      <c r="B122" t="n">
+        <v>121</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>ESC</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="n">
+        <v>121</v>
+      </c>
+      <c r="B123" t="n">
+        <v>122</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Bravado</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="n">
+        <v>122</v>
+      </c>
+      <c r="B124" t="n">
+        <v>123</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Team Kinguin</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="n">
+        <v>123</v>
+      </c>
+      <c r="B125" t="n">
+        <v>124</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Counter Logic Games</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="n">
+        <v>124</v>
+      </c>
+      <c r="B126" t="n">
+        <v>125</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Gambit</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="n">
+        <v>125</v>
+      </c>
+      <c r="B127" t="n">
+        <v>126</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Space Soldiers</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="n">
+        <v>126</v>
+      </c>
+      <c r="B128" t="n">
+        <v>127</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Quantum Bellator Fire</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="n">
+        <v>127</v>
+      </c>
+      <c r="B129" t="n">
+        <v>128</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Avangar</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="n">
+        <v>128</v>
+      </c>
+      <c r="B130" t="n">
+        <v>129</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Misfits</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="B131" t="n">
+        <v>130</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Sprout</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="n">
+        <v>130</v>
+      </c>
+      <c r="B132" t="n">
+        <v>131</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Flash</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="n">
+        <v>131</v>
+      </c>
+      <c r="B133" t="n">
+        <v>132</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>100 Thieves</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="n">
+        <v>132</v>
+      </c>
+      <c r="B134" t="n">
+        <v>133</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Immortals</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="n">
+        <v>133</v>
+      </c>
+      <c r="B135" t="n">
+        <v>134</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Rogue</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="n">
+        <v>134</v>
+      </c>
+      <c r="B136" t="n">
+        <v>135</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>FORZE</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="n">
+        <v>135</v>
+      </c>
+      <c r="B137" t="n">
+        <v>136</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>00 Nation</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="n">
+        <v>136</v>
+      </c>
+      <c r="B138" t="n">
+        <v>137</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Into the Beach</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="n">
+        <v>137</v>
+      </c>
+      <c r="B139" t="n">
+        <v>138</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Movistar KOI</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="n">
+        <v>138</v>
+      </c>
+      <c r="B140" t="n">
+        <v>139</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>FLuffy Gangsters</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="n">
+        <v>139</v>
+      </c>
+      <c r="B141" t="n">
+        <v>140</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>NIP Impact</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="n">
+        <v>140</v>
+      </c>
+      <c r="B142" t="n">
+        <v>141</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>FlyQuest RED</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="n">
+        <v>141</v>
+      </c>
+      <c r="B143" t="n">
+        <v>142</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Heroic Academy</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="n">
+        <v>142</v>
+      </c>
+      <c r="B144" t="n">
+        <v>143</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Astralis Talent</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="n">
+        <v>143</v>
+      </c>
+      <c r="B145" t="n">
+        <v>144</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>BIG Academy</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="n">
+        <v>144</v>
+      </c>
+      <c r="B146" t="n">
+        <v>145</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>ENCE Academy</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="n">
+        <v>145</v>
+      </c>
+      <c r="B147" t="n">
+        <v>146</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>MOUZ NXT</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="n">
+        <v>146</v>
+      </c>
+      <c r="B148" t="n">
+        <v>147</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>B8</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="n">
+        <v>147</v>
+      </c>
+      <c r="B149" t="n">
+        <v>148</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>QMISTRY</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="n">
+        <v>148</v>
+      </c>
+      <c r="B150" t="n">
+        <v>149</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Wildcard Academy</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="n">
+        <v>149</v>
+      </c>
+      <c r="B151" t="n">
+        <v>150</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Tsunami</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="n">
+        <v>150</v>
+      </c>
+      <c r="B152" t="n">
+        <v>151</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>NOVAQ</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="n">
+        <v>151</v>
+      </c>
+      <c r="B153" t="n">
+        <v>152</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>HAVU</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="n">
+        <v>152</v>
+      </c>
+      <c r="B154" t="n">
+        <v>153</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>MANA</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="n">
+        <v>153</v>
+      </c>
+      <c r="B155" t="n">
+        <v>154</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>MIBR Academy</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="n">
+        <v>154</v>
+      </c>
+      <c r="B156" t="n">
+        <v>155</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>AMKAL</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="n">
+        <v>155</v>
+      </c>
+      <c r="B157" t="n">
+        <v>156</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Hesta</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="n">
+        <v>156</v>
+      </c>
+      <c r="B158" t="n">
+        <v>157</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>kONO</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="n">
+        <v>157</v>
+      </c>
+      <c r="B159" t="n">
+        <v>158</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>SKYFURY</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="n">
+        <v>158</v>
+      </c>
+      <c r="B160" t="n">
+        <v>159</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>GhoulsW</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="n">
+        <v>159</v>
+      </c>
+      <c r="B161" t="n">
+        <v>160</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>paiN Academy</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="n">
+        <v>160</v>
+      </c>
+      <c r="B162" t="n">
+        <v>161</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Nordix</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="n">
+        <v>161</v>
+      </c>
+      <c r="B163" t="n">
+        <v>162</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Aether</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="B164" t="n">
+        <v>163</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>GATERON</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="n">
+        <v>163</v>
+      </c>
+      <c r="B165" t="n">
+        <v>164</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Shika</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
         <v>0</v>
       </c>
-      <c r="F24" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" t="n">
-        <v>22</v>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E165" t="n">
+        <v>0</v>
+      </c>
+      <c r="F165" t="n">
+        <v>0</v>
+      </c>
+      <c r="G165" t="n">
+        <v>0</v>
+      </c>
+      <c r="H165" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -3408,20 +3408,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E79" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" t="n">
+        <v>-5</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -3783,25 +3777,19 @@
           <t>MenaceGG</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D89" t="n">
+        <v>1</v>
+      </c>
+      <c r="E89" t="n">
+        <v>1</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G89" t="n">
+        <v>8</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -6671,20 +6659,30 @@
           <t>Shika</t>
         </is>
       </c>
-      <c r="D165" t="n">
-        <v>0</v>
-      </c>
-      <c r="E165" t="n">
-        <v>0</v>
-      </c>
-      <c r="F165" t="n">
-        <v>0</v>
-      </c>
-      <c r="G165" t="n">
-        <v>0</v>
-      </c>
-      <c r="H165" t="n">
-        <v>0</v>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -1812,20 +1812,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-5</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -3408,14 +3402,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E79" t="n">
-        <v>0</v>
-      </c>
-      <c r="F79" t="n">
-        <v>1</v>
-      </c>
-      <c r="G79" t="n">
-        <v>-5</v>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -3777,19 +3777,25 @@
           <t>MenaceGG</t>
         </is>
       </c>
-      <c r="D89" t="n">
-        <v>1</v>
-      </c>
-      <c r="E89" t="n">
-        <v>1</v>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G89" t="n">
-        <v>8</v>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -4569,25 +4575,19 @@
           <t>hoorai</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D110" t="n">
+        <v>1</v>
+      </c>
+      <c r="E110" t="n">
+        <v>1</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G110" t="n">
+        <v>8</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -1275,25 +1275,19 @@
           <t>Entropiq</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G23" t="n">
+        <v>8</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1812,14 +1806,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E37" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" t="n">
-        <v>1</v>
-      </c>
-      <c r="G37" t="n">
-        <v>-5</v>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -4314,20 +4314,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E103" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" t="n">
+        <v>1</v>
+      </c>
+      <c r="G103" t="n">
+        <v>-5</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
@@ -4575,19 +4569,25 @@
           <t>hoorai</t>
         </is>
       </c>
-      <c r="D110" t="n">
-        <v>1</v>
-      </c>
-      <c r="E110" t="n">
-        <v>1</v>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G110" t="n">
-        <v>8</v>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -1275,19 +1275,25 @@
           <t>Entropiq</t>
         </is>
       </c>
-      <c r="D23" t="n">
-        <v>1</v>
-      </c>
-      <c r="E23" t="n">
-        <v>1</v>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>8</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -4314,14 +4320,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E103" t="n">
-        <v>0</v>
-      </c>
-      <c r="F103" t="n">
-        <v>1</v>
-      </c>
-      <c r="G103" t="n">
-        <v>-5</v>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -897,22 +897,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1275,19 +1275,25 @@
           <t>Entropiq</t>
         </is>
       </c>
-      <c r="D23" t="n">
-        <v>1</v>
-      </c>
-      <c r="E23" t="n">
-        <v>1</v>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>8</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -2257,25 +2263,19 @@
           <t>M80</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="D49" t="n">
+        <v>3</v>
+      </c>
+      <c r="E49" t="n">
+        <v>3</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="G49" t="n">
+        <v>27</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -2411,12 +2411,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>27</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3865,12 +3865,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -4288,7 +4288,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -4314,14 +4314,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E103" t="n">
-        <v>0</v>
-      </c>
-      <c r="F103" t="n">
-        <v>1</v>
-      </c>
-      <c r="G103" t="n">
-        <v>-5</v>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
@@ -4384,20 +4390,14 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="E105" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" t="n">
+        <v>2</v>
+      </c>
+      <c r="G105" t="n">
+        <v>-2</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
@@ -4533,22 +4533,22 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -4652,17 +4652,17 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -895,25 +895,17 @@
           <t>Legacy</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="D13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>4</v>
+      </c>
+      <c r="G13" t="n">
+        <v>5</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1657,22 +1649,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2263,19 +2255,25 @@
           <t>M80</t>
         </is>
       </c>
-      <c r="D49" t="n">
-        <v>3</v>
-      </c>
-      <c r="E49" t="n">
-        <v>3</v>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G49" t="n">
-        <v>27</v>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -4349,22 +4347,22 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -4390,14 +4388,20 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E105" t="n">
-        <v>0</v>
-      </c>
-      <c r="F105" t="n">
-        <v>2</v>
-      </c>
-      <c r="G105" t="n">
-        <v>-2</v>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
@@ -4645,25 +4649,17 @@
           <t>Verdant</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>-2</t>
-        </is>
+      <c r="D112" t="n">
+        <v>3</v>
+      </c>
+      <c r="E112" t="n">
+        <v>2</v>
+      </c>
+      <c r="F112" t="n">
+        <v>3</v>
+      </c>
+      <c r="G112" t="n">
+        <v>10</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -895,17 +895,25 @@
           <t>Legacy</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>3</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>4</v>
-      </c>
-      <c r="G13" t="n">
-        <v>5</v>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1649,12 +1657,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1664,7 +1672,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>41</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2262,17 +2270,17 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>17</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2412,20 +2420,14 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" t="n">
+        <v>2</v>
+      </c>
+      <c r="G53" t="n">
+        <v>17</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -4347,7 +4349,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -4357,12 +4359,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -4385,22 +4387,22 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -4535,25 +4537,19 @@
           <t>Titan</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="D109" t="n">
+        <v>5</v>
+      </c>
+      <c r="E109" t="n">
+        <v>4</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+      <c r="G109" t="n">
+        <v>41</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -4649,17 +4645,25 @@
           <t>Verdant</t>
         </is>
       </c>
-      <c r="D112" t="n">
-        <v>3</v>
-      </c>
-      <c r="E112" t="n">
-        <v>2</v>
-      </c>
-      <c r="F112" t="n">
-        <v>3</v>
-      </c>
-      <c r="G112" t="n">
-        <v>10</v>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -2268,20 +2268,14 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" t="n">
+        <v>4</v>
+      </c>
+      <c r="G49" t="n">
+        <v>7</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -2415,19 +2409,19 @@
           <t>RED Canids</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="D53" t="n">
+        <v>5</v>
       </c>
       <c r="E53" t="n">
-        <v>0</v>
-      </c>
-      <c r="F53" t="n">
         <v>2</v>
       </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="G53" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -4390,20 +4384,14 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="E105" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" t="n">
+        <v>5</v>
+      </c>
+      <c r="G105" t="n">
+        <v>-1</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
@@ -4537,19 +4525,25 @@
           <t>Titan</t>
         </is>
       </c>
-      <c r="D109" t="n">
-        <v>5</v>
-      </c>
-      <c r="E109" t="n">
-        <v>4</v>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G109" t="n">
-        <v>41</v>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -4645,25 +4639,19 @@
           <t>Verdant</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr">
+      <c r="D112" t="n">
+        <v>5</v>
+      </c>
+      <c r="E112" t="n">
+        <v>4</v>
+      </c>
+      <c r="F112" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="G112" t="n">
+        <v>31</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -1657,12 +1657,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>66</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2268,14 +2268,20 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E49" t="n">
-        <v>0</v>
-      </c>
-      <c r="F49" t="n">
-        <v>4</v>
-      </c>
-      <c r="G49" t="n">
-        <v>7</v>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -2409,19 +2415,19 @@
           <t>RED Canids</t>
         </is>
       </c>
-      <c r="D53" t="n">
-        <v>5</v>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="E53" t="n">
-        <v>2</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="F53" t="n">
+        <v>4</v>
       </c>
       <c r="G53" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -4384,14 +4390,20 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E105" t="n">
-        <v>0</v>
-      </c>
-      <c r="F105" t="n">
-        <v>5</v>
-      </c>
-      <c r="G105" t="n">
-        <v>-1</v>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
@@ -4532,17 +4544,17 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>31</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -4640,10 +4652,10 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E112" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -4651,7 +4663,7 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -2268,14 +2268,20 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E49" t="n">
-        <v>0</v>
-      </c>
-      <c r="F49" t="n">
-        <v>4</v>
-      </c>
-      <c r="G49" t="n">
-        <v>7</v>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -2409,19 +2415,25 @@
           <t>RED Canids</t>
         </is>
       </c>
-      <c r="D53" t="n">
-        <v>5</v>
-      </c>
-      <c r="E53" t="n">
-        <v>2</v>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G53" t="n">
-        <v>34</v>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -4384,14 +4396,20 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E105" t="n">
-        <v>0</v>
-      </c>
-      <c r="F105" t="n">
-        <v>5</v>
-      </c>
-      <c r="G105" t="n">
-        <v>-1</v>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
@@ -4639,19 +4657,25 @@
           <t>Verdant</t>
         </is>
       </c>
-      <c r="D112" t="n">
-        <v>5</v>
-      </c>
-      <c r="E112" t="n">
-        <v>4</v>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G112" t="n">
-        <v>31</v>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
@@ -6652,10 +6676,8 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E165" t="n">
+        <v>0</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -553,25 +553,17 @@
           <t>Liquid</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="D4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>20</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -2377,25 +2369,17 @@
           <t>ECSTATIC</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="D52" t="n">
+        <v>2</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="n">
+        <v>2</v>
+      </c>
+      <c r="G52" t="n">
+        <v>6</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -2420,14 +2404,20 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E53" t="n">
-        <v>0</v>
-      </c>
-      <c r="F53" t="n">
-        <v>4</v>
-      </c>
-      <c r="G53" t="n">
-        <v>24</v>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -2523,25 +2513,17 @@
           <t>Elevate</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="D56" t="n">
+        <v>3</v>
+      </c>
+      <c r="E56" t="n">
+        <v>1</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" t="n">
+        <v>20</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -4651,19 +4633,25 @@
           <t>Verdant</t>
         </is>
       </c>
-      <c r="D112" t="n">
-        <v>7</v>
-      </c>
-      <c r="E112" t="n">
-        <v>6</v>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G112" t="n">
-        <v>56</v>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -553,17 +553,25 @@
           <t>Liquid</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="n">
-        <v>20</v>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -930,20 +938,14 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-2</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -2369,17 +2371,25 @@
           <t>ECSTATIC</t>
         </is>
       </c>
-      <c r="D52" t="n">
-        <v>2</v>
-      </c>
-      <c r="E52" t="n">
-        <v>0</v>
-      </c>
-      <c r="F52" t="n">
-        <v>2</v>
-      </c>
-      <c r="G52" t="n">
-        <v>6</v>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -2513,17 +2523,25 @@
           <t>Elevate</t>
         </is>
       </c>
-      <c r="D56" t="n">
-        <v>3</v>
-      </c>
-      <c r="E56" t="n">
-        <v>1</v>
-      </c>
-      <c r="F56" t="n">
-        <v>1</v>
-      </c>
-      <c r="G56" t="n">
-        <v>20</v>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -2657,25 +2675,17 @@
           <t>Orbit</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="D60" t="n">
+        <v>2</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" t="n">
+        <v>2</v>
+      </c>
+      <c r="G60" t="n">
+        <v>7</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -2999,25 +3009,19 @@
           <t>Bounty Hunters</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="D69" t="n">
+        <v>3</v>
+      </c>
+      <c r="E69" t="n">
+        <v>3</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="G69" t="n">
+        <v>27</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -553,25 +553,17 @@
           <t>Liquid</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+      <c r="D4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" t="n">
+        <v>33</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -938,14 +930,20 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>2</v>
-      </c>
-      <c r="G14" t="n">
-        <v>-2</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1537,22 +1535,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2523,25 +2521,17 @@
           <t>Elevate</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+      <c r="D56" t="n">
+        <v>4</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" t="n">
+        <v>3</v>
+      </c>
+      <c r="G56" t="n">
+        <v>18</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -2675,17 +2665,25 @@
           <t>Orbit</t>
         </is>
       </c>
-      <c r="D60" t="n">
-        <v>2</v>
-      </c>
-      <c r="E60" t="n">
-        <v>0</v>
-      </c>
-      <c r="F60" t="n">
-        <v>2</v>
-      </c>
-      <c r="G60" t="n">
-        <v>7</v>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -3009,19 +3007,25 @@
           <t>Bounty Hunters</t>
         </is>
       </c>
-      <c r="D69" t="n">
-        <v>3</v>
-      </c>
-      <c r="E69" t="n">
-        <v>3</v>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G69" t="n">
-        <v>27</v>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -4601,22 +4605,22 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -553,17 +553,25 @@
           <t>Liquid</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>5</v>
-      </c>
-      <c r="E4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G4" t="n">
-        <v>33</v>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -2374,20 +2382,14 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="n">
+        <v>4</v>
+      </c>
+      <c r="G52" t="n">
+        <v>-4</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -2521,17 +2523,25 @@
           <t>Elevate</t>
         </is>
       </c>
-      <c r="D56" t="n">
-        <v>4</v>
-      </c>
-      <c r="E56" t="n">
-        <v>0</v>
-      </c>
-      <c r="F56" t="n">
-        <v>3</v>
-      </c>
-      <c r="G56" t="n">
-        <v>18</v>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -2665,25 +2675,19 @@
           <t>Orbit</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D60" t="n">
+        <v>4</v>
+      </c>
+      <c r="E60" t="n">
+        <v>2</v>
+      </c>
+      <c r="F60" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="G60" t="n">
+        <v>24</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -3007,25 +3011,19 @@
           <t>Bounty Hunters</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="D69" t="n">
+        <v>5</v>
+      </c>
+      <c r="E69" t="n">
+        <v>5</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+      <c r="G69" t="n">
+        <v>50</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -4608,20 +4606,14 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+      <c r="E111" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" t="n">
+        <v>3</v>
+      </c>
+      <c r="G111" t="n">
+        <v>10</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -933,25 +933,17 @@
           <t>MIBR</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>-2</t>
-        </is>
+      <c r="D14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G14" t="n">
+        <v>9</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1541,25 +1533,17 @@
           <t>SK</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="D30" t="n">
+        <v>3</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>4</v>
+      </c>
+      <c r="G30" t="n">
+        <v>5</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -2382,14 +2366,20 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E52" t="n">
-        <v>0</v>
-      </c>
-      <c r="F52" t="n">
-        <v>4</v>
-      </c>
-      <c r="G52" t="n">
-        <v>-4</v>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-4</t>
+        </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -2676,18 +2666,18 @@
         </is>
       </c>
       <c r="D60" t="n">
+        <v>6</v>
+      </c>
+      <c r="E60" t="n">
         <v>4</v>
       </c>
-      <c r="E60" t="n">
-        <v>2</v>
-      </c>
       <c r="F60" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -3011,19 +3001,25 @@
           <t>Bounty Hunters</t>
         </is>
       </c>
-      <c r="D69" t="n">
-        <v>5</v>
-      </c>
-      <c r="E69" t="n">
-        <v>5</v>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G69" t="n">
-        <v>50</v>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -4610,10 +4606,10 @@
         <v>0</v>
       </c>
       <c r="F111" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G111" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -934,16 +934,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1533,17 +1533,25 @@
           <t>SK</t>
         </is>
       </c>
-      <c r="D30" t="n">
-        <v>3</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" t="n">
-        <v>4</v>
-      </c>
-      <c r="G30" t="n">
-        <v>5</v>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -2513,25 +2521,17 @@
           <t>Elevate</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="D56" t="n">
+        <v>6</v>
+      </c>
+      <c r="E56" t="n">
+        <v>2</v>
+      </c>
+      <c r="F56" t="n">
+        <v>4</v>
+      </c>
+      <c r="G56" t="n">
+        <v>30</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -2665,19 +2665,25 @@
           <t>Orbit</t>
         </is>
       </c>
-      <c r="D60" t="n">
-        <v>6</v>
-      </c>
-      <c r="E60" t="n">
-        <v>4</v>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G60" t="n">
-        <v>45</v>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -4602,14 +4608,20 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E111" t="n">
-        <v>0</v>
-      </c>
-      <c r="F111" t="n">
-        <v>5</v>
-      </c>
-      <c r="G111" t="n">
-        <v>0</v>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -477,20 +477,30 @@
           <t>Vitality</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -505,20 +515,30 @@
           <t>Astralis</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -533,20 +553,30 @@
           <t>Liquid</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -561,20 +591,30 @@
           <t>Mythic</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -589,20 +629,30 @@
           <t>Heroic</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -617,20 +667,30 @@
           <t>Fnatic</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -645,20 +705,30 @@
           <t>FaZe</t>
         </is>
       </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -673,20 +743,30 @@
           <t>BIG</t>
         </is>
       </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -701,20 +781,30 @@
           <t>ENCE</t>
         </is>
       </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -729,20 +819,30 @@
           <t>Ninjas in Pyjamas</t>
         </is>
       </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -757,20 +857,30 @@
           <t>FURIA</t>
         </is>
       </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="n">
-        <v>-5</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -785,20 +895,30 @@
           <t>Legacy</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>3</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>4</v>
-      </c>
-      <c r="G13" t="n">
-        <v>5</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -814,19 +934,21 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -841,20 +963,30 @@
           <t>Natus Vincere</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -869,20 +1001,30 @@
           <t>MOUZ</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -897,20 +1039,30 @@
           <t>G2</t>
         </is>
       </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -925,20 +1077,30 @@
           <t>OG</t>
         </is>
       </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -953,20 +1115,30 @@
           <t>paiN</t>
         </is>
       </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" t="n">
-        <v>-5</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -981,20 +1153,30 @@
           <t>Imperial</t>
         </is>
       </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" t="n">
-        <v>-5</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -1009,20 +1191,30 @@
           <t>Virtus.pro</t>
         </is>
       </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -1037,20 +1229,30 @@
           <t>Spirit</t>
         </is>
       </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -1065,20 +1267,30 @@
           <t>Entropiq</t>
         </is>
       </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -1093,20 +1305,30 @@
           <t>Copenhagen Flames</t>
         </is>
       </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -1121,20 +1343,30 @@
           <t>Envy</t>
         </is>
       </c>
-      <c r="D25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -1149,20 +1381,30 @@
           <t>iBUYPOWER</t>
         </is>
       </c>
-      <c r="D26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -1177,20 +1419,30 @@
           <t>Evil Geniuses</t>
         </is>
       </c>
-      <c r="D27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0</v>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -1205,20 +1457,30 @@
           <t>Dignitas</t>
         </is>
       </c>
-      <c r="D28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="29">
@@ -1233,20 +1495,30 @@
           <t>Cloud9</t>
         </is>
       </c>
-      <c r="D29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -1262,19 +1534,21 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="31">
@@ -1289,20 +1563,24 @@
           <t>Luminosity</t>
         </is>
       </c>
-      <c r="D31" t="n">
-        <v>0</v>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
+        <v>-5</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -1317,20 +1595,30 @@
           <t>Vexed</t>
         </is>
       </c>
-      <c r="D32" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G32" t="n">
-        <v>-5</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0</v>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="33">
@@ -1345,20 +1633,30 @@
           <t>Iluminar</t>
         </is>
       </c>
-      <c r="D33" t="n">
-        <v>7</v>
-      </c>
-      <c r="E33" t="n">
-        <v>6</v>
-      </c>
-      <c r="F33" t="n">
-        <v>1</v>
-      </c>
-      <c r="G33" t="n">
-        <v>66</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="34">
@@ -1373,20 +1671,30 @@
           <t>Falcons</t>
         </is>
       </c>
-      <c r="D34" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0</v>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="35">
@@ -1401,20 +1709,30 @@
           <t>Sangal</t>
         </is>
       </c>
-      <c r="D35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0</v>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="36">
@@ -1429,20 +1747,30 @@
           <t>ShindeN</t>
         </is>
       </c>
-      <c r="D36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0</v>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="37">
@@ -1457,20 +1785,30 @@
           <t>SAW</t>
         </is>
       </c>
-      <c r="D37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0</v>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="38">
@@ -1485,20 +1823,30 @@
           <t>Nexus</t>
         </is>
       </c>
-      <c r="D38" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0</v>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="39">
@@ -1513,20 +1861,30 @@
           <t>9Pandas</t>
         </is>
       </c>
-      <c r="D39" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0</v>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="40">
@@ -1541,20 +1899,30 @@
           <t>Passion UA</t>
         </is>
       </c>
-      <c r="D40" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0</v>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="41">
@@ -1569,20 +1937,30 @@
           <t>ARCRED</t>
         </is>
       </c>
-      <c r="D41" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0</v>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="42">
@@ -1597,20 +1975,30 @@
           <t>Qiang</t>
         </is>
       </c>
-      <c r="D42" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" t="n">
-        <v>0</v>
-      </c>
-      <c r="F42" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0</v>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="43">
@@ -1625,20 +2013,30 @@
           <t>Permitta</t>
         </is>
       </c>
-      <c r="D43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="44">
@@ -1653,20 +2051,30 @@
           <t>Rebels</t>
         </is>
       </c>
-      <c r="D44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0</v>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="45">
@@ -1681,20 +2089,30 @@
           <t>Eternal Fire</t>
         </is>
       </c>
-      <c r="D45" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" t="n">
-        <v>0</v>
-      </c>
-      <c r="F45" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0</v>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="46">
@@ -1709,20 +2127,30 @@
           <t>3DMAX</t>
         </is>
       </c>
-      <c r="D46" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0</v>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="47">
@@ -1737,20 +2165,30 @@
           <t>Aurora</t>
         </is>
       </c>
-      <c r="D47" t="n">
-        <v>0</v>
-      </c>
-      <c r="E47" t="n">
-        <v>0</v>
-      </c>
-      <c r="F47" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0</v>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="48">
@@ -1765,20 +2203,24 @@
           <t>Complexity</t>
         </is>
       </c>
-      <c r="D48" t="n">
-        <v>0</v>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="E48" t="n">
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0</v>
+        <v>-5</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="49">
@@ -1794,19 +2236,21 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E49" t="n">
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="50">
@@ -1821,20 +2265,30 @@
           <t>Wildcard</t>
         </is>
       </c>
-      <c r="D50" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" t="n">
-        <v>0</v>
-      </c>
-      <c r="F50" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0</v>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="51">
@@ -1849,20 +2303,30 @@
           <t>BESTIA</t>
         </is>
       </c>
-      <c r="D51" t="n">
-        <v>0</v>
-      </c>
-      <c r="E51" t="n">
-        <v>0</v>
-      </c>
-      <c r="F51" t="n">
-        <v>0</v>
-      </c>
-      <c r="G51" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0</v>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="52">
@@ -1878,19 +2342,21 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E52" t="n">
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0</v>
+        <v>-4</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="53">
@@ -1906,19 +2372,21 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E53" t="n">
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0</v>
+        <v>24</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="54">
@@ -1933,20 +2401,30 @@
           <t>Case</t>
         </is>
       </c>
-      <c r="D54" t="n">
-        <v>0</v>
-      </c>
-      <c r="E54" t="n">
-        <v>0</v>
-      </c>
-      <c r="F54" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0</v>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="55">
@@ -1961,20 +2439,30 @@
           <t>KRU</t>
         </is>
       </c>
-      <c r="D55" t="n">
-        <v>0</v>
-      </c>
-      <c r="E55" t="n">
-        <v>0</v>
-      </c>
-      <c r="F55" t="n">
-        <v>1</v>
-      </c>
-      <c r="G55" t="n">
-        <v>-5</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0</v>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="56">
@@ -1989,20 +2477,30 @@
           <t>Elevate</t>
         </is>
       </c>
-      <c r="D56" t="n">
-        <v>6</v>
-      </c>
-      <c r="E56" t="n">
-        <v>2</v>
-      </c>
-      <c r="F56" t="n">
-        <v>4</v>
-      </c>
-      <c r="G56" t="n">
-        <v>30</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0</v>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="57">
@@ -2017,20 +2515,30 @@
           <t>GamerLegion</t>
         </is>
       </c>
-      <c r="D57" t="n">
-        <v>0</v>
-      </c>
-      <c r="E57" t="n">
-        <v>0</v>
-      </c>
-      <c r="F57" t="n">
-        <v>0</v>
-      </c>
-      <c r="G57" t="n">
-        <v>0</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0</v>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="58">
@@ -2045,20 +2553,30 @@
           <t>Underground</t>
         </is>
       </c>
-      <c r="D58" t="n">
-        <v>0</v>
-      </c>
-      <c r="E58" t="n">
-        <v>0</v>
-      </c>
-      <c r="F58" t="n">
-        <v>0</v>
-      </c>
-      <c r="G58" t="n">
-        <v>0</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0</v>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="59">
@@ -2073,20 +2591,30 @@
           <t>9z</t>
         </is>
       </c>
-      <c r="D59" t="n">
-        <v>0</v>
-      </c>
-      <c r="E59" t="n">
-        <v>0</v>
-      </c>
-      <c r="F59" t="n">
-        <v>1</v>
-      </c>
-      <c r="G59" t="n">
-        <v>-5</v>
-      </c>
-      <c r="H59" t="n">
-        <v>0</v>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="60">
@@ -2101,20 +2629,30 @@
           <t>Orbit</t>
         </is>
       </c>
-      <c r="D60" t="n">
-        <v>6</v>
-      </c>
-      <c r="E60" t="n">
-        <v>4</v>
-      </c>
-      <c r="F60" t="n">
-        <v>2</v>
-      </c>
-      <c r="G60" t="n">
-        <v>45</v>
-      </c>
-      <c r="H60" t="n">
-        <v>0</v>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="61">
@@ -2129,20 +2667,30 @@
           <t>Limitless</t>
         </is>
       </c>
-      <c r="D61" t="n">
-        <v>0</v>
-      </c>
-      <c r="E61" t="n">
-        <v>0</v>
-      </c>
-      <c r="F61" t="n">
-        <v>0</v>
-      </c>
-      <c r="G61" t="n">
-        <v>0</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0</v>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="62">
@@ -2157,20 +2705,30 @@
           <t>Homyno</t>
         </is>
       </c>
-      <c r="D62" t="n">
-        <v>0</v>
-      </c>
-      <c r="E62" t="n">
-        <v>0</v>
-      </c>
-      <c r="F62" t="n">
-        <v>0</v>
-      </c>
-      <c r="G62" t="n">
-        <v>0</v>
-      </c>
-      <c r="H62" t="n">
-        <v>0</v>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="63">
@@ -2185,20 +2743,30 @@
           <t>Take Flyte</t>
         </is>
       </c>
-      <c r="D63" t="n">
-        <v>0</v>
-      </c>
-      <c r="E63" t="n">
-        <v>0</v>
-      </c>
-      <c r="F63" t="n">
-        <v>0</v>
-      </c>
-      <c r="G63" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" t="n">
-        <v>0</v>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="64">
@@ -2213,20 +2781,30 @@
           <t>The Huns</t>
         </is>
       </c>
-      <c r="D64" t="n">
-        <v>0</v>
-      </c>
-      <c r="E64" t="n">
-        <v>0</v>
-      </c>
-      <c r="F64" t="n">
-        <v>1</v>
-      </c>
-      <c r="G64" t="n">
-        <v>-5</v>
-      </c>
-      <c r="H64" t="n">
-        <v>0</v>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="65">
@@ -2241,20 +2819,24 @@
           <t>Sharks</t>
         </is>
       </c>
-      <c r="D65" t="n">
-        <v>0</v>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="E65" t="n">
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
-      </c>
-      <c r="H65" t="n">
-        <v>0</v>
+        <v>-5</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="66">
@@ -2269,20 +2851,30 @@
           <t>ODDIK</t>
         </is>
       </c>
-      <c r="D66" t="n">
-        <v>0</v>
-      </c>
-      <c r="E66" t="n">
-        <v>0</v>
-      </c>
-      <c r="F66" t="n">
-        <v>0</v>
-      </c>
-      <c r="G66" t="n">
-        <v>0</v>
-      </c>
-      <c r="H66" t="n">
-        <v>0</v>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="67">
@@ -2297,20 +2889,30 @@
           <t>inSanitY</t>
         </is>
       </c>
-      <c r="D67" t="n">
-        <v>0</v>
-      </c>
-      <c r="E67" t="n">
-        <v>0</v>
-      </c>
-      <c r="F67" t="n">
-        <v>0</v>
-      </c>
-      <c r="G67" t="n">
-        <v>0</v>
-      </c>
-      <c r="H67" t="n">
-        <v>0</v>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="68">
@@ -2325,20 +2927,30 @@
           <t>Team Solid</t>
         </is>
       </c>
-      <c r="D68" t="n">
-        <v>0</v>
-      </c>
-      <c r="E68" t="n">
-        <v>0</v>
-      </c>
-      <c r="F68" t="n">
-        <v>0</v>
-      </c>
-      <c r="G68" t="n">
-        <v>0</v>
-      </c>
-      <c r="H68" t="n">
-        <v>0</v>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="69">
@@ -2353,20 +2965,30 @@
           <t>Bounty Hunters</t>
         </is>
       </c>
-      <c r="D69" t="n">
-        <v>0</v>
-      </c>
-      <c r="E69" t="n">
-        <v>0</v>
-      </c>
-      <c r="F69" t="n">
-        <v>0</v>
-      </c>
-      <c r="G69" t="n">
-        <v>0</v>
-      </c>
-      <c r="H69" t="n">
-        <v>0</v>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="70">
@@ -2381,20 +3003,30 @@
           <t>Galorys</t>
         </is>
       </c>
-      <c r="D70" t="n">
-        <v>0</v>
-      </c>
-      <c r="E70" t="n">
-        <v>0</v>
-      </c>
-      <c r="F70" t="n">
-        <v>0</v>
-      </c>
-      <c r="G70" t="n">
-        <v>0</v>
-      </c>
-      <c r="H70" t="n">
-        <v>0</v>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="71">
@@ -2409,20 +3041,30 @@
           <t>Spirit Academy</t>
         </is>
       </c>
-      <c r="D71" t="n">
-        <v>0</v>
-      </c>
-      <c r="E71" t="n">
-        <v>0</v>
-      </c>
-      <c r="F71" t="n">
-        <v>0</v>
-      </c>
-      <c r="G71" t="n">
-        <v>0</v>
-      </c>
-      <c r="H71" t="n">
-        <v>0</v>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="72">
@@ -2437,20 +3079,30 @@
           <t>Tricked</t>
         </is>
       </c>
-      <c r="D72" t="n">
-        <v>0</v>
-      </c>
-      <c r="E72" t="n">
-        <v>0</v>
-      </c>
-      <c r="F72" t="n">
-        <v>0</v>
-      </c>
-      <c r="G72" t="n">
-        <v>0</v>
-      </c>
-      <c r="H72" t="n">
-        <v>0</v>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="73">
@@ -2465,20 +3117,30 @@
           <t>The MongolZ</t>
         </is>
       </c>
-      <c r="D73" t="n">
-        <v>0</v>
-      </c>
-      <c r="E73" t="n">
-        <v>0</v>
-      </c>
-      <c r="F73" t="n">
-        <v>0</v>
-      </c>
-      <c r="G73" t="n">
-        <v>0</v>
-      </c>
-      <c r="H73" t="n">
-        <v>0</v>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="74">
@@ -2493,20 +3155,30 @@
           <t>FlyQuest</t>
         </is>
       </c>
-      <c r="D74" t="n">
-        <v>0</v>
-      </c>
-      <c r="E74" t="n">
-        <v>0</v>
-      </c>
-      <c r="F74" t="n">
-        <v>0</v>
-      </c>
-      <c r="G74" t="n">
-        <v>0</v>
-      </c>
-      <c r="H74" t="n">
-        <v>0</v>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="75">
@@ -2521,20 +3193,30 @@
           <t>PARIVISION</t>
         </is>
       </c>
-      <c r="D75" t="n">
-        <v>0</v>
-      </c>
-      <c r="E75" t="n">
-        <v>0</v>
-      </c>
-      <c r="F75" t="n">
-        <v>0</v>
-      </c>
-      <c r="G75" t="n">
-        <v>0</v>
-      </c>
-      <c r="H75" t="n">
-        <v>0</v>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="76">
@@ -2549,20 +3231,30 @@
           <t>Lynn Vision</t>
         </is>
       </c>
-      <c r="D76" t="n">
-        <v>0</v>
-      </c>
-      <c r="E76" t="n">
-        <v>0</v>
-      </c>
-      <c r="F76" t="n">
-        <v>0</v>
-      </c>
-      <c r="G76" t="n">
-        <v>0</v>
-      </c>
-      <c r="H76" t="n">
-        <v>0</v>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="77">
@@ -2577,20 +3269,30 @@
           <t>VP.Prodigy</t>
         </is>
       </c>
-      <c r="D77" t="n">
-        <v>0</v>
-      </c>
-      <c r="E77" t="n">
-        <v>0</v>
-      </c>
-      <c r="F77" t="n">
-        <v>0</v>
-      </c>
-      <c r="G77" t="n">
-        <v>0</v>
-      </c>
-      <c r="H77" t="n">
-        <v>0</v>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="78">
@@ -2605,20 +3307,30 @@
           <t>TALON</t>
         </is>
       </c>
-      <c r="D78" t="n">
-        <v>0</v>
-      </c>
-      <c r="E78" t="n">
-        <v>0</v>
-      </c>
-      <c r="F78" t="n">
-        <v>0</v>
-      </c>
-      <c r="G78" t="n">
-        <v>0</v>
-      </c>
-      <c r="H78" t="n">
-        <v>0</v>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="79">
@@ -2633,20 +3345,30 @@
           <t>Arcade</t>
         </is>
       </c>
-      <c r="D79" t="n">
-        <v>0</v>
-      </c>
-      <c r="E79" t="n">
-        <v>0</v>
-      </c>
-      <c r="F79" t="n">
-        <v>0</v>
-      </c>
-      <c r="G79" t="n">
-        <v>0</v>
-      </c>
-      <c r="H79" t="n">
-        <v>0</v>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="80">
@@ -2661,20 +3383,30 @@
           <t>NAVI Junior</t>
         </is>
       </c>
-      <c r="D80" t="n">
-        <v>0</v>
-      </c>
-      <c r="E80" t="n">
-        <v>0</v>
-      </c>
-      <c r="F80" t="n">
-        <v>0</v>
-      </c>
-      <c r="G80" t="n">
-        <v>0</v>
-      </c>
-      <c r="H80" t="n">
-        <v>0</v>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="81">
@@ -2689,20 +3421,30 @@
           <t>BC.Game</t>
         </is>
       </c>
-      <c r="D81" t="n">
-        <v>0</v>
-      </c>
-      <c r="E81" t="n">
-        <v>0</v>
-      </c>
-      <c r="F81" t="n">
-        <v>0</v>
-      </c>
-      <c r="G81" t="n">
-        <v>0</v>
-      </c>
-      <c r="H81" t="n">
-        <v>0</v>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="82">
@@ -2717,20 +3459,30 @@
           <t>Vantage</t>
         </is>
       </c>
-      <c r="D82" t="n">
-        <v>0</v>
-      </c>
-      <c r="E82" t="n">
-        <v>0</v>
-      </c>
-      <c r="F82" t="n">
-        <v>0</v>
-      </c>
-      <c r="G82" t="n">
-        <v>0</v>
-      </c>
-      <c r="H82" t="n">
-        <v>0</v>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="83">
@@ -2745,20 +3497,30 @@
           <t>TYLOO</t>
         </is>
       </c>
-      <c r="D83" t="n">
-        <v>0</v>
-      </c>
-      <c r="E83" t="n">
-        <v>0</v>
-      </c>
-      <c r="F83" t="n">
-        <v>0</v>
-      </c>
-      <c r="G83" t="n">
-        <v>0</v>
-      </c>
-      <c r="H83" t="n">
-        <v>0</v>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="84">
@@ -2773,20 +3535,30 @@
           <t>CatEvil</t>
         </is>
       </c>
-      <c r="D84" t="n">
-        <v>0</v>
-      </c>
-      <c r="E84" t="n">
-        <v>0</v>
-      </c>
-      <c r="F84" t="n">
-        <v>0</v>
-      </c>
-      <c r="G84" t="n">
-        <v>0</v>
-      </c>
-      <c r="H84" t="n">
-        <v>0</v>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="85">
@@ -2801,20 +3573,30 @@
           <t>Outsiders</t>
         </is>
       </c>
-      <c r="D85" t="n">
-        <v>0</v>
-      </c>
-      <c r="E85" t="n">
-        <v>0</v>
-      </c>
-      <c r="F85" t="n">
-        <v>0</v>
-      </c>
-      <c r="G85" t="n">
-        <v>0</v>
-      </c>
-      <c r="H85" t="n">
-        <v>0</v>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="86">
@@ -2829,20 +3611,30 @@
           <t>Chinggis Warrios</t>
         </is>
       </c>
-      <c r="D86" t="n">
-        <v>0</v>
-      </c>
-      <c r="E86" t="n">
-        <v>0</v>
-      </c>
-      <c r="F86" t="n">
-        <v>0</v>
-      </c>
-      <c r="G86" t="n">
-        <v>0</v>
-      </c>
-      <c r="H86" t="n">
-        <v>0</v>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="87">
@@ -2857,20 +3649,30 @@
           <t>ATOX</t>
         </is>
       </c>
-      <c r="D87" t="n">
-        <v>0</v>
-      </c>
-      <c r="E87" t="n">
-        <v>0</v>
-      </c>
-      <c r="F87" t="n">
-        <v>0</v>
-      </c>
-      <c r="G87" t="n">
-        <v>0</v>
-      </c>
-      <c r="H87" t="n">
-        <v>0</v>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="88">
@@ -2885,20 +3687,24 @@
           <t>IHC</t>
         </is>
       </c>
-      <c r="D88" t="n">
-        <v>0</v>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="E88" t="n">
         <v>0</v>
       </c>
       <c r="F88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
-      </c>
-      <c r="H88" t="n">
-        <v>0</v>
+        <v>-5</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="89">
@@ -2913,20 +3719,30 @@
           <t>MenaceGG</t>
         </is>
       </c>
-      <c r="D89" t="n">
-        <v>0</v>
-      </c>
-      <c r="E89" t="n">
-        <v>0</v>
-      </c>
-      <c r="F89" t="n">
-        <v>0</v>
-      </c>
-      <c r="G89" t="n">
-        <v>0</v>
-      </c>
-      <c r="H89" t="n">
-        <v>0</v>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="90">
@@ -2941,20 +3757,30 @@
           <t>The Dice</t>
         </is>
       </c>
-      <c r="D90" t="n">
-        <v>0</v>
-      </c>
-      <c r="E90" t="n">
-        <v>0</v>
-      </c>
-      <c r="F90" t="n">
-        <v>0</v>
-      </c>
-      <c r="G90" t="n">
-        <v>0</v>
-      </c>
-      <c r="H90" t="n">
-        <v>0</v>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="91">
@@ -2969,20 +3795,30 @@
           <t>ad hoc</t>
         </is>
       </c>
-      <c r="D91" t="n">
-        <v>0</v>
-      </c>
-      <c r="E91" t="n">
-        <v>0</v>
-      </c>
-      <c r="F91" t="n">
-        <v>0</v>
-      </c>
-      <c r="G91" t="n">
-        <v>0</v>
-      </c>
-      <c r="H91" t="n">
-        <v>0</v>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="92">
@@ -2997,20 +3833,30 @@
           <t>Aravt</t>
         </is>
       </c>
-      <c r="D92" t="n">
-        <v>0</v>
-      </c>
-      <c r="E92" t="n">
-        <v>0</v>
-      </c>
-      <c r="F92" t="n">
-        <v>0</v>
-      </c>
-      <c r="G92" t="n">
-        <v>0</v>
-      </c>
-      <c r="H92" t="n">
-        <v>0</v>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="93">
@@ -3025,20 +3871,30 @@
           <t>Gods Reign</t>
         </is>
       </c>
-      <c r="D93" t="n">
-        <v>0</v>
-      </c>
-      <c r="E93" t="n">
-        <v>0</v>
-      </c>
-      <c r="F93" t="n">
-        <v>0</v>
-      </c>
-      <c r="G93" t="n">
-        <v>0</v>
-      </c>
-      <c r="H93" t="n">
-        <v>0</v>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="94">
@@ -3053,20 +3909,30 @@
           <t>True Rippers</t>
         </is>
       </c>
-      <c r="D94" t="n">
-        <v>0</v>
-      </c>
-      <c r="E94" t="n">
-        <v>0</v>
-      </c>
-      <c r="F94" t="n">
-        <v>0</v>
-      </c>
-      <c r="G94" t="n">
-        <v>0</v>
-      </c>
-      <c r="H94" t="n">
-        <v>0</v>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="95">
@@ -3081,20 +3947,30 @@
           <t>Alliance</t>
         </is>
       </c>
-      <c r="D95" t="n">
-        <v>0</v>
-      </c>
-      <c r="E95" t="n">
-        <v>0</v>
-      </c>
-      <c r="F95" t="n">
-        <v>0</v>
-      </c>
-      <c r="G95" t="n">
-        <v>0</v>
-      </c>
-      <c r="H95" t="n">
-        <v>0</v>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="96">
@@ -3109,20 +3985,30 @@
           <t>Carnival</t>
         </is>
       </c>
-      <c r="D96" t="n">
-        <v>0</v>
-      </c>
-      <c r="E96" t="n">
-        <v>0</v>
-      </c>
-      <c r="F96" t="n">
-        <v>0</v>
-      </c>
-      <c r="G96" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" t="n">
-        <v>0</v>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="97">
@@ -3137,20 +4023,30 @@
           <t>Wings Up</t>
         </is>
       </c>
-      <c r="D97" t="n">
-        <v>0</v>
-      </c>
-      <c r="E97" t="n">
-        <v>0</v>
-      </c>
-      <c r="F97" t="n">
-        <v>0</v>
-      </c>
-      <c r="G97" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" t="n">
-        <v>0</v>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="98">
@@ -3165,20 +4061,30 @@
           <t>Nemiga</t>
         </is>
       </c>
-      <c r="D98" t="n">
-        <v>0</v>
-      </c>
-      <c r="E98" t="n">
-        <v>0</v>
-      </c>
-      <c r="F98" t="n">
-        <v>0</v>
-      </c>
-      <c r="G98" t="n">
-        <v>0</v>
-      </c>
-      <c r="H98" t="n">
-        <v>0</v>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="99">
@@ -3193,20 +4099,30 @@
           <t>Red Viperz</t>
         </is>
       </c>
-      <c r="D99" t="n">
-        <v>0</v>
-      </c>
-      <c r="E99" t="n">
-        <v>0</v>
-      </c>
-      <c r="F99" t="n">
-        <v>0</v>
-      </c>
-      <c r="G99" t="n">
-        <v>0</v>
-      </c>
-      <c r="H99" t="n">
-        <v>0</v>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="100">
@@ -3221,20 +4137,30 @@
           <t>Victores Sumus</t>
         </is>
       </c>
-      <c r="D100" t="n">
-        <v>0</v>
-      </c>
-      <c r="E100" t="n">
-        <v>0</v>
-      </c>
-      <c r="F100" t="n">
-        <v>0</v>
-      </c>
-      <c r="G100" t="n">
-        <v>0</v>
-      </c>
-      <c r="H100" t="n">
-        <v>0</v>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="101">
@@ -3249,20 +4175,30 @@
           <t>Onyx Ravens</t>
         </is>
       </c>
-      <c r="D101" t="n">
-        <v>0</v>
-      </c>
-      <c r="E101" t="n">
-        <v>0</v>
-      </c>
-      <c r="F101" t="n">
-        <v>0</v>
-      </c>
-      <c r="G101" t="n">
-        <v>0</v>
-      </c>
-      <c r="H101" t="n">
-        <v>0</v>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="102">
@@ -3277,20 +4213,30 @@
           <t>Skinvault</t>
         </is>
       </c>
-      <c r="D102" t="n">
-        <v>0</v>
-      </c>
-      <c r="E102" t="n">
-        <v>0</v>
-      </c>
-      <c r="F102" t="n">
-        <v>0</v>
-      </c>
-      <c r="G102" t="n">
-        <v>0</v>
-      </c>
-      <c r="H102" t="n">
-        <v>0</v>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="103">
@@ -3305,20 +4251,30 @@
           <t>Reason Gaming</t>
         </is>
       </c>
-      <c r="D103" t="n">
-        <v>0</v>
-      </c>
-      <c r="E103" t="n">
-        <v>0</v>
-      </c>
-      <c r="F103" t="n">
-        <v>0</v>
-      </c>
-      <c r="G103" t="n">
-        <v>0</v>
-      </c>
-      <c r="H103" t="n">
-        <v>0</v>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="104">
@@ -3333,20 +4289,30 @@
           <t>Bad News Eagles</t>
         </is>
       </c>
-      <c r="D104" t="n">
-        <v>3</v>
-      </c>
-      <c r="E104" t="n">
-        <v>0</v>
-      </c>
-      <c r="F104" t="n">
-        <v>4</v>
-      </c>
-      <c r="G104" t="n">
-        <v>5</v>
-      </c>
-      <c r="H104" t="n">
-        <v>0</v>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="105">
@@ -3361,20 +4327,30 @@
           <t>Wizards</t>
         </is>
       </c>
-      <c r="D105" t="n">
-        <v>3</v>
-      </c>
-      <c r="E105" t="n">
-        <v>0</v>
-      </c>
-      <c r="F105" t="n">
-        <v>5</v>
-      </c>
-      <c r="G105" t="n">
-        <v>-1</v>
-      </c>
-      <c r="H105" t="n">
-        <v>0</v>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="106">
@@ -3389,20 +4365,24 @@
           <t>devils.one</t>
         </is>
       </c>
-      <c r="D106" t="n">
-        <v>0</v>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="E106" t="n">
         <v>0</v>
       </c>
       <c r="F106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G106" t="n">
-        <v>0</v>
-      </c>
-      <c r="H106" t="n">
-        <v>0</v>
+        <v>-5</v>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="107">
@@ -3417,20 +4397,30 @@
           <t>LCDC</t>
         </is>
       </c>
-      <c r="D107" t="n">
-        <v>0</v>
-      </c>
-      <c r="E107" t="n">
-        <v>0</v>
-      </c>
-      <c r="F107" t="n">
-        <v>0</v>
-      </c>
-      <c r="G107" t="n">
-        <v>0</v>
-      </c>
-      <c r="H107" t="n">
-        <v>0</v>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="108">
@@ -3445,20 +4435,30 @@
           <t>Enemy</t>
         </is>
       </c>
-      <c r="D108" t="n">
-        <v>0</v>
-      </c>
-      <c r="E108" t="n">
-        <v>0</v>
-      </c>
-      <c r="F108" t="n">
-        <v>0</v>
-      </c>
-      <c r="G108" t="n">
-        <v>0</v>
-      </c>
-      <c r="H108" t="n">
-        <v>0</v>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="109">
@@ -3473,20 +4473,30 @@
           <t>Titan</t>
         </is>
       </c>
-      <c r="D109" t="n">
-        <v>0</v>
-      </c>
-      <c r="E109" t="n">
-        <v>0</v>
-      </c>
-      <c r="F109" t="n">
-        <v>0</v>
-      </c>
-      <c r="G109" t="n">
-        <v>0</v>
-      </c>
-      <c r="H109" t="n">
-        <v>0</v>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="110">
@@ -3501,20 +4511,30 @@
           <t>hoorai</t>
         </is>
       </c>
-      <c r="D110" t="n">
-        <v>0</v>
-      </c>
-      <c r="E110" t="n">
-        <v>0</v>
-      </c>
-      <c r="F110" t="n">
-        <v>0</v>
-      </c>
-      <c r="G110" t="n">
-        <v>0</v>
-      </c>
-      <c r="H110" t="n">
-        <v>0</v>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="111">
@@ -3530,19 +4550,21 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E111" t="n">
         <v>0</v>
       </c>
       <c r="F111" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
       </c>
-      <c r="H111" t="n">
-        <v>0</v>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="112">
@@ -3557,20 +4579,30 @@
           <t>Verdant</t>
         </is>
       </c>
-      <c r="D112" t="n">
-        <v>7</v>
-      </c>
-      <c r="E112" t="n">
-        <v>6</v>
-      </c>
-      <c r="F112" t="n">
-        <v>3</v>
-      </c>
-      <c r="G112" t="n">
-        <v>56</v>
-      </c>
-      <c r="H112" t="n">
-        <v>0</v>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="113">
@@ -3585,20 +4617,24 @@
           <t>Kappa Bar</t>
         </is>
       </c>
-      <c r="D113" t="n">
-        <v>0</v>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="E113" t="n">
         <v>0</v>
       </c>
       <c r="F113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G113" t="n">
-        <v>0</v>
-      </c>
-      <c r="H113" t="n">
-        <v>0</v>
+        <v>-5</v>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="114">
@@ -3613,20 +4649,30 @@
           <t>MAD Lions</t>
         </is>
       </c>
-      <c r="D114" t="n">
-        <v>0</v>
-      </c>
-      <c r="E114" t="n">
-        <v>0</v>
-      </c>
-      <c r="F114" t="n">
-        <v>0</v>
-      </c>
-      <c r="G114" t="n">
-        <v>0</v>
-      </c>
-      <c r="H114" t="n">
-        <v>0</v>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="115">
@@ -3641,20 +4687,30 @@
           <t>Copenhagen Wolves</t>
         </is>
       </c>
-      <c r="D115" t="n">
-        <v>0</v>
-      </c>
-      <c r="E115" t="n">
-        <v>0</v>
-      </c>
-      <c r="F115" t="n">
-        <v>0</v>
-      </c>
-      <c r="G115" t="n">
-        <v>0</v>
-      </c>
-      <c r="H115" t="n">
-        <v>0</v>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="116">
@@ -3669,20 +4725,30 @@
           <t>Astana Dragons</t>
         </is>
       </c>
-      <c r="D116" t="n">
-        <v>0</v>
-      </c>
-      <c r="E116" t="n">
-        <v>0</v>
-      </c>
-      <c r="F116" t="n">
-        <v>0</v>
-      </c>
-      <c r="G116" t="n">
-        <v>0</v>
-      </c>
-      <c r="H116" t="n">
-        <v>0</v>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="117">
@@ -3697,20 +4763,30 @@
           <t>VeryGames</t>
         </is>
       </c>
-      <c r="D117" t="n">
-        <v>0</v>
-      </c>
-      <c r="E117" t="n">
-        <v>0</v>
-      </c>
-      <c r="F117" t="n">
-        <v>0</v>
-      </c>
-      <c r="G117" t="n">
-        <v>0</v>
-      </c>
-      <c r="H117" t="n">
-        <v>0</v>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="118">
@@ -3725,20 +4801,30 @@
           <t>mousesports</t>
         </is>
       </c>
-      <c r="D118" t="n">
-        <v>0</v>
-      </c>
-      <c r="E118" t="n">
-        <v>0</v>
-      </c>
-      <c r="F118" t="n">
-        <v>0</v>
-      </c>
-      <c r="G118" t="n">
-        <v>0</v>
-      </c>
-      <c r="H118" t="n">
-        <v>0</v>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="119">
@@ -3753,20 +4839,30 @@
           <t>Vox Eminor</t>
         </is>
       </c>
-      <c r="D119" t="n">
-        <v>0</v>
-      </c>
-      <c r="E119" t="n">
-        <v>0</v>
-      </c>
-      <c r="F119" t="n">
-        <v>0</v>
-      </c>
-      <c r="G119" t="n">
-        <v>0</v>
-      </c>
-      <c r="H119" t="n">
-        <v>0</v>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="120">
@@ -3781,20 +4877,30 @@
           <t>LGB eSports</t>
         </is>
       </c>
-      <c r="D120" t="n">
-        <v>0</v>
-      </c>
-      <c r="E120" t="n">
-        <v>0</v>
-      </c>
-      <c r="F120" t="n">
-        <v>0</v>
-      </c>
-      <c r="G120" t="n">
-        <v>0</v>
-      </c>
-      <c r="H120" t="n">
-        <v>0</v>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="121">
@@ -3809,20 +4915,30 @@
           <t>Epsilon</t>
         </is>
       </c>
-      <c r="D121" t="n">
-        <v>0</v>
-      </c>
-      <c r="E121" t="n">
-        <v>0</v>
-      </c>
-      <c r="F121" t="n">
-        <v>0</v>
-      </c>
-      <c r="G121" t="n">
-        <v>0</v>
-      </c>
-      <c r="H121" t="n">
-        <v>0</v>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="122">
@@ -3837,20 +4953,30 @@
           <t>ESC</t>
         </is>
       </c>
-      <c r="D122" t="n">
-        <v>0</v>
-      </c>
-      <c r="E122" t="n">
-        <v>0</v>
-      </c>
-      <c r="F122" t="n">
-        <v>0</v>
-      </c>
-      <c r="G122" t="n">
-        <v>0</v>
-      </c>
-      <c r="H122" t="n">
-        <v>0</v>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="123">
@@ -3865,20 +4991,30 @@
           <t>Bravado</t>
         </is>
       </c>
-      <c r="D123" t="n">
-        <v>0</v>
-      </c>
-      <c r="E123" t="n">
-        <v>0</v>
-      </c>
-      <c r="F123" t="n">
-        <v>0</v>
-      </c>
-      <c r="G123" t="n">
-        <v>0</v>
-      </c>
-      <c r="H123" t="n">
-        <v>0</v>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="124">
@@ -3893,20 +5029,30 @@
           <t>Team Kinguin</t>
         </is>
       </c>
-      <c r="D124" t="n">
-        <v>0</v>
-      </c>
-      <c r="E124" t="n">
-        <v>0</v>
-      </c>
-      <c r="F124" t="n">
-        <v>0</v>
-      </c>
-      <c r="G124" t="n">
-        <v>0</v>
-      </c>
-      <c r="H124" t="n">
-        <v>0</v>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="125">
@@ -3921,20 +5067,30 @@
           <t>Counter Logic Games</t>
         </is>
       </c>
-      <c r="D125" t="n">
-        <v>0</v>
-      </c>
-      <c r="E125" t="n">
-        <v>0</v>
-      </c>
-      <c r="F125" t="n">
-        <v>0</v>
-      </c>
-      <c r="G125" t="n">
-        <v>0</v>
-      </c>
-      <c r="H125" t="n">
-        <v>0</v>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="126">
@@ -3949,20 +5105,30 @@
           <t>Gambit</t>
         </is>
       </c>
-      <c r="D126" t="n">
-        <v>0</v>
-      </c>
-      <c r="E126" t="n">
-        <v>0</v>
-      </c>
-      <c r="F126" t="n">
-        <v>0</v>
-      </c>
-      <c r="G126" t="n">
-        <v>0</v>
-      </c>
-      <c r="H126" t="n">
-        <v>0</v>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="127">
@@ -3977,20 +5143,30 @@
           <t>Space Soldiers</t>
         </is>
       </c>
-      <c r="D127" t="n">
-        <v>0</v>
-      </c>
-      <c r="E127" t="n">
-        <v>0</v>
-      </c>
-      <c r="F127" t="n">
-        <v>0</v>
-      </c>
-      <c r="G127" t="n">
-        <v>0</v>
-      </c>
-      <c r="H127" t="n">
-        <v>0</v>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="128">
@@ -4005,20 +5181,30 @@
           <t>Quantum Bellator Fire</t>
         </is>
       </c>
-      <c r="D128" t="n">
-        <v>0</v>
-      </c>
-      <c r="E128" t="n">
-        <v>0</v>
-      </c>
-      <c r="F128" t="n">
-        <v>0</v>
-      </c>
-      <c r="G128" t="n">
-        <v>0</v>
-      </c>
-      <c r="H128" t="n">
-        <v>0</v>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="129">
@@ -4033,20 +5219,30 @@
           <t>Avangar</t>
         </is>
       </c>
-      <c r="D129" t="n">
-        <v>0</v>
-      </c>
-      <c r="E129" t="n">
-        <v>0</v>
-      </c>
-      <c r="F129" t="n">
-        <v>0</v>
-      </c>
-      <c r="G129" t="n">
-        <v>0</v>
-      </c>
-      <c r="H129" t="n">
-        <v>0</v>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="130">
@@ -4061,20 +5257,30 @@
           <t>Misfits</t>
         </is>
       </c>
-      <c r="D130" t="n">
-        <v>0</v>
-      </c>
-      <c r="E130" t="n">
-        <v>0</v>
-      </c>
-      <c r="F130" t="n">
-        <v>0</v>
-      </c>
-      <c r="G130" t="n">
-        <v>0</v>
-      </c>
-      <c r="H130" t="n">
-        <v>0</v>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="131">
@@ -4089,20 +5295,30 @@
           <t>Sprout</t>
         </is>
       </c>
-      <c r="D131" t="n">
-        <v>0</v>
-      </c>
-      <c r="E131" t="n">
-        <v>0</v>
-      </c>
-      <c r="F131" t="n">
-        <v>0</v>
-      </c>
-      <c r="G131" t="n">
-        <v>0</v>
-      </c>
-      <c r="H131" t="n">
-        <v>0</v>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="132">
@@ -4117,20 +5333,30 @@
           <t>Flash</t>
         </is>
       </c>
-      <c r="D132" t="n">
-        <v>0</v>
-      </c>
-      <c r="E132" t="n">
-        <v>0</v>
-      </c>
-      <c r="F132" t="n">
-        <v>0</v>
-      </c>
-      <c r="G132" t="n">
-        <v>0</v>
-      </c>
-      <c r="H132" t="n">
-        <v>0</v>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="133">
@@ -4145,20 +5371,30 @@
           <t>100 Thieves</t>
         </is>
       </c>
-      <c r="D133" t="n">
-        <v>0</v>
-      </c>
-      <c r="E133" t="n">
-        <v>0</v>
-      </c>
-      <c r="F133" t="n">
-        <v>0</v>
-      </c>
-      <c r="G133" t="n">
-        <v>0</v>
-      </c>
-      <c r="H133" t="n">
-        <v>0</v>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="134">
@@ -4173,20 +5409,30 @@
           <t>Immortals</t>
         </is>
       </c>
-      <c r="D134" t="n">
-        <v>0</v>
-      </c>
-      <c r="E134" t="n">
-        <v>0</v>
-      </c>
-      <c r="F134" t="n">
-        <v>0</v>
-      </c>
-      <c r="G134" t="n">
-        <v>0</v>
-      </c>
-      <c r="H134" t="n">
-        <v>0</v>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="135">
@@ -4201,20 +5447,30 @@
           <t>Rogue</t>
         </is>
       </c>
-      <c r="D135" t="n">
-        <v>0</v>
-      </c>
-      <c r="E135" t="n">
-        <v>0</v>
-      </c>
-      <c r="F135" t="n">
-        <v>0</v>
-      </c>
-      <c r="G135" t="n">
-        <v>0</v>
-      </c>
-      <c r="H135" t="n">
-        <v>0</v>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="136">
@@ -4229,20 +5485,30 @@
           <t>FORZE</t>
         </is>
       </c>
-      <c r="D136" t="n">
-        <v>0</v>
-      </c>
-      <c r="E136" t="n">
-        <v>0</v>
-      </c>
-      <c r="F136" t="n">
-        <v>0</v>
-      </c>
-      <c r="G136" t="n">
-        <v>0</v>
-      </c>
-      <c r="H136" t="n">
-        <v>0</v>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="137">
@@ -4257,20 +5523,30 @@
           <t>00 Nation</t>
         </is>
       </c>
-      <c r="D137" t="n">
-        <v>0</v>
-      </c>
-      <c r="E137" t="n">
-        <v>0</v>
-      </c>
-      <c r="F137" t="n">
-        <v>0</v>
-      </c>
-      <c r="G137" t="n">
-        <v>0</v>
-      </c>
-      <c r="H137" t="n">
-        <v>0</v>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="138">
@@ -4285,20 +5561,30 @@
           <t>Into the Beach</t>
         </is>
       </c>
-      <c r="D138" t="n">
-        <v>0</v>
-      </c>
-      <c r="E138" t="n">
-        <v>0</v>
-      </c>
-      <c r="F138" t="n">
-        <v>0</v>
-      </c>
-      <c r="G138" t="n">
-        <v>0</v>
-      </c>
-      <c r="H138" t="n">
-        <v>0</v>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="139">
@@ -4313,20 +5599,30 @@
           <t>Movistar KOI</t>
         </is>
       </c>
-      <c r="D139" t="n">
-        <v>0</v>
-      </c>
-      <c r="E139" t="n">
-        <v>0</v>
-      </c>
-      <c r="F139" t="n">
-        <v>0</v>
-      </c>
-      <c r="G139" t="n">
-        <v>0</v>
-      </c>
-      <c r="H139" t="n">
-        <v>0</v>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="140">
@@ -4341,20 +5637,30 @@
           <t>FLuffy Gangsters</t>
         </is>
       </c>
-      <c r="D140" t="n">
-        <v>0</v>
-      </c>
-      <c r="E140" t="n">
-        <v>0</v>
-      </c>
-      <c r="F140" t="n">
-        <v>0</v>
-      </c>
-      <c r="G140" t="n">
-        <v>0</v>
-      </c>
-      <c r="H140" t="n">
-        <v>0</v>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="141">
@@ -4369,20 +5675,30 @@
           <t>NIP Impact</t>
         </is>
       </c>
-      <c r="D141" t="n">
-        <v>0</v>
-      </c>
-      <c r="E141" t="n">
-        <v>0</v>
-      </c>
-      <c r="F141" t="n">
-        <v>0</v>
-      </c>
-      <c r="G141" t="n">
-        <v>0</v>
-      </c>
-      <c r="H141" t="n">
-        <v>0</v>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="142">
@@ -4397,20 +5713,30 @@
           <t>FlyQuest RED</t>
         </is>
       </c>
-      <c r="D142" t="n">
-        <v>0</v>
-      </c>
-      <c r="E142" t="n">
-        <v>0</v>
-      </c>
-      <c r="F142" t="n">
-        <v>0</v>
-      </c>
-      <c r="G142" t="n">
-        <v>0</v>
-      </c>
-      <c r="H142" t="n">
-        <v>0</v>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="143">
@@ -4425,20 +5751,30 @@
           <t>Heroic Academy</t>
         </is>
       </c>
-      <c r="D143" t="n">
-        <v>0</v>
-      </c>
-      <c r="E143" t="n">
-        <v>0</v>
-      </c>
-      <c r="F143" t="n">
-        <v>0</v>
-      </c>
-      <c r="G143" t="n">
-        <v>0</v>
-      </c>
-      <c r="H143" t="n">
-        <v>0</v>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="144">
@@ -4453,20 +5789,30 @@
           <t>Astralis Talent</t>
         </is>
       </c>
-      <c r="D144" t="n">
-        <v>0</v>
-      </c>
-      <c r="E144" t="n">
-        <v>0</v>
-      </c>
-      <c r="F144" t="n">
-        <v>0</v>
-      </c>
-      <c r="G144" t="n">
-        <v>0</v>
-      </c>
-      <c r="H144" t="n">
-        <v>0</v>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="145">
@@ -4481,20 +5827,30 @@
           <t>BIG Academy</t>
         </is>
       </c>
-      <c r="D145" t="n">
-        <v>0</v>
-      </c>
-      <c r="E145" t="n">
-        <v>0</v>
-      </c>
-      <c r="F145" t="n">
-        <v>0</v>
-      </c>
-      <c r="G145" t="n">
-        <v>0</v>
-      </c>
-      <c r="H145" t="n">
-        <v>0</v>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="146">
@@ -4509,20 +5865,30 @@
           <t>ENCE Academy</t>
         </is>
       </c>
-      <c r="D146" t="n">
-        <v>0</v>
-      </c>
-      <c r="E146" t="n">
-        <v>0</v>
-      </c>
-      <c r="F146" t="n">
-        <v>0</v>
-      </c>
-      <c r="G146" t="n">
-        <v>0</v>
-      </c>
-      <c r="H146" t="n">
-        <v>0</v>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="147">
@@ -4537,20 +5903,30 @@
           <t>MOUZ NXT</t>
         </is>
       </c>
-      <c r="D147" t="n">
-        <v>0</v>
-      </c>
-      <c r="E147" t="n">
-        <v>0</v>
-      </c>
-      <c r="F147" t="n">
-        <v>0</v>
-      </c>
-      <c r="G147" t="n">
-        <v>0</v>
-      </c>
-      <c r="H147" t="n">
-        <v>0</v>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="148">
@@ -4565,20 +5941,30 @@
           <t>B8</t>
         </is>
       </c>
-      <c r="D148" t="n">
-        <v>0</v>
-      </c>
-      <c r="E148" t="n">
-        <v>0</v>
-      </c>
-      <c r="F148" t="n">
-        <v>0</v>
-      </c>
-      <c r="G148" t="n">
-        <v>0</v>
-      </c>
-      <c r="H148" t="n">
-        <v>0</v>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="149">
@@ -4593,20 +5979,30 @@
           <t>QMISTRY</t>
         </is>
       </c>
-      <c r="D149" t="n">
-        <v>0</v>
-      </c>
-      <c r="E149" t="n">
-        <v>0</v>
-      </c>
-      <c r="F149" t="n">
-        <v>0</v>
-      </c>
-      <c r="G149" t="n">
-        <v>0</v>
-      </c>
-      <c r="H149" t="n">
-        <v>0</v>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="150">
@@ -4621,20 +6017,30 @@
           <t>Wildcard Academy</t>
         </is>
       </c>
-      <c r="D150" t="n">
-        <v>0</v>
-      </c>
-      <c r="E150" t="n">
-        <v>0</v>
-      </c>
-      <c r="F150" t="n">
-        <v>0</v>
-      </c>
-      <c r="G150" t="n">
-        <v>0</v>
-      </c>
-      <c r="H150" t="n">
-        <v>0</v>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="151">
@@ -4649,20 +6055,30 @@
           <t>Tsunami</t>
         </is>
       </c>
-      <c r="D151" t="n">
-        <v>0</v>
-      </c>
-      <c r="E151" t="n">
-        <v>0</v>
-      </c>
-      <c r="F151" t="n">
-        <v>0</v>
-      </c>
-      <c r="G151" t="n">
-        <v>0</v>
-      </c>
-      <c r="H151" t="n">
-        <v>0</v>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="152">
@@ -4677,20 +6093,30 @@
           <t>NOVAQ</t>
         </is>
       </c>
-      <c r="D152" t="n">
-        <v>0</v>
-      </c>
-      <c r="E152" t="n">
-        <v>0</v>
-      </c>
-      <c r="F152" t="n">
-        <v>0</v>
-      </c>
-      <c r="G152" t="n">
-        <v>0</v>
-      </c>
-      <c r="H152" t="n">
-        <v>0</v>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="153">
@@ -4705,20 +6131,30 @@
           <t>HAVU</t>
         </is>
       </c>
-      <c r="D153" t="n">
-        <v>0</v>
-      </c>
-      <c r="E153" t="n">
-        <v>0</v>
-      </c>
-      <c r="F153" t="n">
-        <v>0</v>
-      </c>
-      <c r="G153" t="n">
-        <v>0</v>
-      </c>
-      <c r="H153" t="n">
-        <v>0</v>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="154">
@@ -4733,20 +6169,30 @@
           <t>MANA</t>
         </is>
       </c>
-      <c r="D154" t="n">
-        <v>0</v>
-      </c>
-      <c r="E154" t="n">
-        <v>0</v>
-      </c>
-      <c r="F154" t="n">
-        <v>0</v>
-      </c>
-      <c r="G154" t="n">
-        <v>0</v>
-      </c>
-      <c r="H154" t="n">
-        <v>0</v>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="155">
@@ -4761,20 +6207,30 @@
           <t>MIBR Academy</t>
         </is>
       </c>
-      <c r="D155" t="n">
-        <v>0</v>
-      </c>
-      <c r="E155" t="n">
-        <v>0</v>
-      </c>
-      <c r="F155" t="n">
-        <v>0</v>
-      </c>
-      <c r="G155" t="n">
-        <v>0</v>
-      </c>
-      <c r="H155" t="n">
-        <v>0</v>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="156">
@@ -4789,20 +6245,30 @@
           <t>AMKAL</t>
         </is>
       </c>
-      <c r="D156" t="n">
-        <v>0</v>
-      </c>
-      <c r="E156" t="n">
-        <v>0</v>
-      </c>
-      <c r="F156" t="n">
-        <v>0</v>
-      </c>
-      <c r="G156" t="n">
-        <v>0</v>
-      </c>
-      <c r="H156" t="n">
-        <v>0</v>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="157">
@@ -4817,20 +6283,30 @@
           <t>Hesta</t>
         </is>
       </c>
-      <c r="D157" t="n">
-        <v>0</v>
-      </c>
-      <c r="E157" t="n">
-        <v>0</v>
-      </c>
-      <c r="F157" t="n">
-        <v>0</v>
-      </c>
-      <c r="G157" t="n">
-        <v>0</v>
-      </c>
-      <c r="H157" t="n">
-        <v>0</v>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="158">
@@ -4845,20 +6321,30 @@
           <t>kONO</t>
         </is>
       </c>
-      <c r="D158" t="n">
-        <v>0</v>
-      </c>
-      <c r="E158" t="n">
-        <v>0</v>
-      </c>
-      <c r="F158" t="n">
-        <v>0</v>
-      </c>
-      <c r="G158" t="n">
-        <v>0</v>
-      </c>
-      <c r="H158" t="n">
-        <v>0</v>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="159">
@@ -4873,20 +6359,30 @@
           <t>SKYFURY</t>
         </is>
       </c>
-      <c r="D159" t="n">
-        <v>0</v>
-      </c>
-      <c r="E159" t="n">
-        <v>0</v>
-      </c>
-      <c r="F159" t="n">
-        <v>0</v>
-      </c>
-      <c r="G159" t="n">
-        <v>0</v>
-      </c>
-      <c r="H159" t="n">
-        <v>0</v>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="160">
@@ -4901,20 +6397,30 @@
           <t>GhoulsW</t>
         </is>
       </c>
-      <c r="D160" t="n">
-        <v>0</v>
-      </c>
-      <c r="E160" t="n">
-        <v>0</v>
-      </c>
-      <c r="F160" t="n">
-        <v>0</v>
-      </c>
-      <c r="G160" t="n">
-        <v>0</v>
-      </c>
-      <c r="H160" t="n">
-        <v>0</v>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="161">
@@ -4929,20 +6435,30 @@
           <t>paiN Academy</t>
         </is>
       </c>
-      <c r="D161" t="n">
-        <v>0</v>
-      </c>
-      <c r="E161" t="n">
-        <v>0</v>
-      </c>
-      <c r="F161" t="n">
-        <v>0</v>
-      </c>
-      <c r="G161" t="n">
-        <v>0</v>
-      </c>
-      <c r="H161" t="n">
-        <v>0</v>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="162">
@@ -4957,20 +6473,30 @@
           <t>Nordix</t>
         </is>
       </c>
-      <c r="D162" t="n">
-        <v>0</v>
-      </c>
-      <c r="E162" t="n">
-        <v>0</v>
-      </c>
-      <c r="F162" t="n">
-        <v>0</v>
-      </c>
-      <c r="G162" t="n">
-        <v>0</v>
-      </c>
-      <c r="H162" t="n">
-        <v>0</v>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="163">
@@ -4985,20 +6511,30 @@
           <t>Aether</t>
         </is>
       </c>
-      <c r="D163" t="n">
-        <v>0</v>
-      </c>
-      <c r="E163" t="n">
-        <v>0</v>
-      </c>
-      <c r="F163" t="n">
-        <v>0</v>
-      </c>
-      <c r="G163" t="n">
-        <v>0</v>
-      </c>
-      <c r="H163" t="n">
-        <v>0</v>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="164">
@@ -5013,20 +6549,30 @@
           <t>GATERON</t>
         </is>
       </c>
-      <c r="D164" t="n">
-        <v>0</v>
-      </c>
-      <c r="E164" t="n">
-        <v>0</v>
-      </c>
-      <c r="F164" t="n">
-        <v>0</v>
-      </c>
-      <c r="G164" t="n">
-        <v>0</v>
-      </c>
-      <c r="H164" t="n">
-        <v>0</v>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="165">
@@ -5041,20 +6587,30 @@
           <t>Shika</t>
         </is>
       </c>
-      <c r="D165" t="n">
-        <v>0</v>
-      </c>
-      <c r="E165" t="n">
-        <v>0</v>
-      </c>
-      <c r="F165" t="n">
-        <v>0</v>
-      </c>
-      <c r="G165" t="n">
-        <v>0</v>
-      </c>
-      <c r="H165" t="n">
-        <v>0</v>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -477,25 +477,19 @@
           <t>Vitality</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G2" t="n">
+        <v>8</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -515,25 +509,19 @@
           <t>Astralis</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G3" t="n">
+        <v>8</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -629,25 +617,19 @@
           <t>Heroic</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G6" t="n">
+        <v>8</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -705,25 +687,19 @@
           <t>FaZe</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G8" t="n">
+        <v>8</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -748,20 +724,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-5</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -781,25 +751,19 @@
           <t>ENCE</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G10" t="n">
+        <v>8</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -824,20 +788,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-5</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -933,17 +891,25 @@
           <t>MIBR</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>4</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>5</v>
-      </c>
-      <c r="G14" t="n">
-        <v>8</v>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1006,20 +972,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-5</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1039,25 +999,19 @@
           <t>G2</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G17" t="n">
+        <v>8</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1077,25 +1031,19 @@
           <t>OG</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G18" t="n">
+        <v>8</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1305,25 +1253,19 @@
           <t>Copenhagen Flames</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G24" t="n">
+        <v>8</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1348,20 +1290,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-5</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1381,25 +1317,19 @@
           <t>iBUYPOWER</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G26" t="n">
+        <v>8</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1462,20 +1392,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-5</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -1495,25 +1419,19 @@
           <t>Cloud9</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G29" t="n">
+        <v>8</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -1533,17 +1451,25 @@
           <t>SK</t>
         </is>
       </c>
-      <c r="D30" t="n">
-        <v>3</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" t="n">
-        <v>4</v>
-      </c>
-      <c r="G30" t="n">
-        <v>5</v>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -1568,14 +1494,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E31" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" t="n">
-        <v>1</v>
-      </c>
-      <c r="G31" t="n">
-        <v>-5</v>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -1676,20 +1608,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-5</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -1747,25 +1673,19 @@
           <t>ShindeN</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G36" t="n">
+        <v>8</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -1823,25 +1743,19 @@
           <t>Nexus</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G38" t="n">
+        <v>8</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -1904,20 +1818,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-5</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -1942,20 +1850,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-5</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -2013,25 +1915,19 @@
           <t>Permitta</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G43" t="n">
+        <v>8</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -2051,25 +1947,19 @@
           <t>Rebels</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G44" t="n">
+        <v>8</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -2089,25 +1979,19 @@
           <t>Eternal Fire</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G45" t="n">
+        <v>8</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -2132,20 +2016,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" t="n">
+        <v>-5</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -2170,20 +2048,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" t="n">
+        <v>-5</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -2208,14 +2080,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E48" t="n">
-        <v>0</v>
-      </c>
-      <c r="F48" t="n">
-        <v>1</v>
-      </c>
-      <c r="G48" t="n">
-        <v>-5</v>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -2235,17 +2113,25 @@
           <t>M80</t>
         </is>
       </c>
-      <c r="D49" t="n">
-        <v>3</v>
-      </c>
-      <c r="E49" t="n">
-        <v>0</v>
-      </c>
-      <c r="F49" t="n">
-        <v>4</v>
-      </c>
-      <c r="G49" t="n">
-        <v>7</v>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -2265,25 +2151,19 @@
           <t>Wildcard</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G50" t="n">
+        <v>8</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -2341,17 +2221,25 @@
           <t>ECSTATIC</t>
         </is>
       </c>
-      <c r="D52" t="n">
-        <v>2</v>
-      </c>
-      <c r="E52" t="n">
-        <v>0</v>
-      </c>
-      <c r="F52" t="n">
-        <v>4</v>
-      </c>
-      <c r="G52" t="n">
-        <v>-4</v>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-4</t>
+        </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -2371,17 +2259,25 @@
           <t>RED Canids</t>
         </is>
       </c>
-      <c r="D53" t="n">
-        <v>5</v>
-      </c>
-      <c r="E53" t="n">
-        <v>0</v>
-      </c>
-      <c r="F53" t="n">
-        <v>4</v>
-      </c>
-      <c r="G53" t="n">
-        <v>24</v>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -2520,20 +2416,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E57" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" t="n">
+        <v>-5</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -2672,20 +2562,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" t="n">
+        <v>-5</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -2824,14 +2708,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E65" t="n">
-        <v>0</v>
-      </c>
-      <c r="F65" t="n">
-        <v>1</v>
-      </c>
-      <c r="G65" t="n">
-        <v>-5</v>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -3008,20 +2898,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E70" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" t="n">
+        <v>-5</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -3160,20 +3044,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E74" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" t="n">
+        <v>-5</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -3692,14 +3570,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E88" t="n">
-        <v>0</v>
-      </c>
-      <c r="F88" t="n">
-        <v>1</v>
-      </c>
-      <c r="G88" t="n">
-        <v>-5</v>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -4370,14 +4254,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E106" t="n">
-        <v>0</v>
-      </c>
-      <c r="F106" t="n">
-        <v>1</v>
-      </c>
-      <c r="G106" t="n">
-        <v>-5</v>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -4402,20 +4292,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E107" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" t="n">
+        <v>1</v>
+      </c>
+      <c r="G107" t="n">
+        <v>-5</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
@@ -4549,17 +4433,25 @@
           <t>GODSENT</t>
         </is>
       </c>
-      <c r="D111" t="n">
-        <v>3</v>
-      </c>
-      <c r="E111" t="n">
-        <v>0</v>
-      </c>
-      <c r="F111" t="n">
-        <v>5</v>
-      </c>
-      <c r="G111" t="n">
-        <v>0</v>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -4622,14 +4514,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E113" t="n">
-        <v>0</v>
-      </c>
-      <c r="F113" t="n">
-        <v>1</v>
-      </c>
-      <c r="G113" t="n">
-        <v>-5</v>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
@@ -4920,20 +4818,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E121" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" t="n">
+        <v>1</v>
+      </c>
+      <c r="G121" t="n">
+        <v>-5</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -477,19 +477,25 @@
           <t>Vitality</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>8</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -509,19 +515,25 @@
           <t>Astralis</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>8</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -617,19 +629,25 @@
           <t>Heroic</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1</v>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>8</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -687,19 +705,25 @@
           <t>FaZe</t>
         </is>
       </c>
-      <c r="D8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1</v>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>8</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -724,14 +748,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="n">
-        <v>-5</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -751,19 +781,25 @@
           <t>ENCE</t>
         </is>
       </c>
-      <c r="D10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1</v>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>8</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -788,14 +824,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="n">
-        <v>-5</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -929,25 +971,19 @@
           <t>Natus Vincere</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G15" t="n">
+        <v>8</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -972,14 +1008,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" t="n">
-        <v>-5</v>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -999,19 +1041,25 @@
           <t>G2</t>
         </is>
       </c>
-      <c r="D17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" t="n">
-        <v>1</v>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>8</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1031,19 +1079,25 @@
           <t>OG</t>
         </is>
       </c>
-      <c r="D18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" t="n">
-        <v>1</v>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>8</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1141,12 +1195,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1156,7 +1210,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1179,12 +1233,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1194,7 +1248,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1215,25 +1269,19 @@
           <t>Entropiq</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G23" t="n">
+        <v>8</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1253,19 +1301,25 @@
           <t>Copenhagen Flames</t>
         </is>
       </c>
-      <c r="D24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" t="n">
-        <v>1</v>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>8</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1290,14 +1344,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G25" t="n">
-        <v>-5</v>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1317,19 +1377,25 @@
           <t>iBUYPOWER</t>
         </is>
       </c>
-      <c r="D26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" t="n">
-        <v>1</v>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>8</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1354,20 +1420,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-5</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1392,14 +1452,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E28" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" t="n">
-        <v>-5</v>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -1419,19 +1485,25 @@
           <t>Cloud9</t>
         </is>
       </c>
-      <c r="D29" t="n">
-        <v>1</v>
-      </c>
-      <c r="E29" t="n">
-        <v>1</v>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>8</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -1608,14 +1680,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E34" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" t="n">
-        <v>1</v>
-      </c>
-      <c r="G34" t="n">
-        <v>-5</v>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -1640,20 +1718,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-5</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -1673,19 +1745,25 @@
           <t>ShindeN</t>
         </is>
       </c>
-      <c r="D36" t="n">
-        <v>1</v>
-      </c>
-      <c r="E36" t="n">
-        <v>1</v>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>8</v>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -1710,20 +1788,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-5</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -1743,19 +1815,25 @@
           <t>Nexus</t>
         </is>
       </c>
-      <c r="D38" t="n">
-        <v>1</v>
-      </c>
-      <c r="E38" t="n">
-        <v>1</v>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>8</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -1780,20 +1858,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-5</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -1818,14 +1890,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E40" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" t="n">
-        <v>1</v>
-      </c>
-      <c r="G40" t="n">
-        <v>-5</v>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -1850,14 +1928,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E41" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" t="n">
-        <v>1</v>
-      </c>
-      <c r="G41" t="n">
-        <v>-5</v>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -1882,20 +1966,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-5</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -1915,19 +1993,25 @@
           <t>Permitta</t>
         </is>
       </c>
-      <c r="D43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E43" t="n">
-        <v>1</v>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G43" t="n">
-        <v>8</v>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -1947,19 +2031,25 @@
           <t>Rebels</t>
         </is>
       </c>
-      <c r="D44" t="n">
-        <v>1</v>
-      </c>
-      <c r="E44" t="n">
-        <v>1</v>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G44" t="n">
-        <v>8</v>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -1979,19 +2069,25 @@
           <t>Eternal Fire</t>
         </is>
       </c>
-      <c r="D45" t="n">
-        <v>1</v>
-      </c>
-      <c r="E45" t="n">
-        <v>1</v>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G45" t="n">
-        <v>8</v>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -2016,14 +2112,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E46" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" t="n">
-        <v>1</v>
-      </c>
-      <c r="G46" t="n">
-        <v>-5</v>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -2048,14 +2150,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E47" t="n">
-        <v>0</v>
-      </c>
-      <c r="F47" t="n">
-        <v>1</v>
-      </c>
-      <c r="G47" t="n">
-        <v>-5</v>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -2151,19 +2259,25 @@
           <t>Wildcard</t>
         </is>
       </c>
-      <c r="D50" t="n">
-        <v>1</v>
-      </c>
-      <c r="E50" t="n">
-        <v>1</v>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G50" t="n">
-        <v>8</v>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -2183,25 +2297,19 @@
           <t>BESTIA</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D51" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" t="n">
+        <v>1</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G51" t="n">
+        <v>8</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -2416,14 +2524,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E57" t="n">
-        <v>0</v>
-      </c>
-      <c r="F57" t="n">
-        <v>1</v>
-      </c>
-      <c r="G57" t="n">
-        <v>-5</v>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -2443,25 +2557,19 @@
           <t>Underground</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D58" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" t="n">
+        <v>1</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G58" t="n">
+        <v>8</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -2562,14 +2670,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E61" t="n">
-        <v>0</v>
-      </c>
-      <c r="F61" t="n">
-        <v>1</v>
-      </c>
-      <c r="G61" t="n">
-        <v>-5</v>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -2589,25 +2703,19 @@
           <t>Homyno</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D62" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" t="n">
+        <v>1</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G62" t="n">
+        <v>8</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -2629,12 +2737,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2644,7 +2752,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -2746,20 +2854,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E66" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" t="n">
+        <v>-5</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -2784,20 +2886,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E67" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" t="n">
+        <v>-5</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -2817,25 +2913,19 @@
           <t>Team Solid</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D68" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" t="n">
+        <v>1</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G68" t="n">
+        <v>8</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -2898,14 +2988,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E70" t="n">
-        <v>0</v>
-      </c>
-      <c r="F70" t="n">
-        <v>1</v>
-      </c>
-      <c r="G70" t="n">
-        <v>-5</v>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -2927,12 +3023,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2942,7 +3038,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -2968,20 +3064,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" t="n">
+        <v>-5</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -3001,25 +3091,19 @@
           <t>The MongolZ</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D73" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" t="n">
+        <v>1</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G73" t="n">
+        <v>8</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -3044,14 +3128,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E74" t="n">
-        <v>0</v>
-      </c>
-      <c r="F74" t="n">
-        <v>1</v>
-      </c>
-      <c r="G74" t="n">
-        <v>-5</v>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -3073,12 +3163,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3088,7 +3178,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3114,20 +3204,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E76" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" t="n">
+        <v>-5</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -3147,25 +3231,19 @@
           <t>VP.Prodigy</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D77" t="n">
+        <v>1</v>
+      </c>
+      <c r="E77" t="n">
+        <v>1</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G77" t="n">
+        <v>8</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -3187,12 +3265,12 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3202,7 +3280,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -3228,20 +3306,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E79" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" t="n">
+        <v>-5</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -3263,12 +3335,12 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3278,7 +3350,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3304,20 +3376,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" t="n">
+        <v>-5</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -3342,20 +3408,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E82" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" t="n">
+        <v>-5</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -3375,25 +3435,19 @@
           <t>TYLOO</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D83" t="n">
+        <v>1</v>
+      </c>
+      <c r="E83" t="n">
+        <v>1</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G83" t="n">
+        <v>8</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -3418,20 +3472,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E84" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" t="n">
+        <v>-5</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -3456,20 +3504,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E85" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" t="n">
+        <v>-5</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -3491,12 +3533,12 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3506,7 +3548,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -3532,20 +3574,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E87" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" t="n">
+        <v>-5</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -3603,25 +3639,19 @@
           <t>MenaceGG</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D89" t="n">
+        <v>1</v>
+      </c>
+      <c r="E89" t="n">
+        <v>1</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G89" t="n">
+        <v>8</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -3646,20 +3676,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E90" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" t="n">
+        <v>-5</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -3684,20 +3708,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E91" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" t="n">
+        <v>1</v>
+      </c>
+      <c r="G91" t="n">
+        <v>-5</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -3717,25 +3735,19 @@
           <t>Aravt</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D92" t="n">
+        <v>1</v>
+      </c>
+      <c r="E92" t="n">
+        <v>1</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G92" t="n">
+        <v>8</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -3760,20 +3772,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E93" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" t="n">
+        <v>1</v>
+      </c>
+      <c r="G93" t="n">
+        <v>-5</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
@@ -3793,25 +3799,19 @@
           <t>True Rippers</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D94" t="n">
+        <v>1</v>
+      </c>
+      <c r="E94" t="n">
+        <v>1</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G94" t="n">
+        <v>8</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -3833,12 +3833,12 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -3874,20 +3874,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E96" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" t="n">
+        <v>1</v>
+      </c>
+      <c r="G96" t="n">
+        <v>-5</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -3912,20 +3906,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E97" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" t="n">
+        <v>1</v>
+      </c>
+      <c r="G97" t="n">
+        <v>-5</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -3947,12 +3935,12 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3962,7 +3950,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -3988,20 +3976,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E99" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" t="n">
+        <v>1</v>
+      </c>
+      <c r="G99" t="n">
+        <v>-5</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -4026,20 +4008,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E100" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" t="n">
+        <v>1</v>
+      </c>
+      <c r="G100" t="n">
+        <v>-5</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -4059,25 +4035,19 @@
           <t>Onyx Ravens</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D101" t="n">
+        <v>1</v>
+      </c>
+      <c r="E101" t="n">
+        <v>1</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G101" t="n">
+        <v>8</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -4102,20 +4072,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E102" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" t="n">
+        <v>1</v>
+      </c>
+      <c r="G102" t="n">
+        <v>-5</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
@@ -4140,20 +4104,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E103" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" t="n">
+        <v>1</v>
+      </c>
+      <c r="G103" t="n">
+        <v>-5</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
@@ -4292,14 +4250,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E107" t="n">
-        <v>0</v>
-      </c>
-      <c r="F107" t="n">
-        <v>1</v>
-      </c>
-      <c r="G107" t="n">
-        <v>-5</v>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
@@ -4395,25 +4359,19 @@
           <t>hoorai</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D110" t="n">
+        <v>1</v>
+      </c>
+      <c r="E110" t="n">
+        <v>1</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G110" t="n">
+        <v>8</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -4818,14 +4776,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E121" t="n">
-        <v>0</v>
-      </c>
-      <c r="F121" t="n">
-        <v>1</v>
-      </c>
-      <c r="G121" t="n">
-        <v>-5</v>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -971,19 +971,25 @@
           <t>Natus Vincere</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" t="n">
-        <v>1</v>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>8</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1269,19 +1275,25 @@
           <t>Entropiq</t>
         </is>
       </c>
-      <c r="D23" t="n">
-        <v>1</v>
-      </c>
-      <c r="E23" t="n">
-        <v>1</v>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>8</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1420,14 +1432,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" t="n">
-        <v>-5</v>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1718,14 +1736,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E35" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" t="n">
-        <v>1</v>
-      </c>
-      <c r="G35" t="n">
-        <v>-5</v>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -1788,14 +1812,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E37" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" t="n">
-        <v>1</v>
-      </c>
-      <c r="G37" t="n">
-        <v>-5</v>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -1858,14 +1888,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E39" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" t="n">
-        <v>1</v>
-      </c>
-      <c r="G39" t="n">
-        <v>-5</v>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -1966,14 +2002,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E42" t="n">
-        <v>0</v>
-      </c>
-      <c r="F42" t="n">
-        <v>1</v>
-      </c>
-      <c r="G42" t="n">
-        <v>-5</v>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -2297,19 +2339,25 @@
           <t>BESTIA</t>
         </is>
       </c>
-      <c r="D51" t="n">
-        <v>1</v>
-      </c>
-      <c r="E51" t="n">
-        <v>1</v>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G51" t="n">
-        <v>8</v>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -2557,19 +2605,25 @@
           <t>Underground</t>
         </is>
       </c>
-      <c r="D58" t="n">
-        <v>1</v>
-      </c>
-      <c r="E58" t="n">
-        <v>1</v>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G58" t="n">
-        <v>8</v>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -2703,19 +2757,25 @@
           <t>Homyno</t>
         </is>
       </c>
-      <c r="D62" t="n">
-        <v>1</v>
-      </c>
-      <c r="E62" t="n">
-        <v>1</v>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G62" t="n">
-        <v>8</v>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -2854,14 +2914,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E66" t="n">
-        <v>0</v>
-      </c>
-      <c r="F66" t="n">
-        <v>1</v>
-      </c>
-      <c r="G66" t="n">
-        <v>-5</v>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -2886,14 +2952,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E67" t="n">
-        <v>0</v>
-      </c>
-      <c r="F67" t="n">
-        <v>1</v>
-      </c>
-      <c r="G67" t="n">
-        <v>-5</v>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -2913,19 +2985,25 @@
           <t>Team Solid</t>
         </is>
       </c>
-      <c r="D68" t="n">
-        <v>1</v>
-      </c>
-      <c r="E68" t="n">
-        <v>1</v>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G68" t="n">
-        <v>8</v>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -3064,14 +3142,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E72" t="n">
-        <v>0</v>
-      </c>
-      <c r="F72" t="n">
-        <v>1</v>
-      </c>
-      <c r="G72" t="n">
-        <v>-5</v>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -3091,19 +3175,25 @@
           <t>The MongolZ</t>
         </is>
       </c>
-      <c r="D73" t="n">
-        <v>1</v>
-      </c>
-      <c r="E73" t="n">
-        <v>1</v>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G73" t="n">
-        <v>8</v>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -3204,14 +3294,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E76" t="n">
-        <v>0</v>
-      </c>
-      <c r="F76" t="n">
-        <v>1</v>
-      </c>
-      <c r="G76" t="n">
-        <v>-5</v>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -3231,19 +3327,25 @@
           <t>VP.Prodigy</t>
         </is>
       </c>
-      <c r="D77" t="n">
-        <v>1</v>
-      </c>
-      <c r="E77" t="n">
-        <v>1</v>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G77" t="n">
-        <v>8</v>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -3298,7 +3400,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Arcade</t>
+          <t>NomadS</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -3306,14 +3408,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E79" t="n">
-        <v>0</v>
-      </c>
-      <c r="F79" t="n">
-        <v>1</v>
-      </c>
-      <c r="G79" t="n">
-        <v>-5</v>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -3376,14 +3484,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E81" t="n">
-        <v>0</v>
-      </c>
-      <c r="F81" t="n">
-        <v>1</v>
-      </c>
-      <c r="G81" t="n">
-        <v>-5</v>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -3408,14 +3522,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E82" t="n">
-        <v>0</v>
-      </c>
-      <c r="F82" t="n">
-        <v>1</v>
-      </c>
-      <c r="G82" t="n">
-        <v>-5</v>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -3435,19 +3555,25 @@
           <t>TYLOO</t>
         </is>
       </c>
-      <c r="D83" t="n">
-        <v>1</v>
-      </c>
-      <c r="E83" t="n">
-        <v>1</v>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G83" t="n">
-        <v>8</v>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -3472,14 +3598,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E84" t="n">
-        <v>0</v>
-      </c>
-      <c r="F84" t="n">
-        <v>1</v>
-      </c>
-      <c r="G84" t="n">
-        <v>-5</v>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -3504,14 +3636,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E85" t="n">
-        <v>0</v>
-      </c>
-      <c r="F85" t="n">
-        <v>1</v>
-      </c>
-      <c r="G85" t="n">
-        <v>-5</v>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -3574,14 +3712,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E87" t="n">
-        <v>0</v>
-      </c>
-      <c r="F87" t="n">
-        <v>1</v>
-      </c>
-      <c r="G87" t="n">
-        <v>-5</v>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -3639,19 +3783,25 @@
           <t>MenaceGG</t>
         </is>
       </c>
-      <c r="D89" t="n">
-        <v>1</v>
-      </c>
-      <c r="E89" t="n">
-        <v>1</v>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G89" t="n">
-        <v>8</v>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -3676,14 +3826,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E90" t="n">
-        <v>0</v>
-      </c>
-      <c r="F90" t="n">
-        <v>1</v>
-      </c>
-      <c r="G90" t="n">
-        <v>-5</v>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -3708,14 +3864,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E91" t="n">
-        <v>0</v>
-      </c>
-      <c r="F91" t="n">
-        <v>1</v>
-      </c>
-      <c r="G91" t="n">
-        <v>-5</v>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -3735,19 +3897,25 @@
           <t>Aravt</t>
         </is>
       </c>
-      <c r="D92" t="n">
-        <v>1</v>
-      </c>
-      <c r="E92" t="n">
-        <v>1</v>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G92" t="n">
-        <v>8</v>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -3772,14 +3940,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E93" t="n">
-        <v>0</v>
-      </c>
-      <c r="F93" t="n">
-        <v>1</v>
-      </c>
-      <c r="G93" t="n">
-        <v>-5</v>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
@@ -3799,19 +3973,25 @@
           <t>True Rippers</t>
         </is>
       </c>
-      <c r="D94" t="n">
-        <v>1</v>
-      </c>
-      <c r="E94" t="n">
-        <v>1</v>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G94" t="n">
-        <v>8</v>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -3874,14 +4054,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E96" t="n">
-        <v>0</v>
-      </c>
-      <c r="F96" t="n">
-        <v>1</v>
-      </c>
-      <c r="G96" t="n">
-        <v>-5</v>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -3906,14 +4092,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E97" t="n">
-        <v>0</v>
-      </c>
-      <c r="F97" t="n">
-        <v>1</v>
-      </c>
-      <c r="G97" t="n">
-        <v>-5</v>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -3976,14 +4168,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E99" t="n">
-        <v>0</v>
-      </c>
-      <c r="F99" t="n">
-        <v>1</v>
-      </c>
-      <c r="G99" t="n">
-        <v>-5</v>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -4008,14 +4206,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E100" t="n">
-        <v>0</v>
-      </c>
-      <c r="F100" t="n">
-        <v>1</v>
-      </c>
-      <c r="G100" t="n">
-        <v>-5</v>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -4035,19 +4239,25 @@
           <t>Onyx Ravens</t>
         </is>
       </c>
-      <c r="D101" t="n">
-        <v>1</v>
-      </c>
-      <c r="E101" t="n">
-        <v>1</v>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G101" t="n">
-        <v>8</v>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -4072,14 +4282,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E102" t="n">
-        <v>0</v>
-      </c>
-      <c r="F102" t="n">
-        <v>1</v>
-      </c>
-      <c r="G102" t="n">
-        <v>-5</v>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
@@ -4104,14 +4320,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E103" t="n">
-        <v>0</v>
-      </c>
-      <c r="F103" t="n">
-        <v>1</v>
-      </c>
-      <c r="G103" t="n">
-        <v>-5</v>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
@@ -4359,19 +4581,25 @@
           <t>hoorai</t>
         </is>
       </c>
-      <c r="D110" t="n">
-        <v>1</v>
-      </c>
-      <c r="E110" t="n">
-        <v>1</v>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G110" t="n">
-        <v>8</v>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -4768,7 +4996,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>Venom</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -555,12 +555,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -570,7 +570,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>52</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -3030,17 +3030,17 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -2529,25 +2529,19 @@
           <t>Elevate</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="D56" t="n">
+        <v>8</v>
+      </c>
+      <c r="E56" t="n">
+        <v>4</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+      <c r="G56" t="n">
+        <v>51</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -2686,20 +2680,14 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
+      <c r="E60" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" t="n">
+        <v>4</v>
+      </c>
+      <c r="G60" t="n">
+        <v>35</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -522,17 +522,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1059,12 +1059,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>27</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1847,22 +1847,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2073,25 +2073,19 @@
           <t>Rebels</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="D44" t="n">
+        <v>3</v>
+      </c>
+      <c r="E44" t="n">
+        <v>3</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="G44" t="n">
+        <v>27</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -2306,20 +2300,14 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G50" t="n">
+        <v>-2</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -2529,19 +2517,25 @@
           <t>Elevate</t>
         </is>
       </c>
-      <c r="D56" t="n">
-        <v>8</v>
-      </c>
-      <c r="E56" t="n">
-        <v>4</v>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G56" t="n">
-        <v>51</v>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -2680,14 +2674,20 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E60" t="n">
-        <v>0</v>
-      </c>
-      <c r="F60" t="n">
-        <v>4</v>
-      </c>
-      <c r="G60" t="n">
-        <v>35</v>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -479,12 +479,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -494,7 +494,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>27</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -788,17 +788,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -2073,19 +2073,25 @@
           <t>Rebels</t>
         </is>
       </c>
-      <c r="D44" t="n">
-        <v>3</v>
-      </c>
-      <c r="E44" t="n">
-        <v>3</v>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G44" t="n">
-        <v>27</v>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -2300,14 +2306,20 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E50" t="n">
-        <v>0</v>
-      </c>
-      <c r="F50" t="n">
-        <v>2</v>
-      </c>
-      <c r="G50" t="n">
-        <v>-2</v>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -479,12 +479,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -494,7 +494,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -705,25 +705,19 @@
           <t>FaZe</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="G8" t="n">
+        <v>27</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1049,7 +1043,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1059,12 +1053,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1087,22 +1081,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2040,20 +2034,14 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-2</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -2080,17 +2068,17 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>17</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -520,20 +520,14 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>-2</t>
-        </is>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-12</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -705,19 +699,25 @@
           <t>FaZe</t>
         </is>
       </c>
-      <c r="D8" t="n">
-        <v>3</v>
-      </c>
-      <c r="E8" t="n">
-        <v>3</v>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>27</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1839,25 +1839,19 @@
           <t>Nexus</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D38" t="n">
+        <v>4</v>
+      </c>
+      <c r="E38" t="n">
+        <v>2</v>
+      </c>
+      <c r="F38" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="G38" t="n">
+        <v>23</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -2034,14 +2028,20 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E43" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" t="n">
-        <v>2</v>
-      </c>
-      <c r="G43" t="n">
-        <v>-2</v>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -520,14 +520,20 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>4</v>
-      </c>
-      <c r="G3" t="n">
-        <v>-12</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-12</t>
+        </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -775,25 +781,19 @@
           <t>ENCE</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>-2</t>
-        </is>
+      <c r="G10" t="n">
+        <v>15</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1839,19 +1839,25 @@
           <t>Nexus</t>
         </is>
       </c>
-      <c r="D38" t="n">
-        <v>4</v>
-      </c>
-      <c r="E38" t="n">
-        <v>2</v>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>23</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -2294,20 +2300,14 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>-2</t>
-        </is>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="n">
+        <v>4</v>
+      </c>
+      <c r="G50" t="n">
+        <v>-12</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -781,19 +781,25 @@
           <t>ENCE</t>
         </is>
       </c>
-      <c r="D10" t="n">
-        <v>3</v>
-      </c>
-      <c r="E10" t="n">
-        <v>2</v>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>15</v>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1081,12 +1087,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1096,7 +1102,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>42</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2300,14 +2306,20 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E50" t="n">
-        <v>0</v>
-      </c>
-      <c r="F50" t="n">
-        <v>4</v>
-      </c>
-      <c r="G50" t="n">
-        <v>-12</v>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>-12</t>
+        </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -1850,20 +1850,14 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>4</v>
+      </c>
+      <c r="G38" t="n">
+        <v>13</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -2073,25 +2067,19 @@
           <t>Rebels</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D44" t="n">
+        <v>5</v>
+      </c>
+      <c r="E44" t="n">
+        <v>2</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
+      <c r="G44" t="n">
+        <v>34</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -477,25 +477,19 @@
           <t>Vitality</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="D2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E2" t="n">
+        <v>7</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
+      <c r="G2" t="n">
+        <v>77</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -1052,20 +1046,14 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>4</v>
+      </c>
+      <c r="G17" t="n">
+        <v>22</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1850,14 +1838,20 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" t="n">
-        <v>4</v>
-      </c>
-      <c r="G38" t="n">
-        <v>13</v>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -2067,19 +2061,25 @@
           <t>Rebels</t>
         </is>
       </c>
-      <c r="D44" t="n">
-        <v>5</v>
-      </c>
-      <c r="E44" t="n">
-        <v>2</v>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G44" t="n">
-        <v>34</v>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -477,19 +477,25 @@
           <t>Vitality</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>7</v>
-      </c>
-      <c r="E2" t="n">
-        <v>7</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>77</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -1046,14 +1052,20 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>4</v>
-      </c>
-      <c r="G17" t="n">
-        <v>22</v>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1080,17 +1092,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1491,25 +1503,17 @@
           <t>Cloud9</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="D29" t="n">
+        <v>3</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" t="n">
+        <v>20</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -2063,22 +2067,22 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2099,25 +2103,17 @@
           <t>Eternal Fire</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="D45" t="n">
+        <v>2</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="n">
+        <v>2</v>
+      </c>
+      <c r="G45" t="n">
+        <v>7</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -1389,25 +1389,19 @@
           <t>iBUYPOWER</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="D26" t="n">
+        <v>3</v>
+      </c>
+      <c r="E26" t="n">
+        <v>3</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="G26" t="n">
+        <v>27</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1503,17 +1497,25 @@
           <t>Cloud9</t>
         </is>
       </c>
-      <c r="D29" t="n">
-        <v>3</v>
-      </c>
-      <c r="E29" t="n">
-        <v>2</v>
-      </c>
-      <c r="F29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" t="n">
-        <v>20</v>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -1766,20 +1768,14 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-2</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -2103,17 +2099,25 @@
           <t>Eternal Fire</t>
         </is>
       </c>
-      <c r="D45" t="n">
-        <v>2</v>
-      </c>
-      <c r="E45" t="n">
-        <v>0</v>
-      </c>
-      <c r="F45" t="n">
-        <v>2</v>
-      </c>
-      <c r="G45" t="n">
-        <v>7</v>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -629,25 +629,19 @@
           <t>Heroic</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="D6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="G6" t="n">
+        <v>27</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -707,22 +701,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1389,19 +1383,19 @@
           <t>iBUYPOWER</t>
         </is>
       </c>
-      <c r="D26" t="n">
-        <v>3</v>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="E26" t="n">
-        <v>3</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2</v>
       </c>
       <c r="G26" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1499,22 +1493,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>33</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1768,14 +1762,20 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" t="n">
-        <v>2</v>
-      </c>
-      <c r="G36" t="n">
-        <v>-2</v>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -629,19 +629,25 @@
           <t>Heroic</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>3</v>
-      </c>
-      <c r="E6" t="n">
-        <v>3</v>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>27</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -704,20 +710,14 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>4</v>
+      </c>
+      <c r="G8" t="n">
+        <v>15</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1307,25 +1307,19 @@
           <t>Copenhagen Flames</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="D24" t="n">
+        <v>5</v>
+      </c>
+      <c r="E24" t="n">
+        <v>5</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="G24" t="n">
+        <v>50</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1388,14 +1382,20 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" t="n">
-        <v>2</v>
-      </c>
-      <c r="G26" t="n">
-        <v>17</v>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1769,12 +1769,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2035,12 +2035,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2101,22 +2101,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -710,14 +710,20 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>4</v>
-      </c>
-      <c r="G8" t="n">
-        <v>15</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1307,19 +1313,25 @@
           <t>Copenhagen Flames</t>
         </is>
       </c>
-      <c r="D24" t="n">
-        <v>5</v>
-      </c>
-      <c r="E24" t="n">
-        <v>5</v>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>50</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1377,25 +1389,17 @@
           <t>iBUYPOWER</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
+      <c r="D26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>4</v>
+      </c>
+      <c r="G26" t="n">
+        <v>15</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -2099,25 +2103,17 @@
           <t>Eternal Fire</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
+      <c r="D45" t="n">
+        <v>6</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" t="n">
+        <v>4</v>
+      </c>
+      <c r="G45" t="n">
+        <v>32</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -629,25 +629,19 @@
           <t>Heroic</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="D6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+      <c r="G6" t="n">
+        <v>50</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -1389,17 +1383,25 @@
           <t>iBUYPOWER</t>
         </is>
       </c>
-      <c r="D26" t="n">
-        <v>4</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" t="n">
-        <v>4</v>
-      </c>
-      <c r="G26" t="n">
-        <v>15</v>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1500,20 +1502,14 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>4</v>
+      </c>
+      <c r="G29" t="n">
+        <v>23</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -2103,17 +2099,25 @@
           <t>Eternal Fire</t>
         </is>
       </c>
-      <c r="D45" t="n">
-        <v>6</v>
-      </c>
-      <c r="E45" t="n">
-        <v>1</v>
-      </c>
-      <c r="F45" t="n">
-        <v>4</v>
-      </c>
-      <c r="G45" t="n">
-        <v>32</v>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -629,19 +629,25 @@
           <t>Heroic</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>5</v>
-      </c>
-      <c r="E6" t="n">
-        <v>5</v>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>50</v>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -972,17 +978,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1200,17 +1206,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1309,22 +1315,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>53</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1502,14 +1508,20 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" t="n">
-        <v>4</v>
-      </c>
-      <c r="G29" t="n">
-        <v>23</v>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -2101,22 +2113,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>44</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2595,22 +2607,22 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2978,20 +2990,14 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="E68" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" t="n">
+        <v>2</v>
+      </c>
+      <c r="G68" t="n">
+        <v>-2</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -3165,12 +3171,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3180,7 +3186,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>27</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3429,25 +3435,19 @@
           <t>NAVI Junior</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="D80" t="n">
+        <v>3</v>
+      </c>
+      <c r="E80" t="n">
+        <v>3</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="G80" t="n">
+        <v>27</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -3963,22 +3963,22 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4229,22 +4229,22 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -971,25 +971,17 @@
           <t>Natus Vincere</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>-2</t>
-        </is>
+      <c r="D15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>3</v>
+      </c>
+      <c r="G15" t="n">
+        <v>9</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1199,25 +1191,17 @@
           <t>Virtus.pro</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>-2</t>
-        </is>
+      <c r="D21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>4</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-4</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -2990,14 +2974,20 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E68" t="n">
-        <v>0</v>
-      </c>
-      <c r="F68" t="n">
-        <v>2</v>
-      </c>
-      <c r="G68" t="n">
-        <v>-2</v>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -3436,10 +3426,10 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E80" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -3447,7 +3437,7 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -3966,20 +3956,14 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+      <c r="E94" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" t="n">
+        <v>3</v>
+      </c>
+      <c r="G94" t="n">
+        <v>10</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -972,16 +972,18 @@
         </is>
       </c>
       <c r="D15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E15" t="n">
         <v>3</v>
       </c>
-      <c r="E15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" t="n">
-        <v>3</v>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="G15" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1191,17 +1193,25 @@
           <t>Virtus.pro</t>
         </is>
       </c>
-      <c r="D21" t="n">
-        <v>2</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>4</v>
-      </c>
-      <c r="G21" t="n">
-        <v>-4</v>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-4</t>
+        </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -2601,12 +2611,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2971,12 +2981,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2986,7 +2996,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3425,19 +3435,25 @@
           <t>NAVI Junior</t>
         </is>
       </c>
-      <c r="D80" t="n">
-        <v>5</v>
-      </c>
-      <c r="E80" t="n">
-        <v>5</v>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G80" t="n">
-        <v>50</v>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -3960,10 +3976,10 @@
         <v>0</v>
       </c>
       <c r="F94" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G94" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -971,19 +971,25 @@
           <t>Natus Vincere</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>5</v>
-      </c>
-      <c r="E15" t="n">
-        <v>3</v>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>28</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -2981,17 +2987,17 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -3171,22 +3177,22 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>39</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3435,25 +3441,17 @@
           <t>NAVI Junior</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
+      <c r="D80" t="n">
+        <v>7</v>
+      </c>
+      <c r="E80" t="n">
+        <v>1</v>
+      </c>
+      <c r="F80" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" t="n">
+        <v>66</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -3972,14 +3970,20 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E94" t="n">
-        <v>0</v>
-      </c>
-      <c r="F94" t="n">
-        <v>5</v>
-      </c>
-      <c r="G94" t="n">
-        <v>0</v>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -4227,25 +4231,17 @@
           <t>Onyx Ravens</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+      <c r="D101" t="n">
+        <v>4</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" t="n">
+        <v>3</v>
+      </c>
+      <c r="G101" t="n">
+        <v>18</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -479,12 +479,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -494,7 +494,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -517,7 +517,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -527,12 +527,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -555,22 +555,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -631,22 +631,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -717,12 +717,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -755,12 +755,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -793,12 +793,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -831,12 +831,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -897,22 +897,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -935,17 +935,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -973,22 +973,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1021,12 +1021,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1059,12 +1059,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1097,12 +1097,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1277,12 +1277,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1325,12 +1325,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1401,12 +1401,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1439,12 +1439,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1477,12 +1477,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1541,25 +1541,19 @@
           <t>SK</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>8</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -1584,20 +1578,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-5</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -1657,22 +1645,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1705,12 +1693,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1743,12 +1731,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1771,7 +1759,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1781,12 +1769,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1819,12 +1807,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1847,7 +1835,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1857,12 +1845,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1895,12 +1883,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1933,12 +1921,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -1971,12 +1959,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2009,12 +1997,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2037,7 +2025,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2047,12 +2035,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2075,22 +2063,22 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2113,22 +2101,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2161,12 +2149,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2199,12 +2187,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2263,25 +2251,19 @@
           <t>M80</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D49" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" t="n">
+        <v>1</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>8</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -2303,7 +2285,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2313,12 +2295,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2341,12 +2323,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2356,7 +2338,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2377,25 +2359,19 @@
           <t>ECSTATIC</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D52" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" t="n">
+        <v>1</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>-4</t>
-        </is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>8</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -2415,25 +2391,19 @@
           <t>RED Canids</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D53" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>8</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -2531,22 +2501,22 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>51</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2579,12 +2549,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2607,7 +2577,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2617,12 +2587,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2683,22 +2653,22 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -2731,12 +2701,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -2759,12 +2729,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2774,7 +2744,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -2797,12 +2767,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2812,7 +2782,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -2876,20 +2846,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
+      <c r="E65" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" t="n">
+        <v>-5</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -2921,12 +2885,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -2959,12 +2923,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -2987,7 +2951,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2997,12 +2961,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3025,22 +2989,22 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3073,12 +3037,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3101,12 +3065,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3116,7 +3080,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3149,12 +3113,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3177,22 +3141,22 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3225,12 +3189,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3253,12 +3217,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3268,7 +3232,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3301,12 +3265,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -3329,12 +3293,12 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3344,7 +3308,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3367,12 +3331,12 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3382,7 +3346,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -3415,12 +3379,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3441,17 +3405,25 @@
           <t>NAVI Junior</t>
         </is>
       </c>
-      <c r="D80" t="n">
-        <v>7</v>
-      </c>
-      <c r="E80" t="n">
-        <v>1</v>
-      </c>
-      <c r="F80" t="n">
-        <v>1</v>
-      </c>
-      <c r="G80" t="n">
-        <v>66</v>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -3483,12 +3455,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -3521,12 +3493,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -3549,12 +3521,12 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3564,7 +3536,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -3597,12 +3569,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -3635,12 +3607,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -3663,12 +3635,12 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3678,7 +3650,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -3711,12 +3683,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -3742,20 +3714,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
+      <c r="E88" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" t="n">
+        <v>-5</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -3777,12 +3743,12 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3792,7 +3758,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -3825,12 +3791,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -3863,12 +3829,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -3891,12 +3857,12 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3906,7 +3872,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -3939,12 +3905,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -3967,7 +3933,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -3977,7 +3943,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -4005,12 +3971,12 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -4020,7 +3986,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4053,12 +4019,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4091,12 +4057,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -4119,12 +4085,12 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -4134,7 +4100,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -4167,12 +4133,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -4205,12 +4171,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -4231,17 +4197,25 @@
           <t>Onyx Ravens</t>
         </is>
       </c>
-      <c r="D101" t="n">
-        <v>4</v>
-      </c>
-      <c r="E101" t="n">
-        <v>0</v>
-      </c>
-      <c r="F101" t="n">
-        <v>3</v>
-      </c>
-      <c r="G101" t="n">
-        <v>18</v>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -4273,12 +4247,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -4311,12 +4285,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -4339,22 +4313,22 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -4377,22 +4351,22 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -4418,20 +4392,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
+      <c r="E106" t="n">
+        <v>0</v>
+      </c>
+      <c r="F106" t="n">
+        <v>1</v>
+      </c>
+      <c r="G106" t="n">
+        <v>-5</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -4463,12 +4431,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -4529,22 +4497,22 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -4567,12 +4535,12 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4582,7 +4550,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -4605,22 +4573,22 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -4643,22 +4611,22 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -4995,12 +4963,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -479,12 +479,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -494,7 +494,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -515,25 +515,19 @@
           <t>Astralis</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G3" t="n">
+        <v>8</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -631,12 +625,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -646,7 +640,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -707,12 +701,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -722,7 +716,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -755,12 +749,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -781,25 +775,19 @@
           <t>ENCE</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G10" t="n">
+        <v>8</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -831,12 +819,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1014,20 +1002,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-5</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1047,25 +1029,19 @@
           <t>G2</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G17" t="n">
+        <v>8</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1087,12 +1063,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1102,7 +1078,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1315,12 +1291,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1330,7 +1306,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1363,12 +1339,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1389,25 +1365,19 @@
           <t>iBUYPOWER</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G26" t="n">
+        <v>8</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1470,20 +1440,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-5</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -1505,12 +1469,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1520,7 +1484,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1541,19 +1505,25 @@
           <t>SK</t>
         </is>
       </c>
-      <c r="D30" t="n">
-        <v>1</v>
-      </c>
-      <c r="E30" t="n">
-        <v>1</v>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>8</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -1578,14 +1548,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E31" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" t="n">
-        <v>1</v>
-      </c>
-      <c r="G31" t="n">
-        <v>-5</v>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -1686,20 +1662,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-5</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -1757,25 +1727,19 @@
           <t>ShindeN</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G36" t="n">
+        <v>8</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -1835,12 +1799,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1850,7 +1814,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1921,12 +1885,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -1952,20 +1916,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-5</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -2023,25 +1981,19 @@
           <t>Permitta</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G43" t="n">
+        <v>8</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -2061,25 +2013,19 @@
           <t>Rebels</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G44" t="n">
+        <v>8</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -2099,25 +2045,19 @@
           <t>Eternal Fire</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G45" t="n">
+        <v>8</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -2142,20 +2082,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" t="n">
+        <v>-5</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -2180,20 +2114,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" t="n">
+        <v>-5</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -2251,19 +2179,25 @@
           <t>M80</t>
         </is>
       </c>
-      <c r="D49" t="n">
-        <v>1</v>
-      </c>
-      <c r="E49" t="n">
-        <v>1</v>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G49" t="n">
-        <v>8</v>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -2285,12 +2219,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2300,7 +2234,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2359,19 +2293,25 @@
           <t>ECSTATIC</t>
         </is>
       </c>
-      <c r="D52" t="n">
-        <v>1</v>
-      </c>
-      <c r="E52" t="n">
-        <v>1</v>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G52" t="n">
-        <v>8</v>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -2391,19 +2331,25 @@
           <t>RED Canids</t>
         </is>
       </c>
-      <c r="D53" t="n">
-        <v>1</v>
-      </c>
-      <c r="E53" t="n">
-        <v>1</v>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G53" t="n">
-        <v>8</v>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -2549,12 +2495,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2701,12 +2647,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -2846,14 +2792,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E65" t="n">
-        <v>0</v>
-      </c>
-      <c r="F65" t="n">
-        <v>1</v>
-      </c>
-      <c r="G65" t="n">
-        <v>-5</v>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -3037,12 +2989,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3189,12 +3141,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3714,14 +3666,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E88" t="n">
-        <v>0</v>
-      </c>
-      <c r="F88" t="n">
-        <v>1</v>
-      </c>
-      <c r="G88" t="n">
-        <v>-5</v>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -4392,14 +4350,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E106" t="n">
-        <v>0</v>
-      </c>
-      <c r="F106" t="n">
-        <v>1</v>
-      </c>
-      <c r="G106" t="n">
-        <v>-5</v>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -4416,7 +4380,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>LCDC</t>
+          <t>LDLC</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -4424,20 +4388,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E107" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" t="n">
+        <v>1</v>
+      </c>
+      <c r="G107" t="n">
+        <v>-5</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
@@ -4956,20 +4914,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E121" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" t="n">
+        <v>1</v>
+      </c>
+      <c r="G121" t="n">
+        <v>-5</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -515,19 +515,25 @@
           <t>Astralis</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>8</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -775,19 +781,25 @@
           <t>ENCE</t>
         </is>
       </c>
-      <c r="D10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1</v>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>8</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -961,12 +973,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -976,7 +988,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1002,14 +1014,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" t="n">
-        <v>-5</v>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1029,19 +1047,25 @@
           <t>G2</t>
         </is>
       </c>
-      <c r="D17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" t="n">
-        <v>1</v>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>8</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1177,12 +1201,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1192,7 +1216,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1215,12 +1239,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1230,7 +1254,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1251,25 +1275,19 @@
           <t>Entropiq</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G23" t="n">
+        <v>8</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1365,19 +1383,25 @@
           <t>iBUYPOWER</t>
         </is>
       </c>
-      <c r="D26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" t="n">
-        <v>1</v>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>8</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1409,12 +1433,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1440,14 +1464,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E28" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" t="n">
-        <v>-5</v>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -1662,14 +1692,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E34" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" t="n">
-        <v>1</v>
-      </c>
-      <c r="G34" t="n">
-        <v>-5</v>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -1701,12 +1737,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1727,19 +1763,25 @@
           <t>ShindeN</t>
         </is>
       </c>
-      <c r="D36" t="n">
-        <v>1</v>
-      </c>
-      <c r="E36" t="n">
-        <v>1</v>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>8</v>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -1764,20 +1806,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-5</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -1847,12 +1883,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1916,14 +1952,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E41" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" t="n">
-        <v>1</v>
-      </c>
-      <c r="G41" t="n">
-        <v>-5</v>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -1955,12 +1997,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -1981,19 +2023,25 @@
           <t>Permitta</t>
         </is>
       </c>
-      <c r="D43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E43" t="n">
-        <v>1</v>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G43" t="n">
-        <v>8</v>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -2013,19 +2061,25 @@
           <t>Rebels</t>
         </is>
       </c>
-      <c r="D44" t="n">
-        <v>1</v>
-      </c>
-      <c r="E44" t="n">
-        <v>1</v>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G44" t="n">
-        <v>8</v>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -2045,19 +2099,25 @@
           <t>Eternal Fire</t>
         </is>
       </c>
-      <c r="D45" t="n">
-        <v>1</v>
-      </c>
-      <c r="E45" t="n">
-        <v>1</v>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G45" t="n">
-        <v>8</v>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -2082,14 +2142,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E46" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" t="n">
-        <v>1</v>
-      </c>
-      <c r="G46" t="n">
-        <v>-5</v>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -2114,14 +2180,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E47" t="n">
-        <v>0</v>
-      </c>
-      <c r="F47" t="n">
-        <v>1</v>
-      </c>
-      <c r="G47" t="n">
-        <v>-5</v>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -2257,12 +2329,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2272,7 +2344,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2521,25 +2593,19 @@
           <t>Underground</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D58" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" t="n">
+        <v>1</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G58" t="n">
+        <v>8</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -2673,25 +2739,19 @@
           <t>Homyno</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D62" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" t="n">
+        <v>1</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G62" t="n">
+        <v>8</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -2713,12 +2773,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2728,7 +2788,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -2837,12 +2897,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -2875,12 +2935,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -2903,12 +2963,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2918,7 +2978,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3017,12 +3077,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3032,7 +3092,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3065,12 +3125,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3091,25 +3151,19 @@
           <t>The MongolZ</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D73" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" t="n">
+        <v>1</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G73" t="n">
+        <v>8</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -3169,12 +3223,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3184,7 +3238,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3217,12 +3271,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -3245,12 +3299,12 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3260,7 +3314,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3283,12 +3337,12 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3298,7 +3352,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -3324,20 +3378,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E79" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" t="n">
+        <v>-5</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -3359,12 +3407,12 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3374,7 +3422,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3407,12 +3455,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -3445,12 +3493,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -3471,25 +3519,19 @@
           <t>TYLOO</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D83" t="n">
+        <v>1</v>
+      </c>
+      <c r="E83" t="n">
+        <v>1</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G83" t="n">
+        <v>8</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -3521,12 +3563,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -3552,20 +3594,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E85" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" t="n">
+        <v>-5</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -3587,12 +3623,12 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3602,7 +3638,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -3635,12 +3671,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -3699,25 +3735,19 @@
           <t>MenaceGG</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D89" t="n">
+        <v>1</v>
+      </c>
+      <c r="E89" t="n">
+        <v>1</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G89" t="n">
+        <v>8</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -3742,20 +3772,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E90" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" t="n">
+        <v>-5</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -3780,20 +3804,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E91" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" t="n">
+        <v>1</v>
+      </c>
+      <c r="G91" t="n">
+        <v>-5</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -3815,12 +3833,12 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3830,7 +3848,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -3863,12 +3881,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -3889,25 +3907,19 @@
           <t>True Rippers</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D94" t="n">
+        <v>1</v>
+      </c>
+      <c r="E94" t="n">
+        <v>1</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G94" t="n">
+        <v>8</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -3929,12 +3941,12 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3944,7 +3956,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -3977,12 +3989,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4015,12 +4027,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -4043,12 +4055,12 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -4058,7 +4070,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -4084,20 +4096,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E99" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" t="n">
+        <v>1</v>
+      </c>
+      <c r="G99" t="n">
+        <v>-5</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -4122,20 +4128,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E100" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" t="n">
+        <v>1</v>
+      </c>
+      <c r="G100" t="n">
+        <v>-5</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -4157,12 +4157,12 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -4205,12 +4205,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -4236,20 +4236,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E103" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" t="n">
+        <v>1</v>
+      </c>
+      <c r="G103" t="n">
+        <v>-5</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
@@ -4388,14 +4382,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E107" t="n">
-        <v>0</v>
-      </c>
-      <c r="F107" t="n">
-        <v>1</v>
-      </c>
-      <c r="G107" t="n">
-        <v>-5</v>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
@@ -4491,25 +4491,19 @@
           <t>hoorai</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D110" t="n">
+        <v>1</v>
+      </c>
+      <c r="E110" t="n">
+        <v>1</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G110" t="n">
+        <v>8</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -4914,14 +4908,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E121" t="n">
-        <v>0</v>
-      </c>
-      <c r="F121" t="n">
-        <v>1</v>
-      </c>
-      <c r="G121" t="n">
-        <v>-5</v>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -895,25 +895,17 @@
           <t>Legacy</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="D13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>4</v>
+      </c>
+      <c r="G13" t="n">
+        <v>5</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1275,19 +1267,25 @@
           <t>Entropiq</t>
         </is>
       </c>
-      <c r="D23" t="n">
-        <v>1</v>
-      </c>
-      <c r="E23" t="n">
-        <v>1</v>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>8</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1649,25 +1647,19 @@
           <t>Iluminar</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="D33" t="n">
+        <v>7</v>
+      </c>
+      <c r="E33" t="n">
+        <v>6</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>66</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -1806,14 +1798,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E37" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" t="n">
-        <v>1</v>
-      </c>
-      <c r="G37" t="n">
-        <v>-5</v>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -2253,23 +2251,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" t="n">
+        <v>4</v>
+      </c>
+      <c r="G49" t="n">
+        <v>7</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -2403,25 +2395,17 @@
           <t>RED Canids</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="D53" t="n">
+        <v>5</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" t="n">
+        <v>4</v>
+      </c>
+      <c r="G53" t="n">
+        <v>24</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -2593,19 +2577,25 @@
           <t>Underground</t>
         </is>
       </c>
-      <c r="D58" t="n">
-        <v>1</v>
-      </c>
-      <c r="E58" t="n">
-        <v>1</v>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G58" t="n">
-        <v>8</v>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -2739,19 +2729,25 @@
           <t>Homyno</t>
         </is>
       </c>
-      <c r="D62" t="n">
-        <v>1</v>
-      </c>
-      <c r="E62" t="n">
-        <v>1</v>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G62" t="n">
-        <v>8</v>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -3151,19 +3147,25 @@
           <t>The MongolZ</t>
         </is>
       </c>
-      <c r="D73" t="n">
-        <v>1</v>
-      </c>
-      <c r="E73" t="n">
-        <v>1</v>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G73" t="n">
-        <v>8</v>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -3378,14 +3380,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E79" t="n">
-        <v>0</v>
-      </c>
-      <c r="F79" t="n">
-        <v>1</v>
-      </c>
-      <c r="G79" t="n">
-        <v>-5</v>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -3519,19 +3527,25 @@
           <t>TYLOO</t>
         </is>
       </c>
-      <c r="D83" t="n">
-        <v>1</v>
-      </c>
-      <c r="E83" t="n">
-        <v>1</v>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G83" t="n">
-        <v>8</v>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -3594,14 +3608,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E85" t="n">
-        <v>0</v>
-      </c>
-      <c r="F85" t="n">
-        <v>1</v>
-      </c>
-      <c r="G85" t="n">
-        <v>-5</v>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -3735,19 +3755,25 @@
           <t>MenaceGG</t>
         </is>
       </c>
-      <c r="D89" t="n">
-        <v>1</v>
-      </c>
-      <c r="E89" t="n">
-        <v>1</v>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G89" t="n">
-        <v>8</v>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -3772,14 +3798,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E90" t="n">
-        <v>0</v>
-      </c>
-      <c r="F90" t="n">
-        <v>1</v>
-      </c>
-      <c r="G90" t="n">
-        <v>-5</v>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -3804,14 +3836,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E91" t="n">
-        <v>0</v>
-      </c>
-      <c r="F91" t="n">
-        <v>1</v>
-      </c>
-      <c r="G91" t="n">
-        <v>-5</v>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -3907,19 +3945,25 @@
           <t>True Rippers</t>
         </is>
       </c>
-      <c r="D94" t="n">
-        <v>1</v>
-      </c>
-      <c r="E94" t="n">
-        <v>1</v>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G94" t="n">
-        <v>8</v>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -4096,14 +4140,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E99" t="n">
-        <v>0</v>
-      </c>
-      <c r="F99" t="n">
-        <v>1</v>
-      </c>
-      <c r="G99" t="n">
-        <v>-5</v>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -4128,14 +4178,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E100" t="n">
-        <v>0</v>
-      </c>
-      <c r="F100" t="n">
-        <v>1</v>
-      </c>
-      <c r="G100" t="n">
-        <v>-5</v>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -4236,14 +4292,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E103" t="n">
-        <v>0</v>
-      </c>
-      <c r="F103" t="n">
-        <v>1</v>
-      </c>
-      <c r="G103" t="n">
-        <v>-5</v>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
@@ -4263,25 +4325,17 @@
           <t>Bad News Eagles</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="D104" t="n">
+        <v>3</v>
+      </c>
+      <c r="E104" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" t="n">
+        <v>4</v>
+      </c>
+      <c r="G104" t="n">
+        <v>5</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
@@ -4301,25 +4355,17 @@
           <t>Wizards</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="D105" t="n">
+        <v>3</v>
+      </c>
+      <c r="E105" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" t="n">
+        <v>5</v>
+      </c>
+      <c r="G105" t="n">
+        <v>-1</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
@@ -4453,25 +4499,17 @@
           <t>Titan</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="D109" t="n">
+        <v>5</v>
+      </c>
+      <c r="E109" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" t="n">
+        <v>3</v>
+      </c>
+      <c r="G109" t="n">
+        <v>31</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -4491,19 +4529,25 @@
           <t>hoorai</t>
         </is>
       </c>
-      <c r="D110" t="n">
-        <v>1</v>
-      </c>
-      <c r="E110" t="n">
-        <v>1</v>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G110" t="n">
-        <v>8</v>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -4561,25 +4605,17 @@
           <t>Verdant</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="D112" t="n">
+        <v>7</v>
+      </c>
+      <c r="E112" t="n">
+        <v>6</v>
+      </c>
+      <c r="F112" t="n">
+        <v>3</v>
+      </c>
+      <c r="G112" t="n">
+        <v>56</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -553,25 +553,17 @@
           <t>Liquid</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="D4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" t="n">
+        <v>52</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -895,17 +887,25 @@
           <t>Legacy</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>3</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>4</v>
-      </c>
-      <c r="G13" t="n">
-        <v>5</v>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -925,25 +925,17 @@
           <t>MIBR</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="D14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>5</v>
+      </c>
+      <c r="G14" t="n">
+        <v>8</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1533,25 +1525,17 @@
           <t>SK</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="D30" t="n">
+        <v>3</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>4</v>
+      </c>
+      <c r="G30" t="n">
+        <v>5</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -1647,19 +1631,25 @@
           <t>Iluminar</t>
         </is>
       </c>
-      <c r="D33" t="n">
-        <v>7</v>
-      </c>
-      <c r="E33" t="n">
-        <v>6</v>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>66</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -2254,14 +2244,20 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E49" t="n">
-        <v>0</v>
-      </c>
-      <c r="F49" t="n">
-        <v>4</v>
-      </c>
-      <c r="G49" t="n">
-        <v>7</v>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -2357,25 +2353,17 @@
           <t>ECSTATIC</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="D52" t="n">
+        <v>2</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="n">
+        <v>4</v>
+      </c>
+      <c r="G52" t="n">
+        <v>-4</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -2395,17 +2383,25 @@
           <t>RED Canids</t>
         </is>
       </c>
-      <c r="D53" t="n">
-        <v>5</v>
-      </c>
-      <c r="E53" t="n">
-        <v>0</v>
-      </c>
-      <c r="F53" t="n">
-        <v>4</v>
-      </c>
-      <c r="G53" t="n">
-        <v>24</v>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -2501,25 +2497,17 @@
           <t>Elevate</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="D56" t="n">
+        <v>8</v>
+      </c>
+      <c r="E56" t="n">
+        <v>4</v>
+      </c>
+      <c r="F56" t="n">
+        <v>4</v>
+      </c>
+      <c r="G56" t="n">
+        <v>51</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -2653,25 +2641,17 @@
           <t>Orbit</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="D60" t="n">
+        <v>6</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" t="n">
+        <v>4</v>
+      </c>
+      <c r="G60" t="n">
+        <v>35</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -2995,25 +2975,17 @@
           <t>Bounty Hunters</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="D69" t="n">
+        <v>5</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" t="n">
+        <v>2</v>
+      </c>
+      <c r="G69" t="n">
+        <v>40</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -4325,17 +4297,25 @@
           <t>Bad News Eagles</t>
         </is>
       </c>
-      <c r="D104" t="n">
-        <v>3</v>
-      </c>
-      <c r="E104" t="n">
-        <v>0</v>
-      </c>
-      <c r="F104" t="n">
-        <v>4</v>
-      </c>
-      <c r="G104" t="n">
-        <v>5</v>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
@@ -4355,17 +4335,25 @@
           <t>Wizards</t>
         </is>
       </c>
-      <c r="D105" t="n">
-        <v>3</v>
-      </c>
-      <c r="E105" t="n">
-        <v>0</v>
-      </c>
-      <c r="F105" t="n">
-        <v>5</v>
-      </c>
-      <c r="G105" t="n">
-        <v>-1</v>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
@@ -4499,17 +4487,25 @@
           <t>Titan</t>
         </is>
       </c>
-      <c r="D109" t="n">
-        <v>5</v>
-      </c>
-      <c r="E109" t="n">
-        <v>0</v>
-      </c>
-      <c r="F109" t="n">
-        <v>3</v>
-      </c>
-      <c r="G109" t="n">
-        <v>31</v>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -4567,25 +4563,17 @@
           <t>GODSENT</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="D111" t="n">
+        <v>3</v>
+      </c>
+      <c r="E111" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" t="n">
+        <v>5</v>
+      </c>
+      <c r="G111" t="n">
+        <v>0</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -4605,17 +4593,25 @@
           <t>Verdant</t>
         </is>
       </c>
-      <c r="D112" t="n">
-        <v>7</v>
-      </c>
-      <c r="E112" t="n">
-        <v>6</v>
-      </c>
-      <c r="F112" t="n">
-        <v>3</v>
-      </c>
-      <c r="G112" t="n">
-        <v>56</v>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -477,25 +477,19 @@
           <t>Vitality</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="D2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E2" t="n">
+        <v>7</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="G2" t="n">
+        <v>77</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -520,20 +514,14 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-12</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -553,17 +541,25 @@
           <t>Liquid</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>7</v>
-      </c>
-      <c r="E4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G4" t="n">
-        <v>52</v>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -773,25 +769,17 @@
           <t>ENCE</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="D10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>4</v>
+      </c>
+      <c r="G10" t="n">
+        <v>5</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -925,17 +913,25 @@
           <t>MIBR</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>4</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>5</v>
-      </c>
-      <c r="G14" t="n">
-        <v>8</v>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1031,25 +1027,17 @@
           <t>G2</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="D17" t="n">
+        <v>5</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>4</v>
+      </c>
+      <c r="G17" t="n">
+        <v>22</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1069,25 +1057,17 @@
           <t>OG</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="D18" t="n">
+        <v>6</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>4</v>
+      </c>
+      <c r="G18" t="n">
+        <v>32</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1525,17 +1505,25 @@
           <t>SK</t>
         </is>
       </c>
-      <c r="D30" t="n">
-        <v>3</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" t="n">
-        <v>4</v>
-      </c>
-      <c r="G30" t="n">
-        <v>5</v>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -1821,25 +1809,17 @@
           <t>Nexus</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="D38" t="n">
+        <v>3</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>4</v>
+      </c>
+      <c r="G38" t="n">
+        <v>5</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -2049,25 +2029,17 @@
           <t>Rebels</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="D44" t="n">
+        <v>7</v>
+      </c>
+      <c r="E44" t="n">
+        <v>4</v>
+      </c>
+      <c r="F44" t="n">
+        <v>2</v>
+      </c>
+      <c r="G44" t="n">
+        <v>55</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -2282,20 +2254,14 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="n">
+        <v>4</v>
+      </c>
+      <c r="G50" t="n">
+        <v>-12</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -2353,17 +2319,25 @@
           <t>ECSTATIC</t>
         </is>
       </c>
-      <c r="D52" t="n">
-        <v>2</v>
-      </c>
-      <c r="E52" t="n">
-        <v>0</v>
-      </c>
-      <c r="F52" t="n">
-        <v>4</v>
-      </c>
-      <c r="G52" t="n">
-        <v>-4</v>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-4</t>
+        </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -2497,17 +2471,25 @@
           <t>Elevate</t>
         </is>
       </c>
-      <c r="D56" t="n">
-        <v>8</v>
-      </c>
-      <c r="E56" t="n">
-        <v>4</v>
-      </c>
-      <c r="F56" t="n">
-        <v>4</v>
-      </c>
-      <c r="G56" t="n">
-        <v>51</v>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -2641,17 +2623,25 @@
           <t>Orbit</t>
         </is>
       </c>
-      <c r="D60" t="n">
-        <v>6</v>
-      </c>
-      <c r="E60" t="n">
-        <v>0</v>
-      </c>
-      <c r="F60" t="n">
-        <v>4</v>
-      </c>
-      <c r="G60" t="n">
-        <v>35</v>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -2975,17 +2965,25 @@
           <t>Bounty Hunters</t>
         </is>
       </c>
-      <c r="D69" t="n">
-        <v>5</v>
-      </c>
-      <c r="E69" t="n">
-        <v>0</v>
-      </c>
-      <c r="F69" t="n">
-        <v>2</v>
-      </c>
-      <c r="G69" t="n">
-        <v>40</v>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -4563,17 +4561,25 @@
           <t>GODSENT</t>
         </is>
       </c>
-      <c r="D111" t="n">
-        <v>3</v>
-      </c>
-      <c r="E111" t="n">
-        <v>0</v>
-      </c>
-      <c r="F111" t="n">
-        <v>5</v>
-      </c>
-      <c r="G111" t="n">
-        <v>0</v>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -477,19 +477,25 @@
           <t>Vitality</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>7</v>
-      </c>
-      <c r="E2" t="n">
-        <v>7</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>77</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -514,14 +520,20 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>4</v>
-      </c>
-      <c r="G3" t="n">
-        <v>-12</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-12</t>
+        </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -619,22 +631,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>62</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -695,22 +707,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -769,17 +781,25 @@
           <t>ENCE</t>
         </is>
       </c>
-      <c r="D10" t="n">
-        <v>3</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>4</v>
-      </c>
-      <c r="G10" t="n">
-        <v>5</v>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1027,17 +1047,25 @@
           <t>G2</t>
         </is>
       </c>
-      <c r="D17" t="n">
-        <v>5</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>4</v>
-      </c>
-      <c r="G17" t="n">
-        <v>22</v>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1057,17 +1085,25 @@
           <t>OG</t>
         </is>
       </c>
-      <c r="D18" t="n">
-        <v>6</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>4</v>
-      </c>
-      <c r="G18" t="n">
-        <v>32</v>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1279,22 +1315,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>46</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1355,22 +1391,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1469,22 +1505,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>23</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1740,17 +1776,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1809,17 +1845,25 @@
           <t>Nexus</t>
         </is>
       </c>
-      <c r="D38" t="n">
-        <v>3</v>
-      </c>
-      <c r="E38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" t="n">
-        <v>4</v>
-      </c>
-      <c r="G38" t="n">
-        <v>5</v>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -1993,22 +2037,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2029,17 +2073,25 @@
           <t>Rebels</t>
         </is>
       </c>
-      <c r="D44" t="n">
-        <v>7</v>
-      </c>
-      <c r="E44" t="n">
-        <v>4</v>
-      </c>
-      <c r="F44" t="n">
-        <v>2</v>
-      </c>
-      <c r="G44" t="n">
-        <v>55</v>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -2061,22 +2113,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>42</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2254,14 +2306,20 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E50" t="n">
-        <v>0</v>
-      </c>
-      <c r="F50" t="n">
-        <v>4</v>
-      </c>
-      <c r="G50" t="n">
-        <v>-12</v>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>-12</t>
+        </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -971,25 +971,17 @@
           <t>Natus Vincere</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="D15" t="n">
+        <v>7</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>5</v>
+      </c>
+      <c r="G15" t="n">
+        <v>35</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1199,25 +1191,17 @@
           <t>Virtus.pro</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="D21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>4</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-4</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -2605,25 +2589,17 @@
           <t>Underground</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="D58" t="n">
+        <v>2</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" t="n">
+        <v>4</v>
+      </c>
+      <c r="G58" t="n">
+        <v>-3</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -2985,25 +2961,17 @@
           <t>Team Solid</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="D68" t="n">
+        <v>4</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" t="n">
+        <v>4</v>
+      </c>
+      <c r="G68" t="n">
+        <v>15</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -3175,25 +3143,17 @@
           <t>The MongolZ</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="D73" t="n">
+        <v>8</v>
+      </c>
+      <c r="E73" t="n">
+        <v>1</v>
+      </c>
+      <c r="F73" t="n">
+        <v>4</v>
+      </c>
+      <c r="G73" t="n">
+        <v>53</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -3441,25 +3401,17 @@
           <t>NAVI Junior</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="D80" t="n">
+        <v>5</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" t="n">
+        <v>2</v>
+      </c>
+      <c r="G80" t="n">
+        <v>40</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -3973,25 +3925,17 @@
           <t>True Rippers</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="D94" t="n">
+        <v>3</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" t="n">
+        <v>5</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -4239,25 +4183,17 @@
           <t>Onyx Ravens</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="D101" t="n">
+        <v>7</v>
+      </c>
+      <c r="E101" t="n">
+        <v>4</v>
+      </c>
+      <c r="F101" t="n">
+        <v>2</v>
+      </c>
+      <c r="G101" t="n">
+        <v>53</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -971,17 +971,25 @@
           <t>Natus Vincere</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>7</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>5</v>
-      </c>
-      <c r="G15" t="n">
-        <v>35</v>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1191,17 +1199,25 @@
           <t>Virtus.pro</t>
         </is>
       </c>
-      <c r="D21" t="n">
-        <v>2</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>4</v>
-      </c>
-      <c r="G21" t="n">
-        <v>-4</v>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-4</t>
+        </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1264,20 +1280,14 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>4</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-12</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -2589,17 +2599,25 @@
           <t>Underground</t>
         </is>
       </c>
-      <c r="D58" t="n">
-        <v>2</v>
-      </c>
-      <c r="E58" t="n">
-        <v>0</v>
-      </c>
-      <c r="F58" t="n">
-        <v>4</v>
-      </c>
-      <c r="G58" t="n">
-        <v>-3</v>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>-3</t>
+        </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -2776,20 +2794,14 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" t="n">
+        <v>2</v>
+      </c>
+      <c r="G63" t="n">
+        <v>-2</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -2961,17 +2973,25 @@
           <t>Team Solid</t>
         </is>
       </c>
-      <c r="D68" t="n">
-        <v>4</v>
-      </c>
-      <c r="E68" t="n">
-        <v>0</v>
-      </c>
-      <c r="F68" t="n">
-        <v>4</v>
-      </c>
-      <c r="G68" t="n">
-        <v>15</v>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -3067,25 +3087,17 @@
           <t>Spirit Academy</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="D71" t="n">
+        <v>4</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" t="n">
+        <v>5</v>
+      </c>
+      <c r="G71" t="n">
+        <v>8</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -3143,17 +3155,25 @@
           <t>The MongolZ</t>
         </is>
       </c>
-      <c r="D73" t="n">
-        <v>8</v>
-      </c>
-      <c r="E73" t="n">
-        <v>1</v>
-      </c>
-      <c r="F73" t="n">
-        <v>4</v>
-      </c>
-      <c r="G73" t="n">
-        <v>53</v>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -3211,25 +3231,17 @@
           <t>PARIVISION</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="D75" t="n">
+        <v>7</v>
+      </c>
+      <c r="E75" t="n">
+        <v>4</v>
+      </c>
+      <c r="F75" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" t="n">
+        <v>60</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -3401,17 +3413,25 @@
           <t>NAVI Junior</t>
         </is>
       </c>
-      <c r="D80" t="n">
-        <v>5</v>
-      </c>
-      <c r="E80" t="n">
-        <v>0</v>
-      </c>
-      <c r="F80" t="n">
-        <v>2</v>
-      </c>
-      <c r="G80" t="n">
-        <v>40</v>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -3621,25 +3641,17 @@
           <t>Chinggis Warrios</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="D86" t="n">
+        <v>6</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" t="n">
+        <v>5</v>
+      </c>
+      <c r="G86" t="n">
+        <v>26</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -3735,25 +3747,17 @@
           <t>MenaceGG</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="D89" t="n">
+        <v>4</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" t="n">
+        <v>4</v>
+      </c>
+      <c r="G89" t="n">
+        <v>13</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -3925,17 +3929,25 @@
           <t>True Rippers</t>
         </is>
       </c>
-      <c r="D94" t="n">
-        <v>3</v>
-      </c>
-      <c r="E94" t="n">
-        <v>0</v>
-      </c>
-      <c r="F94" t="n">
-        <v>5</v>
-      </c>
-      <c r="G94" t="n">
-        <v>0</v>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -4069,25 +4081,17 @@
           <t>Nemiga</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="D98" t="n">
+        <v>7</v>
+      </c>
+      <c r="E98" t="n">
+        <v>4</v>
+      </c>
+      <c r="F98" t="n">
+        <v>3</v>
+      </c>
+      <c r="G98" t="n">
+        <v>48</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -4183,17 +4187,25 @@
           <t>Onyx Ravens</t>
         </is>
       </c>
-      <c r="D101" t="n">
-        <v>7</v>
-      </c>
-      <c r="E101" t="n">
-        <v>4</v>
-      </c>
-      <c r="F101" t="n">
-        <v>2</v>
-      </c>
-      <c r="G101" t="n">
-        <v>53</v>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -4517,25 +4529,17 @@
           <t>hoorai</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="D110" t="n">
+        <v>5</v>
+      </c>
+      <c r="E110" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" t="n">
+        <v>2</v>
+      </c>
+      <c r="G110" t="n">
+        <v>40</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -1280,14 +1280,20 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>4</v>
-      </c>
-      <c r="G23" t="n">
-        <v>-12</v>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-12</t>
+        </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -2794,14 +2800,20 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E63" t="n">
-        <v>0</v>
-      </c>
-      <c r="F63" t="n">
-        <v>2</v>
-      </c>
-      <c r="G63" t="n">
-        <v>-2</v>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -3087,17 +3099,25 @@
           <t>Spirit Academy</t>
         </is>
       </c>
-      <c r="D71" t="n">
-        <v>4</v>
-      </c>
-      <c r="E71" t="n">
-        <v>0</v>
-      </c>
-      <c r="F71" t="n">
-        <v>5</v>
-      </c>
-      <c r="G71" t="n">
-        <v>8</v>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -3231,17 +3251,25 @@
           <t>PARIVISION</t>
         </is>
       </c>
-      <c r="D75" t="n">
-        <v>7</v>
-      </c>
-      <c r="E75" t="n">
-        <v>4</v>
-      </c>
-      <c r="F75" t="n">
-        <v>1</v>
-      </c>
-      <c r="G75" t="n">
-        <v>60</v>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -3641,17 +3669,25 @@
           <t>Chinggis Warrios</t>
         </is>
       </c>
-      <c r="D86" t="n">
-        <v>6</v>
-      </c>
-      <c r="E86" t="n">
-        <v>0</v>
-      </c>
-      <c r="F86" t="n">
-        <v>5</v>
-      </c>
-      <c r="G86" t="n">
-        <v>26</v>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -3747,17 +3783,25 @@
           <t>MenaceGG</t>
         </is>
       </c>
-      <c r="D89" t="n">
-        <v>4</v>
-      </c>
-      <c r="E89" t="n">
-        <v>0</v>
-      </c>
-      <c r="F89" t="n">
-        <v>4</v>
-      </c>
-      <c r="G89" t="n">
-        <v>13</v>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -4081,17 +4125,25 @@
           <t>Nemiga</t>
         </is>
       </c>
-      <c r="D98" t="n">
-        <v>7</v>
-      </c>
-      <c r="E98" t="n">
-        <v>4</v>
-      </c>
-      <c r="F98" t="n">
-        <v>3</v>
-      </c>
-      <c r="G98" t="n">
-        <v>48</v>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -4529,17 +4581,25 @@
           <t>hoorai</t>
         </is>
       </c>
-      <c r="D110" t="n">
-        <v>5</v>
-      </c>
-      <c r="E110" t="n">
-        <v>0</v>
-      </c>
-      <c r="F110" t="n">
-        <v>2</v>
-      </c>
-      <c r="G110" t="n">
-        <v>40</v>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -1237,25 +1237,17 @@
           <t>Spirit</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="D22" t="n">
+        <v>7</v>
+      </c>
+      <c r="E22" t="n">
+        <v>4</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" t="n">
+        <v>60</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -2339,25 +2331,17 @@
           <t>BESTIA</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="D51" t="n">
+        <v>5</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="n">
+        <v>4</v>
+      </c>
+      <c r="G51" t="n">
+        <v>22</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -2757,25 +2741,17 @@
           <t>Homyno</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="D62" t="n">
+        <v>4</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" t="n">
+        <v>4</v>
+      </c>
+      <c r="G62" t="n">
+        <v>15</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -3327,25 +3303,17 @@
           <t>VP.Prodigy</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="D77" t="n">
+        <v>2</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" t="n">
+        <v>4</v>
+      </c>
+      <c r="G77" t="n">
+        <v>-3</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -3365,25 +3333,17 @@
           <t>TALON</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="D78" t="n">
+        <v>8</v>
+      </c>
+      <c r="E78" t="n">
+        <v>4</v>
+      </c>
+      <c r="F78" t="n">
+        <v>4</v>
+      </c>
+      <c r="G78" t="n">
+        <v>53</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -3555,25 +3515,17 @@
           <t>TYLOO</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="D83" t="n">
+        <v>6</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" t="n">
+        <v>5</v>
+      </c>
+      <c r="G83" t="n">
+        <v>30</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -3897,25 +3849,17 @@
           <t>Aravt</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="D92" t="n">
+        <v>3</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" t="n">
+        <v>4</v>
+      </c>
+      <c r="G92" t="n">
+        <v>5</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -4011,25 +3955,17 @@
           <t>Alliance</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="D95" t="n">
+        <v>4</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" t="n">
+        <v>5</v>
+      </c>
+      <c r="G95" t="n">
+        <v>10</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -862,20 +862,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-15</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -971,25 +965,17 @@
           <t>Natus Vincere</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
+      <c r="D15" t="n">
+        <v>11</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" t="n">
+        <v>7</v>
+      </c>
+      <c r="G15" t="n">
+        <v>58</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1085,25 +1071,17 @@
           <t>OG</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
+      <c r="D18" t="n">
+        <v>8</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>6</v>
+      </c>
+      <c r="G18" t="n">
+        <v>39</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1128,10 +1106,8 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E19" t="n">
+        <v>0</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1237,17 +1213,25 @@
           <t>Spirit</t>
         </is>
       </c>
-      <c r="D22" t="n">
-        <v>7</v>
-      </c>
-      <c r="E22" t="n">
-        <v>4</v>
-      </c>
-      <c r="F22" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" t="n">
-        <v>60</v>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1305,25 +1289,19 @@
           <t>Copenhagen Flames</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D24" t="n">
+        <v>11</v>
+      </c>
+      <c r="E24" t="n">
+        <v>4</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
+      <c r="G24" t="n">
+        <v>84</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -2331,17 +2309,25 @@
           <t>BESTIA</t>
         </is>
       </c>
-      <c r="D51" t="n">
-        <v>5</v>
-      </c>
-      <c r="E51" t="n">
-        <v>0</v>
-      </c>
-      <c r="F51" t="n">
-        <v>4</v>
-      </c>
-      <c r="G51" t="n">
-        <v>22</v>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -2399,25 +2385,17 @@
           <t>RED Canids</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
+      <c r="D53" t="n">
+        <v>6</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" t="n">
+        <v>6</v>
+      </c>
+      <c r="G53" t="n">
+        <v>22</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -2665,25 +2643,17 @@
           <t>Orbit</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
+      <c r="D60" t="n">
+        <v>7</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" t="n">
+        <v>6</v>
+      </c>
+      <c r="G60" t="n">
+        <v>33</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -2741,17 +2711,25 @@
           <t>Homyno</t>
         </is>
       </c>
-      <c r="D62" t="n">
-        <v>4</v>
-      </c>
-      <c r="E62" t="n">
-        <v>0</v>
-      </c>
-      <c r="F62" t="n">
-        <v>4</v>
-      </c>
-      <c r="G62" t="n">
-        <v>15</v>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -3303,17 +3281,25 @@
           <t>VP.Prodigy</t>
         </is>
       </c>
-      <c r="D77" t="n">
-        <v>2</v>
-      </c>
-      <c r="E77" t="n">
-        <v>0</v>
-      </c>
-      <c r="F77" t="n">
-        <v>4</v>
-      </c>
-      <c r="G77" t="n">
-        <v>-3</v>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>-3</t>
+        </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -3333,17 +3319,25 @@
           <t>TALON</t>
         </is>
       </c>
-      <c r="D78" t="n">
-        <v>8</v>
-      </c>
-      <c r="E78" t="n">
-        <v>4</v>
-      </c>
-      <c r="F78" t="n">
-        <v>4</v>
-      </c>
-      <c r="G78" t="n">
-        <v>53</v>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -3516,16 +3510,16 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E83" t="n">
         <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G83" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -3626,20 +3620,14 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
+      <c r="E86" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" t="n">
+        <v>7</v>
+      </c>
+      <c r="G86" t="n">
+        <v>16</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -3849,17 +3837,25 @@
           <t>Aravt</t>
         </is>
       </c>
-      <c r="D92" t="n">
-        <v>3</v>
-      </c>
-      <c r="E92" t="n">
-        <v>0</v>
-      </c>
-      <c r="F92" t="n">
-        <v>4</v>
-      </c>
-      <c r="G92" t="n">
-        <v>5</v>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -3955,17 +3951,25 @@
           <t>Alliance</t>
         </is>
       </c>
-      <c r="D95" t="n">
-        <v>4</v>
-      </c>
-      <c r="E95" t="n">
-        <v>0</v>
-      </c>
-      <c r="F95" t="n">
-        <v>5</v>
-      </c>
-      <c r="G95" t="n">
-        <v>10</v>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -862,14 +862,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>3</v>
-      </c>
-      <c r="G12" t="n">
-        <v>-15</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-15</t>
+        </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -965,17 +971,25 @@
           <t>Natus Vincere</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>11</v>
-      </c>
-      <c r="E15" t="n">
-        <v>2</v>
-      </c>
-      <c r="F15" t="n">
-        <v>7</v>
-      </c>
-      <c r="G15" t="n">
-        <v>58</v>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1071,17 +1085,25 @@
           <t>OG</t>
         </is>
       </c>
-      <c r="D18" t="n">
-        <v>8</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>6</v>
-      </c>
-      <c r="G18" t="n">
-        <v>39</v>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1106,8 +1128,10 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E19" t="n">
-        <v>0</v>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1289,19 +1313,25 @@
           <t>Copenhagen Flames</t>
         </is>
       </c>
-      <c r="D24" t="n">
-        <v>11</v>
-      </c>
-      <c r="E24" t="n">
-        <v>4</v>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>84</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -2045,22 +2075,22 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2081,25 +2111,17 @@
           <t>Eternal Fire</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
+      <c r="D45" t="n">
+        <v>12</v>
+      </c>
+      <c r="E45" t="n">
+        <v>3</v>
+      </c>
+      <c r="F45" t="n">
+        <v>6</v>
+      </c>
+      <c r="G45" t="n">
+        <v>74</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -2385,17 +2407,25 @@
           <t>RED Canids</t>
         </is>
       </c>
-      <c r="D53" t="n">
-        <v>6</v>
-      </c>
-      <c r="E53" t="n">
-        <v>0</v>
-      </c>
-      <c r="F53" t="n">
-        <v>6</v>
-      </c>
-      <c r="G53" t="n">
-        <v>22</v>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -2643,17 +2673,25 @@
           <t>Orbit</t>
         </is>
       </c>
-      <c r="D60" t="n">
-        <v>7</v>
-      </c>
-      <c r="E60" t="n">
-        <v>0</v>
-      </c>
-      <c r="F60" t="n">
-        <v>6</v>
-      </c>
-      <c r="G60" t="n">
-        <v>33</v>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -2979,7 +3017,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2989,12 +3027,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3509,17 +3547,25 @@
           <t>TYLOO</t>
         </is>
       </c>
-      <c r="D83" t="n">
-        <v>9</v>
-      </c>
-      <c r="E83" t="n">
-        <v>0</v>
-      </c>
-      <c r="F83" t="n">
-        <v>8</v>
-      </c>
-      <c r="G83" t="n">
-        <v>42</v>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -3620,14 +3666,20 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E86" t="n">
-        <v>0</v>
-      </c>
-      <c r="F86" t="n">
-        <v>7</v>
-      </c>
-      <c r="G86" t="n">
-        <v>16</v>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -2111,17 +2111,25 @@
           <t>Eternal Fire</t>
         </is>
       </c>
-      <c r="D45" t="n">
-        <v>12</v>
-      </c>
-      <c r="E45" t="n">
-        <v>3</v>
-      </c>
-      <c r="F45" t="n">
-        <v>6</v>
-      </c>
-      <c r="G45" t="n">
-        <v>74</v>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -2331,25 +2339,17 @@
           <t>BESTIA</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="D51" t="n">
+        <v>9</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="n">
+        <v>8</v>
+      </c>
+      <c r="G51" t="n">
+        <v>40</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -1503,25 +1503,17 @@
           <t>Cloud9</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2</v>
+      </c>
+      <c r="F29" t="n">
+        <v>7</v>
+      </c>
+      <c r="G29" t="n">
+        <v>50</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -2339,17 +2331,25 @@
           <t>BESTIA</t>
         </is>
       </c>
-      <c r="D51" t="n">
-        <v>9</v>
-      </c>
-      <c r="E51" t="n">
-        <v>0</v>
-      </c>
-      <c r="F51" t="n">
-        <v>8</v>
-      </c>
-      <c r="G51" t="n">
-        <v>40</v>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -4117,25 +4117,17 @@
           <t>Nemiga</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
+      <c r="D98" t="n">
+        <v>11</v>
+      </c>
+      <c r="E98" t="n">
+        <v>2</v>
+      </c>
+      <c r="F98" t="n">
+        <v>4</v>
+      </c>
+      <c r="G98" t="n">
+        <v>85</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -1503,17 +1503,25 @@
           <t>Cloud9</t>
         </is>
       </c>
-      <c r="D29" t="n">
-        <v>10</v>
-      </c>
-      <c r="E29" t="n">
-        <v>2</v>
-      </c>
-      <c r="F29" t="n">
-        <v>7</v>
-      </c>
-      <c r="G29" t="n">
-        <v>50</v>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -2521,25 +2529,17 @@
           <t>Elevate</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
+      <c r="D56" t="n">
+        <v>12</v>
+      </c>
+      <c r="E56" t="n">
+        <v>2</v>
+      </c>
+      <c r="F56" t="n">
+        <v>6</v>
+      </c>
+      <c r="G56" t="n">
+        <v>83</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -4117,17 +4117,25 @@
           <t>Nemiga</t>
         </is>
       </c>
-      <c r="D98" t="n">
-        <v>11</v>
-      </c>
-      <c r="E98" t="n">
-        <v>2</v>
-      </c>
-      <c r="F98" t="n">
-        <v>4</v>
-      </c>
-      <c r="G98" t="n">
-        <v>85</v>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -4527,25 +4535,17 @@
           <t>Titan</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
+      <c r="D109" t="n">
+        <v>9</v>
+      </c>
+      <c r="E109" t="n">
+        <v>2</v>
+      </c>
+      <c r="F109" t="n">
+        <v>7</v>
+      </c>
+      <c r="G109" t="n">
+        <v>45</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -2529,17 +2529,25 @@
           <t>Elevate</t>
         </is>
       </c>
-      <c r="D56" t="n">
-        <v>12</v>
-      </c>
-      <c r="E56" t="n">
-        <v>2</v>
-      </c>
-      <c r="F56" t="n">
-        <v>6</v>
-      </c>
-      <c r="G56" t="n">
-        <v>83</v>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -3357,25 +3365,17 @@
           <t>TALON</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
+      <c r="D78" t="n">
+        <v>9</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" t="n">
+        <v>8</v>
+      </c>
+      <c r="G78" t="n">
+        <v>41</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -4535,17 +4535,25 @@
           <t>Titan</t>
         </is>
       </c>
-      <c r="D109" t="n">
-        <v>9</v>
-      </c>
-      <c r="E109" t="n">
-        <v>2</v>
-      </c>
-      <c r="F109" t="n">
-        <v>7</v>
-      </c>
-      <c r="G109" t="n">
-        <v>45</v>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -4565,25 +4573,17 @@
           <t>hoorai</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
+      <c r="D110" t="n">
+        <v>6</v>
+      </c>
+      <c r="E110" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" t="n">
+        <v>6</v>
+      </c>
+      <c r="G110" t="n">
+        <v>28</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -1313,25 +1313,19 @@
           <t>Copenhagen Flames</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
+      <c r="D24" t="n">
+        <v>15</v>
+      </c>
+      <c r="E24" t="n">
+        <v>8</v>
+      </c>
+      <c r="F24" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
+      <c r="G24" t="n">
+        <v>138</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -3365,17 +3359,25 @@
           <t>TALON</t>
         </is>
       </c>
-      <c r="D78" t="n">
-        <v>9</v>
-      </c>
-      <c r="E78" t="n">
-        <v>0</v>
-      </c>
-      <c r="F78" t="n">
-        <v>8</v>
-      </c>
-      <c r="G78" t="n">
-        <v>41</v>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -3435,22 +3437,22 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>61</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -4573,17 +4575,25 @@
           <t>hoorai</t>
         </is>
       </c>
-      <c r="D110" t="n">
-        <v>6</v>
-      </c>
-      <c r="E110" t="n">
-        <v>0</v>
-      </c>
-      <c r="F110" t="n">
-        <v>6</v>
-      </c>
-      <c r="G110" t="n">
-        <v>28</v>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -976,20 +976,14 @@
           <t>11</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>11</v>
+      </c>
+      <c r="G15" t="n">
+        <v>38</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1047,25 +1041,17 @@
           <t>G2</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="D17" t="n">
+        <v>7</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>8</v>
+      </c>
+      <c r="G17" t="n">
+        <v>18</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1313,19 +1299,25 @@
           <t>Copenhagen Flames</t>
         </is>
       </c>
-      <c r="D24" t="n">
-        <v>15</v>
-      </c>
-      <c r="E24" t="n">
-        <v>8</v>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>138</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -976,14 +976,20 @@
           <t>11</t>
         </is>
       </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>11</v>
-      </c>
-      <c r="G15" t="n">
-        <v>38</v>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1041,17 +1047,25 @@
           <t>G2</t>
         </is>
       </c>
-      <c r="D17" t="n">
-        <v>7</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>8</v>
-      </c>
-      <c r="G17" t="n">
-        <v>18</v>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -3161,25 +3175,17 @@
           <t>The MongolZ</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
+      <c r="D73" t="n">
+        <v>12</v>
+      </c>
+      <c r="E73" t="n">
+        <v>1</v>
+      </c>
+      <c r="F73" t="n">
+        <v>6</v>
+      </c>
+      <c r="G73" t="n">
+        <v>77</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -4645,22 +4651,22 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>64</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -477,25 +477,19 @@
           <t>Vitality</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="D2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E2" t="n">
+        <v>8</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
+      <c r="G2" t="n">
+        <v>92</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -553,25 +547,19 @@
           <t>Liquid</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="D4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E4" t="n">
+        <v>4</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
+      <c r="G4" t="n">
+        <v>63</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -634,20 +622,14 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>57</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -1242,20 +1224,14 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2</v>
+      </c>
+      <c r="G22" t="n">
+        <v>55</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1318,20 +1294,14 @@
           <t>15</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>5</v>
+      </c>
+      <c r="G24" t="n">
+        <v>133</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1508,20 +1478,14 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>8</v>
+      </c>
+      <c r="G29" t="n">
+        <v>45</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -2111,25 +2075,19 @@
           <t>Eternal Fire</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="D45" t="n">
+        <v>13</v>
+      </c>
+      <c r="E45" t="n">
+        <v>4</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
+      <c r="G45" t="n">
+        <v>85</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -2534,20 +2492,14 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
+      <c r="E56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" t="n">
+        <v>7</v>
+      </c>
+      <c r="G56" t="n">
+        <v>78</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -3175,17 +3127,25 @@
           <t>The MongolZ</t>
         </is>
       </c>
-      <c r="D73" t="n">
-        <v>12</v>
-      </c>
-      <c r="E73" t="n">
-        <v>1</v>
-      </c>
-      <c r="F73" t="n">
-        <v>6</v>
-      </c>
-      <c r="G73" t="n">
-        <v>77</v>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -3243,25 +3203,19 @@
           <t>PARIVISION</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="D75" t="n">
+        <v>8</v>
+      </c>
+      <c r="E75" t="n">
+        <v>5</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
+      <c r="G75" t="n">
+        <v>72</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -4122,20 +4076,14 @@
           <t>11</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
+      <c r="E98" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" t="n">
+        <v>5</v>
+      </c>
+      <c r="G98" t="n">
+        <v>80</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -4231,25 +4179,19 @@
           <t>Onyx Ravens</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="D101" t="n">
+        <v>8</v>
+      </c>
+      <c r="E101" t="n">
+        <v>5</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
+      <c r="G101" t="n">
+        <v>65</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -4535,25 +4477,19 @@
           <t>Titan</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="D109" t="n">
+        <v>10</v>
+      </c>
+      <c r="E109" t="n">
+        <v>3</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
+      <c r="G109" t="n">
+        <v>55</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -477,19 +477,25 @@
           <t>Vitality</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>8</v>
-      </c>
-      <c r="E2" t="n">
-        <v>8</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>92</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -547,19 +553,25 @@
           <t>Liquid</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>8</v>
-      </c>
-      <c r="E4" t="n">
-        <v>4</v>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>63</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -622,14 +634,20 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G6" t="n">
-        <v>57</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -1224,14 +1242,20 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>2</v>
-      </c>
-      <c r="G22" t="n">
-        <v>55</v>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1294,14 +1318,20 @@
           <t>15</t>
         </is>
       </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>5</v>
-      </c>
-      <c r="G24" t="n">
-        <v>133</v>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1478,14 +1508,20 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" t="n">
-        <v>8</v>
-      </c>
-      <c r="G29" t="n">
-        <v>45</v>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -2075,19 +2111,25 @@
           <t>Eternal Fire</t>
         </is>
       </c>
-      <c r="D45" t="n">
-        <v>13</v>
-      </c>
-      <c r="E45" t="n">
-        <v>4</v>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G45" t="n">
-        <v>85</v>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -2492,14 +2534,20 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E56" t="n">
-        <v>0</v>
-      </c>
-      <c r="F56" t="n">
-        <v>7</v>
-      </c>
-      <c r="G56" t="n">
-        <v>78</v>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -3203,19 +3251,25 @@
           <t>PARIVISION</t>
         </is>
       </c>
-      <c r="D75" t="n">
-        <v>8</v>
-      </c>
-      <c r="E75" t="n">
-        <v>5</v>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G75" t="n">
-        <v>72</v>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -4076,14 +4130,20 @@
           <t>11</t>
         </is>
       </c>
-      <c r="E98" t="n">
-        <v>0</v>
-      </c>
-      <c r="F98" t="n">
-        <v>5</v>
-      </c>
-      <c r="G98" t="n">
-        <v>80</v>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -4179,19 +4239,25 @@
           <t>Onyx Ravens</t>
         </is>
       </c>
-      <c r="D101" t="n">
-        <v>8</v>
-      </c>
-      <c r="E101" t="n">
-        <v>5</v>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G101" t="n">
-        <v>65</v>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -4477,19 +4543,25 @@
           <t>Titan</t>
         </is>
       </c>
-      <c r="D109" t="n">
-        <v>10</v>
-      </c>
-      <c r="E109" t="n">
-        <v>3</v>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="G109" t="n">
-        <v>55</v>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -479,12 +479,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -494,7 +494,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -517,7 +517,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -527,12 +527,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -555,22 +555,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -603,12 +603,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -631,7 +631,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -641,12 +641,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -717,12 +717,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -755,12 +755,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -793,12 +793,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -831,12 +831,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -895,25 +895,17 @@
           <t>Legacy</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="D13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>4</v>
+      </c>
+      <c r="G13" t="n">
+        <v>5</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -935,7 +927,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -945,12 +937,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -973,7 +965,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -983,12 +975,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1021,12 +1013,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1049,7 +1041,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1059,12 +1051,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1087,7 +1079,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1097,12 +1089,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1135,12 +1127,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1173,12 +1165,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1201,7 +1193,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1211,12 +1203,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1239,7 +1231,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1249,12 +1241,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1277,7 +1269,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1287,12 +1279,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1315,7 +1307,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1325,12 +1317,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1363,12 +1355,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1391,7 +1383,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1401,12 +1393,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1439,12 +1431,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1477,12 +1469,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1505,7 +1497,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1515,12 +1507,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1543,7 +1535,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1553,12 +1545,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1591,12 +1583,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1622,20 +1614,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-5</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -1657,22 +1643,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1705,12 +1691,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1743,12 +1729,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1771,7 +1757,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1781,12 +1767,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1819,12 +1805,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1847,7 +1833,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1857,12 +1843,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1895,12 +1881,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1933,12 +1919,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -1971,12 +1957,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2009,12 +1995,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2037,7 +2023,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2047,12 +2033,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2075,7 +2061,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2085,12 +2071,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2113,22 +2099,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2161,12 +2147,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2199,12 +2185,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2237,12 +2223,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2265,7 +2251,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2275,12 +2261,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2303,7 +2289,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2313,12 +2299,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2341,7 +2327,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2351,12 +2337,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2379,7 +2365,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2389,12 +2375,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2417,7 +2403,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2427,12 +2413,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2465,12 +2451,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2503,12 +2489,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2531,7 +2517,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2541,12 +2527,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2579,12 +2565,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2607,7 +2593,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2617,12 +2603,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2655,12 +2641,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -2683,7 +2669,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2693,12 +2679,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -2731,12 +2717,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -2759,7 +2745,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2769,12 +2755,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -2797,7 +2783,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2807,12 +2793,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -2838,20 +2824,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
+      <c r="E64" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" t="n">
+        <v>-5</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -2883,12 +2863,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -2921,12 +2901,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -2959,12 +2939,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -2987,7 +2967,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2997,12 +2977,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3025,7 +3005,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3035,12 +3015,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3073,12 +3053,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3101,7 +3081,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -3111,12 +3091,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3149,12 +3129,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3177,22 +3157,22 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3225,12 +3205,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3253,22 +3233,22 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3301,12 +3281,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -3329,7 +3309,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -3339,12 +3319,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3367,7 +3347,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -3377,12 +3357,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -3415,12 +3395,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3443,22 +3423,22 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3491,12 +3471,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -3529,12 +3509,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -3557,7 +3537,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -3567,12 +3547,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -3605,12 +3585,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -3643,12 +3623,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -3671,7 +3651,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -3681,12 +3661,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -3719,12 +3699,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -3757,12 +3737,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -3785,7 +3765,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -3795,12 +3775,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -3833,12 +3813,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -3871,12 +3851,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -3899,7 +3879,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -3909,12 +3889,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -3947,12 +3927,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -3975,7 +3955,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -3985,7 +3965,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -4013,7 +3993,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -4023,12 +4003,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4061,12 +4041,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4099,12 +4079,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -4127,7 +4107,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -4137,12 +4117,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -4175,12 +4155,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -4213,12 +4193,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -4241,22 +4221,22 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -4289,12 +4269,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -4327,12 +4307,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -4355,7 +4335,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -4365,12 +4345,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -4441,12 +4421,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -4479,12 +4459,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -4517,12 +4497,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -4545,22 +4525,22 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -4583,7 +4563,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -4593,12 +4573,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -4621,7 +4601,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -4631,7 +4611,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -4659,7 +4639,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -4669,12 +4649,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -4707,12 +4687,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -5011,12 +4991,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -895,17 +895,25 @@
           <t>Legacy</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>3</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>4</v>
-      </c>
-      <c r="G13" t="n">
-        <v>5</v>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1127,12 +1135,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1614,14 +1622,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E32" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G32" t="n">
-        <v>-5</v>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -2634,20 +2648,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E59" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" t="n">
+        <v>-5</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -2824,14 +2832,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E64" t="n">
-        <v>0</v>
-      </c>
-      <c r="F64" t="n">
-        <v>1</v>
-      </c>
-      <c r="G64" t="n">
-        <v>-5</v>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -4333,25 +4347,17 @@
           <t>Bad News Eagles</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D104" t="n">
+        <v>3</v>
+      </c>
+      <c r="E104" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" t="n">
+        <v>4</v>
+      </c>
+      <c r="G104" t="n">
+        <v>5</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
@@ -4639,7 +4645,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -4649,12 +4655,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>64</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -1166,20 +1166,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-5</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1655,25 +1649,17 @@
           <t>Iluminar</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D33" t="n">
+        <v>8</v>
+      </c>
+      <c r="E33" t="n">
+        <v>7</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" t="n">
+        <v>80</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -2496,20 +2482,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" t="n">
+        <v>-5</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -2529,25 +2509,17 @@
           <t>Elevate</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D56" t="n">
+        <v>11</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" t="n">
+        <v>8</v>
+      </c>
+      <c r="G56" t="n">
+        <v>56</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -2648,14 +2620,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E59" t="n">
-        <v>0</v>
-      </c>
-      <c r="F59" t="n">
-        <v>1</v>
-      </c>
-      <c r="G59" t="n">
-        <v>-5</v>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -4347,17 +4325,25 @@
           <t>Bad News Eagles</t>
         </is>
       </c>
-      <c r="D104" t="n">
-        <v>3</v>
-      </c>
-      <c r="E104" t="n">
-        <v>0</v>
-      </c>
-      <c r="F104" t="n">
-        <v>4</v>
-      </c>
-      <c r="G104" t="n">
-        <v>5</v>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -553,25 +553,17 @@
           <t>Liquid</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" t="n">
+        <v>63</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -596,20 +588,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-5</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -857,25 +843,17 @@
           <t>FURIA</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>6</v>
+      </c>
+      <c r="G12" t="n">
+        <v>5</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -933,25 +911,17 @@
           <t>MIBR</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>5</v>
+      </c>
+      <c r="G14" t="n">
+        <v>8</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1166,14 +1136,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" t="n">
-        <v>-5</v>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1535,25 +1511,17 @@
           <t>SK</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D30" t="n">
+        <v>3</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>4</v>
+      </c>
+      <c r="G30" t="n">
+        <v>5</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -1578,20 +1546,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-5</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -1649,17 +1611,25 @@
           <t>Iluminar</t>
         </is>
       </c>
-      <c r="D33" t="n">
-        <v>8</v>
-      </c>
-      <c r="E33" t="n">
-        <v>7</v>
-      </c>
-      <c r="F33" t="n">
-        <v>1</v>
-      </c>
-      <c r="G33" t="n">
-        <v>80</v>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -2216,20 +2186,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" t="n">
+        <v>-5</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -2249,25 +2213,17 @@
           <t>M80</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D49" t="n">
+        <v>3</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" t="n">
+        <v>4</v>
+      </c>
+      <c r="G49" t="n">
+        <v>7</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -2363,25 +2319,17 @@
           <t>ECSTATIC</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D52" t="n">
+        <v>2</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="n">
+        <v>4</v>
+      </c>
+      <c r="G52" t="n">
+        <v>-4</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -2401,25 +2349,17 @@
           <t>RED Canids</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D53" t="n">
+        <v>6</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" t="n">
+        <v>6</v>
+      </c>
+      <c r="G53" t="n">
+        <v>22</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -2444,20 +2384,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" t="n">
+        <v>-5</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -2482,14 +2416,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E55" t="n">
-        <v>0</v>
-      </c>
-      <c r="F55" t="n">
-        <v>1</v>
-      </c>
-      <c r="G55" t="n">
-        <v>-5</v>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -2509,17 +2449,25 @@
           <t>Elevate</t>
         </is>
       </c>
-      <c r="D56" t="n">
-        <v>11</v>
-      </c>
-      <c r="E56" t="n">
-        <v>0</v>
-      </c>
-      <c r="F56" t="n">
-        <v>8</v>
-      </c>
-      <c r="G56" t="n">
-        <v>56</v>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -2653,25 +2601,17 @@
           <t>Orbit</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D60" t="n">
+        <v>7</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" t="n">
+        <v>6</v>
+      </c>
+      <c r="G60" t="n">
+        <v>33</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -2848,20 +2788,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E65" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" t="n">
+        <v>-5</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -2995,25 +2929,17 @@
           <t>Bounty Hunters</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D69" t="n">
+        <v>9</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" t="n">
+        <v>8</v>
+      </c>
+      <c r="G69" t="n">
+        <v>45</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -3722,20 +3648,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E88" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" t="n">
+        <v>-5</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -4406,20 +4326,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E106" t="n">
+        <v>0</v>
+      </c>
+      <c r="F106" t="n">
+        <v>1</v>
+      </c>
+      <c r="G106" t="n">
+        <v>-5</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -4482,20 +4396,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E108" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" t="n">
+        <v>1</v>
+      </c>
+      <c r="G108" t="n">
+        <v>-5</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -4515,25 +4423,17 @@
           <t>Titan</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D109" t="n">
+        <v>10</v>
+      </c>
+      <c r="E109" t="n">
+        <v>3</v>
+      </c>
+      <c r="F109" t="n">
+        <v>7</v>
+      </c>
+      <c r="G109" t="n">
+        <v>55</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -4591,25 +4491,17 @@
           <t>GODSENT</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D111" t="n">
+        <v>3</v>
+      </c>
+      <c r="E111" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" t="n">
+        <v>5</v>
+      </c>
+      <c r="G111" t="n">
+        <v>0</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -4672,20 +4564,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E113" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" t="n">
+        <v>1</v>
+      </c>
+      <c r="G113" t="n">
+        <v>-5</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -553,17 +553,25 @@
           <t>Liquid</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>8</v>
-      </c>
-      <c r="E4" t="n">
-        <v>4</v>
-      </c>
-      <c r="F4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G4" t="n">
-        <v>63</v>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -588,14 +596,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" t="n">
-        <v>-5</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -843,17 +857,25 @@
           <t>FURIA</t>
         </is>
       </c>
-      <c r="D12" t="n">
-        <v>4</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>6</v>
-      </c>
-      <c r="G12" t="n">
-        <v>5</v>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -911,17 +933,25 @@
           <t>MIBR</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>4</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>5</v>
-      </c>
-      <c r="G14" t="n">
-        <v>8</v>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1055,25 +1085,17 @@
           <t>OG</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D18" t="n">
+        <v>8</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>6</v>
+      </c>
+      <c r="G18" t="n">
+        <v>39</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1511,17 +1533,25 @@
           <t>SK</t>
         </is>
       </c>
-      <c r="D30" t="n">
-        <v>3</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" t="n">
-        <v>4</v>
-      </c>
-      <c r="G30" t="n">
-        <v>5</v>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -1546,14 +1576,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E31" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" t="n">
-        <v>1</v>
-      </c>
-      <c r="G31" t="n">
-        <v>-5</v>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -2186,14 +2222,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E48" t="n">
-        <v>0</v>
-      </c>
-      <c r="F48" t="n">
-        <v>1</v>
-      </c>
-      <c r="G48" t="n">
-        <v>-5</v>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -2213,17 +2255,25 @@
           <t>M80</t>
         </is>
       </c>
-      <c r="D49" t="n">
-        <v>3</v>
-      </c>
-      <c r="E49" t="n">
-        <v>0</v>
-      </c>
-      <c r="F49" t="n">
-        <v>4</v>
-      </c>
-      <c r="G49" t="n">
-        <v>7</v>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -2319,17 +2369,25 @@
           <t>ECSTATIC</t>
         </is>
       </c>
-      <c r="D52" t="n">
-        <v>2</v>
-      </c>
-      <c r="E52" t="n">
-        <v>0</v>
-      </c>
-      <c r="F52" t="n">
-        <v>4</v>
-      </c>
-      <c r="G52" t="n">
-        <v>-4</v>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-4</t>
+        </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -2349,17 +2407,25 @@
           <t>RED Canids</t>
         </is>
       </c>
-      <c r="D53" t="n">
-        <v>6</v>
-      </c>
-      <c r="E53" t="n">
-        <v>0</v>
-      </c>
-      <c r="F53" t="n">
-        <v>6</v>
-      </c>
-      <c r="G53" t="n">
-        <v>22</v>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -2384,14 +2450,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E54" t="n">
-        <v>0</v>
-      </c>
-      <c r="F54" t="n">
-        <v>1</v>
-      </c>
-      <c r="G54" t="n">
-        <v>-5</v>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -2601,17 +2673,25 @@
           <t>Orbit</t>
         </is>
       </c>
-      <c r="D60" t="n">
-        <v>7</v>
-      </c>
-      <c r="E60" t="n">
-        <v>0</v>
-      </c>
-      <c r="F60" t="n">
-        <v>6</v>
-      </c>
-      <c r="G60" t="n">
-        <v>33</v>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -2788,14 +2868,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E65" t="n">
-        <v>0</v>
-      </c>
-      <c r="F65" t="n">
-        <v>1</v>
-      </c>
-      <c r="G65" t="n">
-        <v>-5</v>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -2929,17 +3015,25 @@
           <t>Bounty Hunters</t>
         </is>
       </c>
-      <c r="D69" t="n">
-        <v>9</v>
-      </c>
-      <c r="E69" t="n">
-        <v>0</v>
-      </c>
-      <c r="F69" t="n">
-        <v>8</v>
-      </c>
-      <c r="G69" t="n">
-        <v>45</v>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -2964,20 +3058,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E70" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" t="n">
+        <v>-5</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -3648,14 +3736,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E88" t="n">
-        <v>0</v>
-      </c>
-      <c r="F88" t="n">
-        <v>1</v>
-      </c>
-      <c r="G88" t="n">
-        <v>-5</v>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -4326,14 +4420,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E106" t="n">
-        <v>0</v>
-      </c>
-      <c r="F106" t="n">
-        <v>1</v>
-      </c>
-      <c r="G106" t="n">
-        <v>-5</v>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -4396,14 +4496,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E108" t="n">
-        <v>0</v>
-      </c>
-      <c r="F108" t="n">
-        <v>1</v>
-      </c>
-      <c r="G108" t="n">
-        <v>-5</v>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -4423,17 +4529,25 @@
           <t>Titan</t>
         </is>
       </c>
-      <c r="D109" t="n">
-        <v>10</v>
-      </c>
-      <c r="E109" t="n">
-        <v>3</v>
-      </c>
-      <c r="F109" t="n">
-        <v>7</v>
-      </c>
-      <c r="G109" t="n">
-        <v>55</v>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -4491,17 +4605,25 @@
           <t>GODSENT</t>
         </is>
       </c>
-      <c r="D111" t="n">
-        <v>3</v>
-      </c>
-      <c r="E111" t="n">
-        <v>0</v>
-      </c>
-      <c r="F111" t="n">
-        <v>5</v>
-      </c>
-      <c r="G111" t="n">
-        <v>0</v>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -4564,14 +4686,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E113" t="n">
-        <v>0</v>
-      </c>
-      <c r="F113" t="n">
-        <v>1</v>
-      </c>
-      <c r="G113" t="n">
-        <v>-5</v>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -477,25 +477,19 @@
           <t>Vitality</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E2" t="n">
+        <v>8</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G2" t="n">
+        <v>92</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -515,25 +509,17 @@
           <t>Astralis</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-12</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -629,25 +615,17 @@
           <t>Heroic</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>57</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -705,25 +683,17 @@
           <t>FaZe</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>4</v>
+      </c>
+      <c r="G8" t="n">
+        <v>15</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -755,12 +725,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -781,25 +751,17 @@
           <t>ENCE</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>4</v>
+      </c>
+      <c r="G10" t="n">
+        <v>5</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -831,12 +793,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-15</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1009,25 +971,17 @@
           <t>MOUZ</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>3</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-7</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1047,25 +1001,17 @@
           <t>G2</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D17" t="n">
+        <v>7</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>8</v>
+      </c>
+      <c r="G17" t="n">
+        <v>18</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1085,17 +1031,25 @@
           <t>OG</t>
         </is>
       </c>
-      <c r="D18" t="n">
-        <v>8</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>6</v>
-      </c>
-      <c r="G18" t="n">
-        <v>39</v>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1305,25 +1259,17 @@
           <t>Copenhagen Flames</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D24" t="n">
+        <v>15</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>5</v>
+      </c>
+      <c r="G24" t="n">
+        <v>133</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1355,12 +1301,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1381,25 +1327,17 @@
           <t>iBUYPOWER</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>4</v>
+      </c>
+      <c r="G26" t="n">
+        <v>15</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1457,25 +1395,17 @@
           <t>Dignitas</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D28" t="n">
+        <v>3</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>4</v>
+      </c>
+      <c r="G28" t="n">
+        <v>4</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -1495,25 +1425,17 @@
           <t>Cloud9</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>8</v>
+      </c>
+      <c r="G29" t="n">
+        <v>45</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -1685,25 +1607,17 @@
           <t>Falcons</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D34" t="n">
+        <v>6</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>3</v>
+      </c>
+      <c r="G34" t="n">
+        <v>39</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -1763,7 +1677,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1773,12 +1687,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1837,25 +1751,17 @@
           <t>Nexus</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D38" t="n">
+        <v>4</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>4</v>
+      </c>
+      <c r="G38" t="n">
+        <v>13</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -1925,12 +1831,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -1963,12 +1869,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2029,7 +1935,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2039,12 +1945,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2065,25 +1971,17 @@
           <t>Rebels</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D44" t="n">
+        <v>10</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>7</v>
+      </c>
+      <c r="G44" t="n">
+        <v>54</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -2103,25 +2001,17 @@
           <t>Eternal Fire</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D45" t="n">
+        <v>13</v>
+      </c>
+      <c r="E45" t="n">
+        <v>4</v>
+      </c>
+      <c r="F45" t="n">
+        <v>6</v>
+      </c>
+      <c r="G45" t="n">
+        <v>85</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -2146,20 +2036,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" t="n">
+        <v>-5</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -2184,20 +2068,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="n">
+        <v>3</v>
+      </c>
+      <c r="G47" t="n">
+        <v>-15</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -2293,25 +2171,17 @@
           <t>Wildcard</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="n">
+        <v>4</v>
+      </c>
+      <c r="G50" t="n">
+        <v>-12</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -2571,12 +2441,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2723,12 +2593,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3058,14 +2928,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E70" t="n">
-        <v>0</v>
-      </c>
-      <c r="F70" t="n">
-        <v>1</v>
-      </c>
-      <c r="G70" t="n">
-        <v>-5</v>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -3211,12 +3087,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4455,7 +4331,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -4465,12 +4341,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -4997,12 +4873,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -477,19 +477,25 @@
           <t>Vitality</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>8</v>
-      </c>
-      <c r="E2" t="n">
-        <v>8</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>92</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -509,17 +515,25 @@
           <t>Astralis</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>4</v>
-      </c>
-      <c r="G3" t="n">
-        <v>-12</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-12</t>
+        </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -615,17 +629,25 @@
           <t>Heroic</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>7</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G6" t="n">
-        <v>57</v>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -683,17 +705,25 @@
           <t>FaZe</t>
         </is>
       </c>
-      <c r="D8" t="n">
-        <v>4</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>4</v>
-      </c>
-      <c r="G8" t="n">
-        <v>15</v>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -751,17 +781,25 @@
           <t>ENCE</t>
         </is>
       </c>
-      <c r="D10" t="n">
-        <v>3</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>4</v>
-      </c>
-      <c r="G10" t="n">
-        <v>5</v>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -933,25 +971,17 @@
           <t>Natus Vincere</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D15" t="n">
+        <v>8</v>
+      </c>
+      <c r="E15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>72</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -971,17 +1001,25 @@
           <t>MOUZ</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>3</v>
-      </c>
-      <c r="G16" t="n">
-        <v>-7</v>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-7</t>
+        </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1001,17 +1039,25 @@
           <t>G2</t>
         </is>
       </c>
-      <c r="D17" t="n">
-        <v>7</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>8</v>
-      </c>
-      <c r="G17" t="n">
-        <v>18</v>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1145,25 +1191,17 @@
           <t>Virtus.pro</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>4</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-4</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1183,25 +1221,17 @@
           <t>Spirit</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D22" t="n">
+        <v>7</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2</v>
+      </c>
+      <c r="G22" t="n">
+        <v>55</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1221,25 +1251,17 @@
           <t>Entropiq</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>4</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-12</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1259,17 +1281,25 @@
           <t>Copenhagen Flames</t>
         </is>
       </c>
-      <c r="D24" t="n">
-        <v>15</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>5</v>
-      </c>
-      <c r="G24" t="n">
-        <v>133</v>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1327,17 +1357,25 @@
           <t>iBUYPOWER</t>
         </is>
       </c>
-      <c r="D26" t="n">
-        <v>4</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" t="n">
-        <v>4</v>
-      </c>
-      <c r="G26" t="n">
-        <v>15</v>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1369,12 +1407,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1395,17 +1433,25 @@
           <t>Dignitas</t>
         </is>
       </c>
-      <c r="D28" t="n">
-        <v>3</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" t="n">
-        <v>4</v>
-      </c>
-      <c r="G28" t="n">
-        <v>4</v>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -1425,17 +1471,25 @@
           <t>Cloud9</t>
         </is>
       </c>
-      <c r="D29" t="n">
-        <v>10</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" t="n">
-        <v>8</v>
-      </c>
-      <c r="G29" t="n">
-        <v>45</v>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -1607,17 +1661,25 @@
           <t>Falcons</t>
         </is>
       </c>
-      <c r="D34" t="n">
-        <v>6</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" t="n">
-        <v>3</v>
-      </c>
-      <c r="G34" t="n">
-        <v>39</v>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -1649,12 +1711,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1725,12 +1787,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1751,17 +1813,25 @@
           <t>Nexus</t>
         </is>
       </c>
-      <c r="D38" t="n">
-        <v>4</v>
-      </c>
-      <c r="E38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" t="n">
-        <v>4</v>
-      </c>
-      <c r="G38" t="n">
-        <v>13</v>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -1793,12 +1863,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1907,12 +1977,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -1971,17 +2041,25 @@
           <t>Rebels</t>
         </is>
       </c>
-      <c r="D44" t="n">
-        <v>10</v>
-      </c>
-      <c r="E44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" t="n">
-        <v>7</v>
-      </c>
-      <c r="G44" t="n">
-        <v>54</v>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -2001,17 +2079,25 @@
           <t>Eternal Fire</t>
         </is>
       </c>
-      <c r="D45" t="n">
-        <v>13</v>
-      </c>
-      <c r="E45" t="n">
-        <v>4</v>
-      </c>
-      <c r="F45" t="n">
-        <v>6</v>
-      </c>
-      <c r="G45" t="n">
-        <v>85</v>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -2036,14 +2122,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E46" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" t="n">
-        <v>1</v>
-      </c>
-      <c r="G46" t="n">
-        <v>-5</v>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -2068,14 +2160,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E47" t="n">
-        <v>0</v>
-      </c>
-      <c r="F47" t="n">
-        <v>3</v>
-      </c>
-      <c r="G47" t="n">
-        <v>-15</v>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-15</t>
+        </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -2171,17 +2269,25 @@
           <t>Wildcard</t>
         </is>
       </c>
-      <c r="D50" t="n">
-        <v>1</v>
-      </c>
-      <c r="E50" t="n">
-        <v>0</v>
-      </c>
-      <c r="F50" t="n">
-        <v>4</v>
-      </c>
-      <c r="G50" t="n">
-        <v>-12</v>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>-12</t>
+        </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -2201,25 +2307,17 @@
           <t>BESTIA</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D51" t="n">
+        <v>9</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="n">
+        <v>8</v>
+      </c>
+      <c r="G51" t="n">
+        <v>40</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -2467,25 +2565,17 @@
           <t>Underground</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D58" t="n">
+        <v>2</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" t="n">
+        <v>4</v>
+      </c>
+      <c r="G58" t="n">
+        <v>-3</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -2619,25 +2709,17 @@
           <t>Homyno</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D62" t="n">
+        <v>4</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" t="n">
+        <v>4</v>
+      </c>
+      <c r="G62" t="n">
+        <v>15</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -2657,25 +2739,17 @@
           <t>Take Flyte</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D63" t="n">
+        <v>2</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" t="n">
+        <v>4</v>
+      </c>
+      <c r="G63" t="n">
+        <v>-4</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -2783,12 +2857,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -2821,12 +2895,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -2844,28 +2918,20 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Team Solid</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>Solid</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>4</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" t="n">
+        <v>4</v>
+      </c>
+      <c r="G68" t="n">
+        <v>15</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -2963,7 +3029,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2973,12 +3039,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3011,12 +3077,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3037,25 +3103,17 @@
           <t>The MongolZ</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D73" t="n">
+        <v>13</v>
+      </c>
+      <c r="E73" t="n">
+        <v>2</v>
+      </c>
+      <c r="F73" t="n">
+        <v>6</v>
+      </c>
+      <c r="G73" t="n">
+        <v>86</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -3115,22 +3173,22 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>72</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3163,12 +3221,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -3189,25 +3247,17 @@
           <t>VP.Prodigy</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D77" t="n">
+        <v>2</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" t="n">
+        <v>4</v>
+      </c>
+      <c r="G77" t="n">
+        <v>-3</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -3229,7 +3279,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -3239,12 +3289,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>41</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -3277,12 +3327,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3305,7 +3355,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -3315,12 +3365,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>38</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3353,12 +3403,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -3391,12 +3441,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -3417,25 +3467,17 @@
           <t>TYLOO</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D83" t="n">
+        <v>9</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" t="n">
+        <v>8</v>
+      </c>
+      <c r="G83" t="n">
+        <v>42</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -3467,12 +3509,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -3505,12 +3547,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -3533,7 +3575,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -3543,12 +3585,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -3581,12 +3623,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -3645,25 +3687,17 @@
           <t>MenaceGG</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D89" t="n">
+        <v>4</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" t="n">
+        <v>4</v>
+      </c>
+      <c r="G89" t="n">
+        <v>13</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -3695,12 +3729,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -3733,12 +3767,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -3759,25 +3793,17 @@
           <t>Aravt</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D92" t="n">
+        <v>3</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" t="n">
+        <v>4</v>
+      </c>
+      <c r="G92" t="n">
+        <v>5</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -3809,12 +3835,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -3835,25 +3861,17 @@
           <t>True Rippers</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D94" t="n">
+        <v>3</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" t="n">
+        <v>5</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -3875,7 +3893,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -3885,12 +3903,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -3923,12 +3941,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -3961,12 +3979,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -3989,7 +4007,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -3999,12 +4017,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>80</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -4037,12 +4055,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -4075,12 +4093,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -4101,25 +4119,17 @@
           <t>Onyx Ravens</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D101" t="n">
+        <v>11</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" t="n">
+        <v>9</v>
+      </c>
+      <c r="G101" t="n">
+        <v>48</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -4151,12 +4161,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -4174,7 +4184,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Reason Gaming</t>
+          <t>Reason</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -4189,12 +4199,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-15</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -4443,25 +4453,17 @@
           <t>hoorai</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D110" t="n">
+        <v>6</v>
+      </c>
+      <c r="E110" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" t="n">
+        <v>6</v>
+      </c>
+      <c r="G110" t="n">
+        <v>28</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -4972,7 +4974,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Team Kinguin</t>
+          <t>Kinguin</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -482,20 +482,14 @@
           <t>8</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>87</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -553,25 +547,19 @@
           <t>Liquid</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="D4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E4" t="n">
+        <v>5</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
+      <c r="G4" t="n">
+        <v>75</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -971,17 +959,19 @@
           <t>Natus Vincere</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>8</v>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="E15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" t="n">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1191,17 +1181,25 @@
           <t>Virtus.pro</t>
         </is>
       </c>
-      <c r="D21" t="n">
-        <v>2</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>4</v>
-      </c>
-      <c r="G21" t="n">
-        <v>-4</v>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-4</t>
+        </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1221,17 +1219,25 @@
           <t>Spirit</t>
         </is>
       </c>
-      <c r="D22" t="n">
-        <v>7</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>2</v>
-      </c>
-      <c r="G22" t="n">
-        <v>55</v>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1251,17 +1257,25 @@
           <t>Entropiq</t>
         </is>
       </c>
-      <c r="D23" t="n">
-        <v>1</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>4</v>
-      </c>
-      <c r="G23" t="n">
-        <v>-12</v>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-12</t>
+        </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -2307,17 +2321,25 @@
           <t>BESTIA</t>
         </is>
       </c>
-      <c r="D51" t="n">
-        <v>9</v>
-      </c>
-      <c r="E51" t="n">
-        <v>0</v>
-      </c>
-      <c r="F51" t="n">
-        <v>8</v>
-      </c>
-      <c r="G51" t="n">
-        <v>40</v>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -2565,17 +2587,25 @@
           <t>Underground</t>
         </is>
       </c>
-      <c r="D58" t="n">
-        <v>2</v>
-      </c>
-      <c r="E58" t="n">
-        <v>0</v>
-      </c>
-      <c r="F58" t="n">
-        <v>4</v>
-      </c>
-      <c r="G58" t="n">
-        <v>-3</v>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>-3</t>
+        </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -2709,17 +2739,25 @@
           <t>Homyno</t>
         </is>
       </c>
-      <c r="D62" t="n">
-        <v>4</v>
-      </c>
-      <c r="E62" t="n">
-        <v>0</v>
-      </c>
-      <c r="F62" t="n">
-        <v>4</v>
-      </c>
-      <c r="G62" t="n">
-        <v>15</v>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -2739,17 +2777,25 @@
           <t>Take Flyte</t>
         </is>
       </c>
-      <c r="D63" t="n">
-        <v>2</v>
-      </c>
-      <c r="E63" t="n">
-        <v>0</v>
-      </c>
-      <c r="F63" t="n">
-        <v>4</v>
-      </c>
-      <c r="G63" t="n">
-        <v>-4</v>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>-4</t>
+        </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -2921,17 +2967,25 @@
           <t>Solid</t>
         </is>
       </c>
-      <c r="D68" t="n">
-        <v>4</v>
-      </c>
-      <c r="E68" t="n">
-        <v>0</v>
-      </c>
-      <c r="F68" t="n">
-        <v>4</v>
-      </c>
-      <c r="G68" t="n">
-        <v>15</v>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -3104,16 +3158,18 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
-      </c>
-      <c r="F73" t="n">
-        <v>6</v>
+        <v>3</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="G73" t="n">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -3176,20 +3232,14 @@
           <t>8</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
+      <c r="E75" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" t="n">
+        <v>2</v>
+      </c>
+      <c r="G75" t="n">
+        <v>67</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -3247,17 +3297,25 @@
           <t>VP.Prodigy</t>
         </is>
       </c>
-      <c r="D77" t="n">
-        <v>2</v>
-      </c>
-      <c r="E77" t="n">
-        <v>0</v>
-      </c>
-      <c r="F77" t="n">
-        <v>4</v>
-      </c>
-      <c r="G77" t="n">
-        <v>-3</v>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>-3</t>
+        </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -3467,17 +3525,25 @@
           <t>TYLOO</t>
         </is>
       </c>
-      <c r="D83" t="n">
-        <v>9</v>
-      </c>
-      <c r="E83" t="n">
-        <v>0</v>
-      </c>
-      <c r="F83" t="n">
-        <v>8</v>
-      </c>
-      <c r="G83" t="n">
-        <v>42</v>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -3687,17 +3753,25 @@
           <t>MenaceGG</t>
         </is>
       </c>
-      <c r="D89" t="n">
-        <v>4</v>
-      </c>
-      <c r="E89" t="n">
-        <v>0</v>
-      </c>
-      <c r="F89" t="n">
-        <v>4</v>
-      </c>
-      <c r="G89" t="n">
-        <v>13</v>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -3793,17 +3867,25 @@
           <t>Aravt</t>
         </is>
       </c>
-      <c r="D92" t="n">
-        <v>3</v>
-      </c>
-      <c r="E92" t="n">
-        <v>0</v>
-      </c>
-      <c r="F92" t="n">
-        <v>4</v>
-      </c>
-      <c r="G92" t="n">
-        <v>5</v>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -3861,17 +3943,25 @@
           <t>True Rippers</t>
         </is>
       </c>
-      <c r="D94" t="n">
-        <v>3</v>
-      </c>
-      <c r="E94" t="n">
-        <v>0</v>
-      </c>
-      <c r="F94" t="n">
-        <v>5</v>
-      </c>
-      <c r="G94" t="n">
-        <v>0</v>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -4119,17 +4209,25 @@
           <t>Onyx Ravens</t>
         </is>
       </c>
-      <c r="D101" t="n">
-        <v>11</v>
-      </c>
-      <c r="E101" t="n">
-        <v>0</v>
-      </c>
-      <c r="F101" t="n">
-        <v>9</v>
-      </c>
-      <c r="G101" t="n">
-        <v>48</v>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -4415,25 +4513,19 @@
           <t>Titan</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="D109" t="n">
+        <v>11</v>
+      </c>
+      <c r="E109" t="n">
+        <v>4</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
+      <c r="G109" t="n">
+        <v>66</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -4453,17 +4545,25 @@
           <t>hoorai</t>
         </is>
       </c>
-      <c r="D110" t="n">
-        <v>6</v>
-      </c>
-      <c r="E110" t="n">
-        <v>0</v>
-      </c>
-      <c r="F110" t="n">
-        <v>6</v>
-      </c>
-      <c r="G110" t="n">
-        <v>28</v>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -482,14 +482,20 @@
           <t>8</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" t="n">
-        <v>87</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -547,19 +553,25 @@
           <t>Liquid</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>9</v>
-      </c>
-      <c r="E4" t="n">
-        <v>5</v>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>75</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -964,14 +976,20 @@
           <t>8</t>
         </is>
       </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>2</v>
-      </c>
-      <c r="G15" t="n">
-        <v>67</v>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1637,25 +1655,19 @@
           <t>Iluminar</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="D33" t="n">
+        <v>9</v>
+      </c>
+      <c r="E33" t="n">
+        <v>8</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="G33" t="n">
+        <v>95</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -2098,20 +2110,14 @@
           <t>13</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="n">
+        <v>7</v>
+      </c>
+      <c r="G45" t="n">
+        <v>80</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -3157,19 +3163,25 @@
           <t>The MongolZ</t>
         </is>
       </c>
-      <c r="D73" t="n">
-        <v>14</v>
-      </c>
-      <c r="E73" t="n">
-        <v>3</v>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G73" t="n">
-        <v>96</v>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -3232,14 +3244,20 @@
           <t>8</t>
         </is>
       </c>
-      <c r="E75" t="n">
-        <v>0</v>
-      </c>
-      <c r="F75" t="n">
-        <v>2</v>
-      </c>
-      <c r="G75" t="n">
-        <v>67</v>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -4513,19 +4531,25 @@
           <t>Titan</t>
         </is>
       </c>
-      <c r="D109" t="n">
-        <v>11</v>
-      </c>
-      <c r="E109" t="n">
-        <v>4</v>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="G109" t="n">
-        <v>66</v>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -812,19 +812,25 @@
           <t>FURIA</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v>3</v>
-      </c>
-      <c r="D12" t="n">
-        <v>3</v>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" t="n">
-        <v>27</v>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>

--- a/hltv.xlsx
+++ b/hltv.xlsx
@@ -464,27 +464,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
     </row>
